--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -24798,6 +24798,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1063">
+      <c r="A1063" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1063" t="n">
+        <v>14988</v>
+      </c>
+      <c r="C1063" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>20.7999992370605</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>20.7999992370605</v>
+      </c>
+      <c r="G1063" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -24821,6 +24821,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1064">
+      <c r="A1064" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1064" t="n">
+        <v>6157</v>
+      </c>
+      <c r="C1064" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>20.7999992370605</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="G1064" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -24844,6 +24844,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1065">
+      <c r="A1065" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1065" t="n">
+        <v>7192</v>
+      </c>
+      <c r="C1065" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1065" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -24867,6 +24867,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1066">
+      <c r="A1066" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1066" t="n">
+        <v>8111</v>
+      </c>
+      <c r="C1066" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>21</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>21.1000003814697</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="G1066" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -24708,10 +24708,10 @@
     </row>
     <row r="1059">
       <c r="A1059" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1059" t="n">
-        <v>6058</v>
+        <v>13893</v>
       </c>
       <c r="C1059" t="n">
         <v>21.5</v>
@@ -24720,10 +24720,10 @@
         <v>20.8999996185303</v>
       </c>
       <c r="E1059" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="F1059" t="n">
         <v>21</v>
-      </c>
-      <c r="F1059" t="n">
-        <v>21.2000007629395</v>
       </c>
       <c r="G1059" t="s">
         <v>7</v>
@@ -24731,22 +24731,22 @@
     </row>
     <row r="1060">
       <c r="A1060" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1060" t="n">
-        <v>6398</v>
+        <v>6058</v>
       </c>
       <c r="C1060" t="n">
-        <v>21.2999992370605</v>
+        <v>21.5</v>
       </c>
       <c r="D1060" t="n">
         <v>20.8999996185303</v>
       </c>
       <c r="E1060" t="n">
-        <v>21.2999992370605</v>
+        <v>21</v>
       </c>
       <c r="F1060" t="n">
-        <v>20.8999996185303</v>
+        <v>21.2000007629395</v>
       </c>
       <c r="G1060" t="s">
         <v>7</v>
@@ -24754,22 +24754,22 @@
     </row>
     <row r="1061">
       <c r="A1061" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1061" t="n">
-        <v>9967</v>
+        <v>6398</v>
       </c>
       <c r="C1061" t="n">
-        <v>21.5</v>
+        <v>21.2999992370605</v>
       </c>
       <c r="D1061" t="n">
-        <v>21</v>
+        <v>20.8999996185303</v>
       </c>
       <c r="E1061" t="n">
-        <v>21</v>
+        <v>21.2999992370605</v>
       </c>
       <c r="F1061" t="n">
-        <v>21.1000003814697</v>
+        <v>20.8999996185303</v>
       </c>
       <c r="G1061" t="s">
         <v>7</v>
@@ -24777,22 +24777,22 @@
     </row>
     <row r="1062">
       <c r="A1062" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1062" t="n">
-        <v>11073</v>
+        <v>9967</v>
       </c>
       <c r="C1062" t="n">
-        <v>21.7000007629395</v>
+        <v>21.5</v>
       </c>
       <c r="D1062" t="n">
-        <v>21.2000007629395</v>
+        <v>21</v>
       </c>
       <c r="E1062" t="n">
-        <v>21.2000007629395</v>
+        <v>21</v>
       </c>
       <c r="F1062" t="n">
-        <v>21.3999996185303</v>
+        <v>21.1000003814697</v>
       </c>
       <c r="G1062" t="s">
         <v>7</v>
@@ -24800,22 +24800,22 @@
     </row>
     <row r="1063">
       <c r="A1063" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1063" t="n">
-        <v>14988</v>
+        <v>11073</v>
       </c>
       <c r="C1063" t="n">
-        <v>21.5</v>
+        <v>21.7000007629395</v>
       </c>
       <c r="D1063" t="n">
-        <v>20.7999992370605</v>
+        <v>21.2000007629395</v>
       </c>
       <c r="E1063" t="n">
-        <v>21.5</v>
+        <v>21.2000007629395</v>
       </c>
       <c r="F1063" t="n">
-        <v>20.7999992370605</v>
+        <v>21.3999996185303</v>
       </c>
       <c r="G1063" t="s">
         <v>7</v>
@@ -24823,22 +24823,22 @@
     </row>
     <row r="1064">
       <c r="A1064" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1064" t="n">
-        <v>6157</v>
+        <v>14988</v>
       </c>
       <c r="C1064" t="n">
-        <v>21.2000007629395</v>
+        <v>21.5</v>
       </c>
       <c r="D1064" t="n">
-        <v>20.7000007629395</v>
+        <v>20.7999992370605</v>
       </c>
       <c r="E1064" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F1064" t="n">
         <v>20.7999992370605</v>
-      </c>
-      <c r="F1064" t="n">
-        <v>21.2000007629395</v>
       </c>
       <c r="G1064" t="s">
         <v>7</v>
@@ -24846,22 +24846,22 @@
     </row>
     <row r="1065">
       <c r="A1065" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1065" t="n">
-        <v>7192</v>
+        <v>6157</v>
       </c>
       <c r="C1065" t="n">
-        <v>21.3999996185303</v>
+        <v>21.2000007629395</v>
       </c>
       <c r="D1065" t="n">
-        <v>20.8999996185303</v>
+        <v>20.7000007629395</v>
       </c>
       <c r="E1065" t="n">
-        <v>20.8999996185303</v>
+        <v>20.7999992370605</v>
       </c>
       <c r="F1065" t="n">
-        <v>21</v>
+        <v>21.2000007629395</v>
       </c>
       <c r="G1065" t="s">
         <v>7</v>
@@ -24869,24 +24869,47 @@
     </row>
     <row r="1066">
       <c r="A1066" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1066" t="n">
-        <v>8111</v>
+        <v>7192</v>
       </c>
       <c r="C1066" t="n">
-        <v>21.8999996185303</v>
+        <v>21.3999996185303</v>
       </c>
       <c r="D1066" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="F1066" t="n">
         <v>21</v>
       </c>
-      <c r="E1066" t="n">
-        <v>21.1000003814697</v>
-      </c>
-      <c r="F1066" t="n">
+      <c r="G1066" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1067" t="n">
+        <v>16891</v>
+      </c>
+      <c r="C1067" t="n">
         <v>21.7999992370605</v>
       </c>
-      <c r="G1066" t="s">
+      <c r="D1067" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="G1067" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G3" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G8" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G11" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G12" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G13" t="n">
-        <v>5.86392879486084</v>
+        <v>5.86392831802368</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>5.77458906173706</v>
+        <v>5.7745885848999</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G36" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G41" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G42" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G53" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G62" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G68" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G70" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G72" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G79" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G81" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>5.88017225265503</v>
+        <v>5.88017177581787</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G91" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>5.86392879486084</v>
+        <v>5.86392831802368</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G93" t="n">
-        <v>5.88017225265503</v>
+        <v>5.88017177581787</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>5.88017225265503</v>
+        <v>5.88017177581787</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G102" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G104" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G105" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G114" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G116" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G126" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G128" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>5.66900539398193</v>
+        <v>5.66900587081909</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>5.66900539398193</v>
+        <v>5.66900587081909</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G154" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>7.5</v>
       </c>
       <c r="G162" t="n">
-        <v>6.09133815765381</v>
+        <v>6.09133863449097</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>6.46494054794312</v>
+        <v>6.46494102478027</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>6.27001762390137</v>
+        <v>6.27001714706421</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G166" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G170" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>6.41621017456055</v>
+        <v>6.41620969772339</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>6.41621017456055</v>
+        <v>6.41620969772339</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G177" t="n">
-        <v>6.20504331588745</v>
+        <v>6.20504379272461</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G181" t="n">
-        <v>6.4811840057373</v>
+        <v>6.48118352890015</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483730316162</v>
+        <v>6.72483777999878</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G191" t="n">
-        <v>6.78981161117554</v>
+        <v>6.7898120880127</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G194" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G195" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G196" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8</v>
       </c>
       <c r="G197" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8</v>
       </c>
       <c r="G199" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G200" t="n">
-        <v>6.97704172134399</v>
+        <v>6.97704124450684</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G201" t="n">
-        <v>6.97704172134399</v>
+        <v>6.97704124450684</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>8</v>
       </c>
       <c r="G209" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8</v>
       </c>
       <c r="G210" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G212" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G217" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8</v>
       </c>
       <c r="G232" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G236" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180593490601</v>
+        <v>6.59180641174316</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G240" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G254" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>8</v>
       </c>
       <c r="G257" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8</v>
       </c>
       <c r="G259" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G261" t="n">
-        <v>6.97704172134399</v>
+        <v>6.97704124450684</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8</v>
       </c>
       <c r="G270" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8</v>
       </c>
       <c r="G272" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G276" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G281" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8</v>
       </c>
       <c r="G287" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>8</v>
       </c>
       <c r="G288" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>8</v>
       </c>
       <c r="G294" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>8</v>
       </c>
       <c r="G295" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>8</v>
       </c>
       <c r="G296" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G298" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8</v>
       </c>
       <c r="G300" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G307" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G308" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8</v>
       </c>
       <c r="G325" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>7.1482572555542</v>
+        <v>7.14825773239136</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83312034606934</v>
+        <v>7.83311986923218</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G406" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G422" t="n">
-        <v>8.81761169433594</v>
+        <v>8.81761074066162</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>8.73200225830078</v>
+        <v>8.7320032119751</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>10.5</v>
       </c>
       <c r="G427" t="n">
-        <v>8.9888277053833</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.9888277053833</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G449" t="n">
-        <v>8.73200225830078</v>
+        <v>8.7320032119751</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.86041450500488</v>
+        <v>8.8604154586792</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>10.5</v>
       </c>
       <c r="G451" t="n">
-        <v>8.9888277053833</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -28166,6 +28166,32 @@
         <v>21.2000007629395</v>
       </c>
       <c r="H1069" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1070" t="n">
+        <v>13049</v>
+      </c>
+      <c r="C1070" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="H1070" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -499,7 +499,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7745885848999</v>
+        <v>5.77458906173706</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G21" t="n">
-        <v>5.83956289291382</v>
+        <v>5.83956336975098</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G27" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G41" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64464044570923</v>
+        <v>5.64464092254639</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>5.89641618728638</v>
+        <v>5.89641571044922</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G90" t="n">
-        <v>5.89641618728638</v>
+        <v>5.89641571044922</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G104" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G116" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G128" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G145" t="n">
-        <v>5.73398017883301</v>
+        <v>5.73397970199585</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>6.27001714706421</v>
+        <v>6.27001762390137</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G178" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G181" t="n">
-        <v>6.48118352890015</v>
+        <v>6.4811840057373</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>6.52991485595703</v>
+        <v>6.52991533279419</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G186" t="n">
-        <v>6.513671875</v>
+        <v>6.51367139816284</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483777999878</v>
+        <v>6.72483825683594</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64362001419067</v>
+        <v>6.64362049102783</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G191" t="n">
-        <v>6.7898120880127</v>
+        <v>6.78981161117554</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G192" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G193" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180641174316</v>
+        <v>6.59180545806885</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G240" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G254" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.75</v>
       </c>
       <c r="G265" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G307" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G308" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.75</v>
       </c>
       <c r="G312" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G313" t="n">
-        <v>6.37778663635254</v>
+        <v>6.37778615951538</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>6.50619792938232</v>
+        <v>6.50619840621948</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.75</v>
       </c>
       <c r="G316" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>7.75</v>
       </c>
       <c r="G317" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.75</v>
       </c>
       <c r="G318" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>7.75</v>
       </c>
       <c r="G319" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G327" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.5</v>
       </c>
       <c r="G329" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>7.14825773239136</v>
+        <v>7.1482572555542</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.25</v>
       </c>
       <c r="G333" t="n">
-        <v>7.06264925003052</v>
+        <v>7.06264972686768</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G337" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>8.25</v>
       </c>
       <c r="G342" t="n">
-        <v>7.06264925003052</v>
+        <v>7.06264972686768</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G349" t="n">
-        <v>7.36227703094482</v>
+        <v>7.36227750778198</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G350" t="n">
-        <v>7.36227703094482</v>
+        <v>7.36227750778198</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.5</v>
       </c>
       <c r="G351" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.5</v>
       </c>
       <c r="G352" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>8.5</v>
       </c>
       <c r="G353" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>7.44788455963135</v>
+        <v>7.44788408279419</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>7.44788455963135</v>
+        <v>7.44788408279419</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>7.53349304199219</v>
+        <v>7.53349256515503</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>7.79031658172607</v>
+        <v>7.79031610488892</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83311986923218</v>
+        <v>7.83312034606934</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G382" t="n">
-        <v>8.00433731079102</v>
+        <v>8.0043363571167</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G386" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G392" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G407" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G409" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G410" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G411" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>8.90321826934814</v>
+        <v>8.90321731567383</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>8.90321826934814</v>
+        <v>8.90321731567383</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>8.7320032119751</v>
+        <v>8.73200225830078</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90321826934814</v>
+        <v>8.90321731567383</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>8.90321826934814</v>
+        <v>8.90321731567383</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G444" t="n">
-        <v>8.54366588592529</v>
+        <v>8.54366493225098</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G449" t="n">
-        <v>8.7320032119751</v>
+        <v>8.73200225830078</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.8604154586792</v>
+        <v>8.86041450500488</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>9.28845500946045</v>
+        <v>9.28845405578613</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>9.14202404022217</v>
+        <v>9.14202308654785</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G520" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G536" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G547" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G586" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G595" t="n">
-        <v>10.6807804107666</v>
+        <v>10.6807794570923</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G596" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>10.4544925689697</v>
+        <v>10.4544916152954</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>10.4544925689697</v>
+        <v>10.4544916152954</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>11.495415687561</v>
+        <v>11.4954147338867</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>11.133355140686</v>
+        <v>11.1333560943604</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G648" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G655" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>12.75</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>12.75</v>
       </c>
       <c r="G666" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>12.75</v>
       </c>
       <c r="G667" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G673" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>12.8078842163086</v>
+        <v>12.8078832626343</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>13.4867477416992</v>
+        <v>13.4867467880249</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>12.8531408309937</v>
+        <v>12.853141784668</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14</v>
       </c>
       <c r="G683" t="n">
-        <v>12.6721115112305</v>
+        <v>12.6721124649048</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>12.8531408309937</v>
+        <v>12.853141784668</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>15</v>
       </c>
       <c r="G688" t="n">
-        <v>13.5772619247437</v>
+        <v>13.577262878418</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>14.5729293823242</v>
+        <v>14.5729284286499</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>14.1203536987305</v>
+        <v>14.1203527450562</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>15.5</v>
       </c>
       <c r="G702" t="n">
-        <v>14.0298385620117</v>
+        <v>14.0298376083374</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>15.5</v>
       </c>
       <c r="G703" t="n">
-        <v>14.0298385620117</v>
+        <v>14.0298376083374</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -28192,6 +28192,32 @@
         <v>21.3999996185303</v>
       </c>
       <c r="H1070" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1071" t="n">
+        <v>8964</v>
+      </c>
+      <c r="C1071" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="H1071" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -551,7 +551,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>5.77458906173706</v>
+        <v>5.7745885848999</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G21" t="n">
-        <v>5.83956336975098</v>
+        <v>5.83956289291382</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G31" t="n">
-        <v>5.82331943511963</v>
+        <v>5.82331991195679</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G39" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G41" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>5.70149230957031</v>
+        <v>5.70149278640747</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64464092254639</v>
+        <v>5.64464044570923</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G104" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G116" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>5.78271055221558</v>
+        <v>5.78271102905273</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G128" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>5.78271055221558</v>
+        <v>5.78271102905273</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>5.71773624420166</v>
+        <v>5.7177357673645</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>5.78271055221558</v>
+        <v>5.78271102905273</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>7.5</v>
       </c>
       <c r="G162" t="n">
-        <v>6.09133863449097</v>
+        <v>6.09133911132812</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>6.46494102478027</v>
+        <v>6.46494054794312</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>6.3999662399292</v>
+        <v>6.39996671676636</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G166" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>6.3999662399292</v>
+        <v>6.39996671676636</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G170" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="n">
-        <v>6.49742794036865</v>
+        <v>6.49742746353149</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8</v>
       </c>
       <c r="G172" t="n">
-        <v>6.49742794036865</v>
+        <v>6.49742746353149</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="n">
-        <v>6.49742794036865</v>
+        <v>6.49742746353149</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>6.41620969772339</v>
+        <v>6.41621017456055</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>6.41620969772339</v>
+        <v>6.41621017456055</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G177" t="n">
-        <v>6.20504379272461</v>
+        <v>6.20504331588745</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G178" t="n">
-        <v>6.3999662399292</v>
+        <v>6.39996671676636</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>6.52991533279419</v>
+        <v>6.52991485595703</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G186" t="n">
-        <v>6.51367139816284</v>
+        <v>6.513671875</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>6.49742794036865</v>
+        <v>6.49742746353149</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483825683594</v>
+        <v>6.72483777999878</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64362049102783</v>
+        <v>6.64362001419067</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G191" t="n">
-        <v>6.78981161117554</v>
+        <v>6.78981113433838</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G194" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G195" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G196" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8</v>
       </c>
       <c r="G197" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8</v>
       </c>
       <c r="G199" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>8</v>
       </c>
       <c r="G209" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8</v>
       </c>
       <c r="G210" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G212" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G217" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8</v>
       </c>
       <c r="G232" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G236" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180545806885</v>
+        <v>6.59180593490601</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G244" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>8</v>
       </c>
       <c r="G257" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8</v>
       </c>
       <c r="G259" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8</v>
       </c>
       <c r="G270" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8</v>
       </c>
       <c r="G272" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G276" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G281" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8</v>
       </c>
       <c r="G287" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>8</v>
       </c>
       <c r="G288" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>8</v>
       </c>
       <c r="G294" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>8</v>
       </c>
       <c r="G295" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>8</v>
       </c>
       <c r="G296" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G298" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8</v>
       </c>
       <c r="G300" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8</v>
       </c>
       <c r="G325" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>7.10545349121094</v>
+        <v>7.1054539680481</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>7.10545349121094</v>
+        <v>7.1054539680481</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>7.10545349121094</v>
+        <v>7.1054539680481</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G348" t="n">
-        <v>7.10545349121094</v>
+        <v>7.1054539680481</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>7.79031610488892</v>
+        <v>7.79031658172607</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83312034606934</v>
+        <v>7.83311939239502</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G386" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G392" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G406" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G407" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G409" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G410" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G411" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>8.64639568328857</v>
+        <v>8.64639472961426</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G444" t="n">
-        <v>8.54366493225098</v>
+        <v>8.54366588592529</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -28218,6 +28218,32 @@
         <v>20.8999996185303</v>
       </c>
       <c r="H1071" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1072" t="n">
+        <v>7466</v>
+      </c>
+      <c r="C1072" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="H1072" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -707,7 +707,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G13" t="n">
-        <v>5.86392831802368</v>
+        <v>5.86392879486084</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G21" t="n">
-        <v>5.83956289291382</v>
+        <v>5.83956336975098</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>5.70149278640747</v>
+        <v>5.70149230957031</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64464044570923</v>
+        <v>5.64463996887207</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G74" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524885177612</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524885177612</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>5.88017177581787</v>
+        <v>5.88017225265503</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>5.86392831802368</v>
+        <v>5.86392879486084</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G93" t="n">
-        <v>5.88017177581787</v>
+        <v>5.88017225265503</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>5.88017177581787</v>
+        <v>5.88017225265503</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524885177612</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>5.7177357673645</v>
+        <v>5.71773672103882</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>7.5</v>
       </c>
       <c r="G162" t="n">
-        <v>6.09133911132812</v>
+        <v>6.09133863449097</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>6.46494054794312</v>
+        <v>6.46494102478027</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>6.27001762390137</v>
+        <v>6.27001714706421</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8</v>
       </c>
       <c r="G172" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G177" t="n">
-        <v>6.20504331588745</v>
+        <v>6.20504379272461</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G183" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G191" t="n">
-        <v>6.78981113433838</v>
+        <v>6.78981161117554</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G192" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G193" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8</v>
       </c>
       <c r="G197" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8</v>
       </c>
       <c r="G199" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>8</v>
       </c>
       <c r="G209" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8</v>
       </c>
       <c r="G210" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8</v>
       </c>
       <c r="G232" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180593490601</v>
+        <v>6.59180641174316</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>8</v>
       </c>
       <c r="G257" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8</v>
       </c>
       <c r="G259" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.75</v>
       </c>
       <c r="G265" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8</v>
       </c>
       <c r="G270" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8</v>
       </c>
       <c r="G272" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8</v>
       </c>
       <c r="G287" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>8</v>
       </c>
       <c r="G288" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>8</v>
       </c>
       <c r="G294" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>8</v>
       </c>
       <c r="G295" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>8</v>
       </c>
       <c r="G296" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8</v>
       </c>
       <c r="G300" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.75</v>
       </c>
       <c r="G312" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G313" t="n">
-        <v>6.37778615951538</v>
+        <v>6.37778663635254</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>6.50619840621948</v>
+        <v>6.50619792938232</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.75</v>
       </c>
       <c r="G316" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>7.75</v>
       </c>
       <c r="G317" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.75</v>
       </c>
       <c r="G318" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>7.75</v>
       </c>
       <c r="G319" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8</v>
       </c>
       <c r="G325" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G327" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>7.1054539680481</v>
+        <v>7.10545349121094</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.5</v>
       </c>
       <c r="G329" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>7.1054539680481</v>
+        <v>7.10545349121094</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G337" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>7.1054539680481</v>
+        <v>7.10545349121094</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G348" t="n">
-        <v>7.1054539680481</v>
+        <v>7.10545349121094</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.5</v>
       </c>
       <c r="G351" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.5</v>
       </c>
       <c r="G352" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>8.5</v>
       </c>
       <c r="G353" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>7.44788408279419</v>
+        <v>7.44788455963135</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>7.44788408279419</v>
+        <v>7.44788455963135</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>7.53349256515503</v>
+        <v>7.53349304199219</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83311939239502</v>
+        <v>7.83312082290649</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>10</v>
       </c>
       <c r="G405" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G406" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.75</v>
       </c>
       <c r="G417" t="n">
-        <v>8.34676742553711</v>
+        <v>8.34676837921143</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G422" t="n">
-        <v>8.81761074066162</v>
+        <v>8.81761169433594</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>8.64639472961426</v>
+        <v>8.64639568328857</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>10</v>
       </c>
       <c r="G426" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>10.5</v>
       </c>
       <c r="G427" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>10</v>
       </c>
       <c r="G438" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>10</v>
       </c>
       <c r="G439" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>10</v>
       </c>
       <c r="G440" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>10</v>
       </c>
       <c r="G445" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>10</v>
       </c>
       <c r="G446" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.86041450500488</v>
+        <v>8.8604154586792</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>10.5</v>
       </c>
       <c r="G451" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>9.28845405578613</v>
+        <v>9.28845500946045</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>9.14202308654785</v>
+        <v>9.14202404022217</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G520" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G536" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G547" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G586" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G595" t="n">
-        <v>10.6807794570923</v>
+        <v>10.6807804107666</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G596" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>10.4544916152954</v>
+        <v>10.4544925689697</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>10.4544916152954</v>
+        <v>10.4544925689697</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>11.4954147338867</v>
+        <v>11.495415687561</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>11.1333560943604</v>
+        <v>11.133355140686</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G648" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G655" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>12.75</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>12.75</v>
       </c>
       <c r="G666" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>12.75</v>
       </c>
       <c r="G667" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G673" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>12.8078832626343</v>
+        <v>12.8078842163086</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>13.4867467880249</v>
+        <v>13.4867477416992</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>12.853141784668</v>
+        <v>12.8531408309937</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14</v>
       </c>
       <c r="G683" t="n">
-        <v>12.6721124649048</v>
+        <v>12.6721115112305</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>12.853141784668</v>
+        <v>12.8531408309937</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>15</v>
       </c>
       <c r="G688" t="n">
-        <v>13.577262878418</v>
+        <v>13.5772619247437</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>14.5729284286499</v>
+        <v>14.5729293823242</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>14.1203527450562</v>
+        <v>14.1203536987305</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>15.5</v>
       </c>
       <c r="G702" t="n">
-        <v>14.0298376083374</v>
+        <v>14.0298385620117</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>15.5</v>
       </c>
       <c r="G703" t="n">
-        <v>14.0298376083374</v>
+        <v>14.0298385620117</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -28244,6 +28244,32 @@
         <v>20.7000007629395</v>
       </c>
       <c r="H1072" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1073" t="n">
+        <v>2647</v>
+      </c>
+      <c r="C1073" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>20.7999992370605</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="H1073" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G3" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G8" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G11" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G12" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7745885848999</v>
+        <v>5.77458906173706</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G20" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G31" t="n">
-        <v>5.82331991195679</v>
+        <v>5.82331943511963</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G36" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G42" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.79083204269409</v>
+        <v>5.79083251953125</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G50" t="n">
-        <v>5.79083204269409</v>
+        <v>5.79083251953125</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>5.79083204269409</v>
+        <v>5.79083251953125</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G53" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G54" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>5.70149230957031</v>
+        <v>5.70149278640747</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64464044570923</v>
+        <v>5.64463949203491</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G62" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G68" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G70" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G72" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G79" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G81" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G91" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G102" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G104" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G105" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G114" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G120" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G123" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G125" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G126" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G128" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>5.7177357673645</v>
+        <v>5.71773672103882</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>5.66900587081909</v>
+        <v>5.66900634765625</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>5.66900587081909</v>
+        <v>5.66900634765625</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G146" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G154" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G156" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G157" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>7.5</v>
       </c>
       <c r="G162" t="n">
-        <v>6.09133911132812</v>
+        <v>6.09133815765381</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>6.27001714706421</v>
+        <v>6.27001762390137</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8</v>
       </c>
       <c r="G172" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>6.41620969772339</v>
+        <v>6.41621017456055</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>6.41620969772339</v>
+        <v>6.41621017456055</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G177" t="n">
-        <v>6.20504379272461</v>
+        <v>6.20504331588745</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G183" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G186" t="n">
-        <v>6.513671875</v>
+        <v>6.51367139816284</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64362001419067</v>
+        <v>6.64362049102783</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G192" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G193" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8</v>
       </c>
       <c r="G197" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8</v>
       </c>
       <c r="G199" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>8</v>
       </c>
       <c r="G209" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8</v>
       </c>
       <c r="G210" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8</v>
       </c>
       <c r="G232" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180593490601</v>
+        <v>6.59180641174316</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>8</v>
       </c>
       <c r="G257" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8</v>
       </c>
       <c r="G259" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.75</v>
       </c>
       <c r="G265" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8</v>
       </c>
       <c r="G270" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8</v>
       </c>
       <c r="G272" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8</v>
       </c>
       <c r="G287" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>8</v>
       </c>
       <c r="G288" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>8</v>
       </c>
       <c r="G294" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>8</v>
       </c>
       <c r="G295" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>8</v>
       </c>
       <c r="G296" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8</v>
       </c>
       <c r="G300" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.75</v>
       </c>
       <c r="G312" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G313" t="n">
-        <v>6.37778615951538</v>
+        <v>6.37778663635254</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>6.50619840621948</v>
+        <v>6.50619792938232</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.75</v>
       </c>
       <c r="G316" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>7.75</v>
       </c>
       <c r="G317" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.75</v>
       </c>
       <c r="G318" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>7.75</v>
       </c>
       <c r="G319" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8</v>
       </c>
       <c r="G325" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G327" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>7.1054539680481</v>
+        <v>7.10545349121094</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.5</v>
       </c>
       <c r="G329" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>7.1054539680481</v>
+        <v>7.10545349121094</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G337" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>7.1054539680481</v>
+        <v>7.10545349121094</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G348" t="n">
-        <v>7.1054539680481</v>
+        <v>7.10545349121094</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.5</v>
       </c>
       <c r="G351" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.5</v>
       </c>
       <c r="G352" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>8.5</v>
       </c>
       <c r="G353" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>7.44788408279419</v>
+        <v>7.44788455963135</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>7.44788408279419</v>
+        <v>7.44788455963135</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>7.53349256515503</v>
+        <v>7.53349304199219</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83311939239502</v>
+        <v>7.83312082290649</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>10</v>
       </c>
       <c r="G405" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G406" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.75</v>
       </c>
       <c r="G417" t="n">
-        <v>8.34676742553711</v>
+        <v>8.34676837921143</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G422" t="n">
-        <v>8.81761074066162</v>
+        <v>8.81761169433594</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>8.64639472961426</v>
+        <v>8.64639568328857</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>10</v>
       </c>
       <c r="G426" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>10.5</v>
       </c>
       <c r="G427" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>10</v>
       </c>
       <c r="G438" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>10</v>
       </c>
       <c r="G439" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>10</v>
       </c>
       <c r="G440" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>10</v>
       </c>
       <c r="G445" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>10</v>
       </c>
       <c r="G446" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.86041450500488</v>
+        <v>8.8604154586792</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>10.5</v>
       </c>
       <c r="G451" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>9.28845405578613</v>
+        <v>9.28845500946045</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>9.14202308654785</v>
+        <v>9.14202404022217</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G520" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G536" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G547" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G586" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G595" t="n">
-        <v>10.6807794570923</v>
+        <v>10.6807804107666</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G596" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>10.4544916152954</v>
+        <v>10.4544925689697</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>10.4544916152954</v>
+        <v>10.4544925689697</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>11.4954147338867</v>
+        <v>11.495415687561</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>11.1333560943604</v>
+        <v>11.133355140686</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G648" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G655" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>12.75</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>12.75</v>
       </c>
       <c r="G666" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>12.75</v>
       </c>
       <c r="G667" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G673" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>12.8078832626343</v>
+        <v>12.8078842163086</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>13.4867467880249</v>
+        <v>13.4867477416992</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>12.853141784668</v>
+        <v>12.8531408309937</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14</v>
       </c>
       <c r="G683" t="n">
-        <v>12.6721124649048</v>
+        <v>12.6721115112305</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>12.853141784668</v>
+        <v>12.8531408309937</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>15</v>
       </c>
       <c r="G688" t="n">
-        <v>13.577262878418</v>
+        <v>13.5772619247437</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>14.5729284286499</v>
+        <v>14.5729293823242</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>14.1203527450562</v>
+        <v>14.1203536987305</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>15.5</v>
       </c>
       <c r="G702" t="n">
-        <v>14.0298376083374</v>
+        <v>14.0298385620117</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>15.5</v>
       </c>
       <c r="G703" t="n">
-        <v>14.0298376083374</v>
+        <v>14.0298385620117</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -28322,6 +28322,32 @@
         <v>20.3999996185303</v>
       </c>
       <c r="H1075" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1076" t="n">
+        <v>10541</v>
+      </c>
+      <c r="C1076" t="n">
+        <v>20.7999992370605</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>20.1000003814697</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>20.1000003814697</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>20.1000003814697</v>
+      </c>
+      <c r="H1076" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -25177,13 +25177,36 @@
         <v>19.2999992370605</v>
       </c>
       <c r="D1079" t="n">
-        <v>18.3500003814697</v>
+        <v>18.2000007629395</v>
       </c>
       <c r="E1079" t="n">
         <v>19.1000003814697</v>
       </c>
-      <c r="F1079"/>
+      <c r="F1079" t="n">
+        <v>18.2000007629395</v>
+      </c>
       <c r="G1079" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1080" t="n">
+        <v>26172</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>18.6499996185303</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>18.2000007629395</v>
+      </c>
+      <c r="F1080"/>
+      <c r="G1080" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -25205,8 +25205,31 @@
       <c r="E1080" t="n">
         <v>18.2000007629395</v>
       </c>
-      <c r="F1080"/>
+      <c r="F1080" t="n">
+        <v>17.9500007629395</v>
+      </c>
       <c r="G1080" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1081" t="n">
+        <v>17900</v>
+      </c>
+      <c r="C1081" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="F1081"/>
+      <c r="G1081" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -25228,8 +25228,31 @@
       <c r="E1081" t="n">
         <v>17.9500007629395</v>
       </c>
-      <c r="F1081"/>
+      <c r="F1081" t="n">
+        <v>18.1499996185303</v>
+      </c>
       <c r="G1081" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1082" t="n">
+        <v>17880</v>
+      </c>
+      <c r="C1082" t="n">
+        <v>18.0499992370605</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>17.6499996185303</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>17.8500003814697</v>
+      </c>
+      <c r="F1082"/>
+      <c r="G1082" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -25251,8 +25251,31 @@
       <c r="E1082" t="n">
         <v>17.8500003814697</v>
       </c>
-      <c r="F1082"/>
+      <c r="F1082" t="n">
+        <v>17.75</v>
+      </c>
       <c r="G1082" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1083" t="n">
+        <v>15567</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="F1083"/>
+      <c r="G1083" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -25281,6 +25281,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1084">
+      <c r="A1084" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1084" t="n">
+        <v>20780</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="G1084" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -707,7 +707,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G13" t="n">
-        <v>5.86392784118652</v>
+        <v>5.86392879486084</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>5.77458906173706</v>
+        <v>5.7745885848999</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G20" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G21" t="n">
-        <v>5.83956336975098</v>
+        <v>5.83956289291382</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G31" t="n">
-        <v>5.82331943511963</v>
+        <v>5.82331991195679</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G41" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.79083251953125</v>
+        <v>5.79083204269409</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G50" t="n">
-        <v>5.79083251953125</v>
+        <v>5.79083204269409</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>5.79083251953125</v>
+        <v>5.79083204269409</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G54" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>5.70149230957031</v>
+        <v>5.70149278640747</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64464044570923</v>
+        <v>5.64463996887207</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G74" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>5.89641571044922</v>
+        <v>5.89641618728638</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>5.88017177581787</v>
+        <v>5.88017225265503</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G90" t="n">
-        <v>5.89641571044922</v>
+        <v>5.89641618728638</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>5.86392784118652</v>
+        <v>5.86392879486084</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G93" t="n">
-        <v>5.88017177581787</v>
+        <v>5.88017225265503</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>5.88017177581787</v>
+        <v>5.88017225265503</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G116" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G120" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G123" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G125" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G146" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G156" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G157" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>7.5</v>
       </c>
       <c r="G162" t="n">
-        <v>6.09133863449097</v>
+        <v>6.09133815765381</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>6.27001714706421</v>
+        <v>6.27001762390137</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G166" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G170" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G177" t="n">
-        <v>6.20504379272461</v>
+        <v>6.20504331588745</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G183" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483777999878</v>
+        <v>6.72483730316162</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64362001419067</v>
+        <v>6.64362049102783</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G191" t="n">
-        <v>6.7898120880127</v>
+        <v>6.78981161117554</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G192" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G193" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G194" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G195" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G196" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G212" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G217" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G236" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180545806885</v>
+        <v>6.59180641174316</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G244" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.75</v>
       </c>
       <c r="G265" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G276" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G281" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G298" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.75</v>
       </c>
       <c r="G312" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G313" t="n">
-        <v>6.37778615951538</v>
+        <v>6.37778663635254</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>6.50619840621948</v>
+        <v>6.50619792938232</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.75</v>
       </c>
       <c r="G316" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>7.75</v>
       </c>
       <c r="G317" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.75</v>
       </c>
       <c r="G318" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>7.75</v>
       </c>
       <c r="G319" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G327" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.5</v>
       </c>
       <c r="G329" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G337" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.5</v>
       </c>
       <c r="G351" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.5</v>
       </c>
       <c r="G352" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>8.5</v>
       </c>
       <c r="G353" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>7.44788408279419</v>
+        <v>7.44788455963135</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>7.44788408279419</v>
+        <v>7.44788455963135</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>7.53349256515503</v>
+        <v>7.53349304199219</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>7.79031610488892</v>
+        <v>7.79031658172607</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83312034606934</v>
+        <v>7.83312082290649</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G386" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G392" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>10</v>
       </c>
       <c r="G405" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G407" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G409" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G410" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G411" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.75</v>
       </c>
       <c r="G417" t="n">
-        <v>8.34676742553711</v>
+        <v>8.34676837921143</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G422" t="n">
-        <v>8.81761074066162</v>
+        <v>8.81761169433594</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>10</v>
       </c>
       <c r="G426" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>10.5</v>
       </c>
       <c r="G427" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>10</v>
       </c>
       <c r="G438" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>10</v>
       </c>
       <c r="G439" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>10</v>
       </c>
       <c r="G440" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G444" t="n">
-        <v>8.54366493225098</v>
+        <v>8.54366588592529</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>10</v>
       </c>
       <c r="G445" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>10</v>
       </c>
       <c r="G446" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.86041450500488</v>
+        <v>8.8604154586792</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>10.5</v>
       </c>
       <c r="G451" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>9.28845405578613</v>
+        <v>9.28845500946045</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>9.14202308654785</v>
+        <v>9.14202404022217</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G520" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G536" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G547" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G586" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G595" t="n">
-        <v>10.6807794570923</v>
+        <v>10.6807804107666</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G596" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>10.4544916152954</v>
+        <v>10.4544925689697</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>10.4544916152954</v>
+        <v>10.4544925689697</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>11.4954147338867</v>
+        <v>11.495415687561</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>11.1333560943604</v>
+        <v>11.133355140686</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G648" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G655" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>12.75</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>12.75</v>
       </c>
       <c r="G666" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>12.75</v>
       </c>
       <c r="G667" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G673" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>12.8078832626343</v>
+        <v>12.8078842163086</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>13.4867467880249</v>
+        <v>13.4867477416992</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>12.853141784668</v>
+        <v>12.8531408309937</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14</v>
       </c>
       <c r="G683" t="n">
-        <v>12.6721124649048</v>
+        <v>12.6721115112305</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>12.853141784668</v>
+        <v>12.8531408309937</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>15</v>
       </c>
       <c r="G688" t="n">
-        <v>13.577262878418</v>
+        <v>13.5772619247437</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>14.5729284286499</v>
+        <v>14.5729293823242</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>14.1203527450562</v>
+        <v>14.1203536987305</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>15.5</v>
       </c>
       <c r="G702" t="n">
-        <v>14.0298376083374</v>
+        <v>14.0298385620117</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>15.5</v>
       </c>
       <c r="G703" t="n">
-        <v>14.0298376083374</v>
+        <v>14.0298385620117</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -28608,6 +28608,32 @@
         <v>17.6000003814697</v>
       </c>
       <c r="H1086" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1087" t="n">
+        <v>17131</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>18.0499992370605</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="H1087" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G3" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G8" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G11" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G12" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G13" t="n">
-        <v>5.86392879486084</v>
+        <v>5.86392831802368</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>5.85580730438232</v>
+        <v>5.85580682754517</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G27" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>5.85580730438232</v>
+        <v>5.85580682754517</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G36" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G42" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>5.85580730438232</v>
+        <v>5.85580682754517</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G53" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>5.70149278640747</v>
+        <v>5.70149230957031</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64463996887207</v>
+        <v>5.64464044570923</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G62" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>5.85580730438232</v>
+        <v>5.85580682754517</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>5.85580730438232</v>
+        <v>5.85580682754517</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G68" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G70" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G72" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G74" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G79" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G81" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G91" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>5.86392879486084</v>
+        <v>5.86392831802368</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G102" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G104" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G105" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G114" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G126" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G128" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>5.71773624420166</v>
+        <v>5.7177357673645</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G154" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>7.5</v>
       </c>
       <c r="G162" t="n">
-        <v>6.09133815765381</v>
+        <v>6.09133911132812</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>6.27001762390137</v>
+        <v>6.27001714706421</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="n">
-        <v>6.49742794036865</v>
+        <v>6.49742746353149</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8</v>
       </c>
       <c r="G172" t="n">
-        <v>6.49742794036865</v>
+        <v>6.49742746353149</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="n">
-        <v>6.49742794036865</v>
+        <v>6.49742746353149</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>6.41621017456055</v>
+        <v>6.41620969772339</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>6.41621017456055</v>
+        <v>6.41620969772339</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G177" t="n">
-        <v>6.20504331588745</v>
+        <v>6.20504379272461</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G178" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>6.57864570617676</v>
+        <v>6.57864618301392</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G183" t="n">
-        <v>6.57864570617676</v>
+        <v>6.57864618301392</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>6.49742794036865</v>
+        <v>6.49742746353149</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.57864570617676</v>
+        <v>6.57864618301392</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483730316162</v>
+        <v>6.72483777999878</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64362049102783</v>
+        <v>6.64362001419067</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G192" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G193" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8</v>
       </c>
       <c r="G197" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8</v>
       </c>
       <c r="G199" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>8</v>
       </c>
       <c r="G209" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8</v>
       </c>
       <c r="G210" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8</v>
       </c>
       <c r="G232" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180641174316</v>
+        <v>6.59180593490601</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>8</v>
       </c>
       <c r="G257" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>8</v>
       </c>
       <c r="G259" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.75</v>
       </c>
       <c r="G265" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8</v>
       </c>
       <c r="G270" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8</v>
       </c>
       <c r="G272" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8</v>
       </c>
       <c r="G287" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>8</v>
       </c>
       <c r="G288" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>8</v>
       </c>
       <c r="G294" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>8</v>
       </c>
       <c r="G295" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>8</v>
       </c>
       <c r="G296" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8</v>
       </c>
       <c r="G300" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.75</v>
       </c>
       <c r="G312" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G313" t="n">
-        <v>6.37778663635254</v>
+        <v>6.37778615951538</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>6.50619792938232</v>
+        <v>6.50619840621948</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.75</v>
       </c>
       <c r="G316" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>7.75</v>
       </c>
       <c r="G317" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.75</v>
       </c>
       <c r="G318" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>7.75</v>
       </c>
       <c r="G319" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8</v>
       </c>
       <c r="G325" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G327" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>7.10545349121094</v>
+        <v>7.1054539680481</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.5</v>
       </c>
       <c r="G329" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>7.10545349121094</v>
+        <v>7.1054539680481</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G337" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>7.10545349121094</v>
+        <v>7.1054539680481</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G348" t="n">
-        <v>7.10545349121094</v>
+        <v>7.1054539680481</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.5</v>
       </c>
       <c r="G351" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.5</v>
       </c>
       <c r="G352" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>8.5</v>
       </c>
       <c r="G353" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>7.44788455963135</v>
+        <v>7.44788408279419</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>7.44788455963135</v>
+        <v>7.44788408279419</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>7.53349304199219</v>
+        <v>7.53349256515503</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83312082290649</v>
+        <v>7.83311939239502</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.38957118988037</v>
+        <v>8.38957214355469</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.38957118988037</v>
+        <v>8.38957214355469</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>10</v>
       </c>
       <c r="G405" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G406" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.75</v>
       </c>
       <c r="G417" t="n">
-        <v>8.34676837921143</v>
+        <v>8.34676742553711</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G422" t="n">
-        <v>8.81761169433594</v>
+        <v>8.81761074066162</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>8.64639568328857</v>
+        <v>8.64639472961426</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>10</v>
       </c>
       <c r="G426" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>10.5</v>
       </c>
       <c r="G427" t="n">
-        <v>8.98882579803467</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.98882579803467</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>10</v>
       </c>
       <c r="G438" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>10</v>
       </c>
       <c r="G439" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>10</v>
       </c>
       <c r="G440" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>10</v>
       </c>
       <c r="G445" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>10</v>
       </c>
       <c r="G446" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.8604154586792</v>
+        <v>8.86041450500488</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>10.5</v>
       </c>
       <c r="G451" t="n">
-        <v>8.98882579803467</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>9.28845500946045</v>
+        <v>9.28845405578613</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>9.14202404022217</v>
+        <v>9.14202308654785</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G520" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G536" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G547" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G586" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G595" t="n">
-        <v>10.6807804107666</v>
+        <v>10.6807794570923</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G596" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>10.4544925689697</v>
+        <v>10.4544916152954</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>10.4544925689697</v>
+        <v>10.4544916152954</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>11.495415687561</v>
+        <v>11.4954147338867</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>11.133355140686</v>
+        <v>11.1333560943604</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G648" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G655" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>12.75</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>12.75</v>
       </c>
       <c r="G666" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>12.75</v>
       </c>
       <c r="G667" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G673" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>12.8078842163086</v>
+        <v>12.8078832626343</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>13.4867477416992</v>
+        <v>13.4867467880249</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>12.8531408309937</v>
+        <v>12.853141784668</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14</v>
       </c>
       <c r="G683" t="n">
-        <v>12.6721115112305</v>
+        <v>12.6721124649048</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>12.8531408309937</v>
+        <v>12.853141784668</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>15</v>
       </c>
       <c r="G688" t="n">
-        <v>13.5772619247437</v>
+        <v>13.577262878418</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>14.5729293823242</v>
+        <v>14.5729284286499</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>14.1203536987305</v>
+        <v>14.1203527450562</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>15.5</v>
       </c>
       <c r="G702" t="n">
-        <v>14.0298385620117</v>
+        <v>14.0298376083374</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>15.5</v>
       </c>
       <c r="G703" t="n">
-        <v>14.0298385620117</v>
+        <v>14.0298376083374</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -28634,6 +28634,32 @@
         <v>17.9500007629395</v>
       </c>
       <c r="H1087" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1088" t="n">
+        <v>8159</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="H1088" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H2" t="n">
         <v>1480</v>
@@ -456,7 +456,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G3" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H3" t="n">
         <v>2424</v>
@@ -485,7 +485,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H4" t="n">
         <v>1025</v>
@@ -543,7 +543,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H6" t="n">
         <v>1022</v>
@@ -601,7 +601,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G8" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H8" t="n">
         <v>6867</v>
@@ -630,7 +630,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H9" t="n">
         <v>1638</v>
@@ -659,7 +659,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H10" t="n">
         <v>2500</v>
@@ -688,7 +688,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G11" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H11" t="n">
         <v>827</v>
@@ -717,7 +717,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G12" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H12" t="n">
         <v>6225</v>
@@ -775,7 +775,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H14" t="n">
         <v>22</v>
@@ -804,7 +804,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H15" t="n">
         <v>216</v>
@@ -862,7 +862,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H17" t="n">
         <v>1221</v>
@@ -891,7 +891,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H18" t="n">
         <v>22</v>
@@ -920,7 +920,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H19" t="n">
         <v>137</v>
@@ -1007,7 +1007,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H22" t="n">
         <v>66</v>
@@ -1065,7 +1065,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H24" t="n">
         <v>6743</v>
@@ -1094,7 +1094,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H25" t="n">
         <v>308</v>
@@ -1123,7 +1123,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H26" t="n">
         <v>1045</v>
@@ -1239,7 +1239,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H32" t="n">
         <v>379</v>
@@ -1326,7 +1326,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>5.72585868835449</v>
+        <v>5.72585821151733</v>
       </c>
       <c r="H33" t="n">
         <v>420</v>
@@ -1355,7 +1355,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H34" t="n">
         <v>3359</v>
@@ -1413,7 +1413,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G36" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H36" t="n">
         <v>80</v>
@@ -1529,7 +1529,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H40" t="n">
         <v>310</v>
@@ -1558,7 +1558,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G41" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H41" t="n">
         <v>271</v>
@@ -1587,7 +1587,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G42" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H42" t="n">
         <v>4000</v>
@@ -1616,7 +1616,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H43" t="n">
         <v>1983</v>
@@ -1645,7 +1645,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H46" t="n">
         <v>1100</v>
@@ -1732,7 +1732,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H47" t="n">
         <v>2065</v>
@@ -1761,7 +1761,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H48" t="n">
         <v>500</v>
@@ -1790,7 +1790,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.79083251953125</v>
+        <v>5.79083204269409</v>
       </c>
       <c r="H49" t="n">
         <v>628</v>
@@ -1819,7 +1819,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G50" t="n">
-        <v>5.79083251953125</v>
+        <v>5.79083204269409</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>5.79083251953125</v>
+        <v>5.79083204269409</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H52" t="n">
         <v>11</v>
@@ -1906,7 +1906,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G53" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H53" t="n">
         <v>500</v>
@@ -1964,7 +1964,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H55" t="n">
         <v>3500</v>
@@ -1993,7 +1993,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H56" t="n">
         <v>1500</v>
@@ -2051,7 +2051,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64464044570923</v>
+        <v>5.64463996887207</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -2080,7 +2080,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>5.72585868835449</v>
+        <v>5.72585821151733</v>
       </c>
       <c r="H59" t="n">
         <v>150</v>
@@ -2109,7 +2109,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>5.72585868835449</v>
+        <v>5.72585821151733</v>
       </c>
       <c r="H60" t="n">
         <v>278</v>
@@ -2138,7 +2138,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>5.72585868835449</v>
+        <v>5.72585821151733</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G62" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H62" t="n">
         <v>1100</v>
@@ -2196,7 +2196,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H63" t="n">
         <v>2557</v>
@@ -2225,7 +2225,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H65" t="n">
         <v>1000</v>
@@ -2283,7 +2283,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H67" t="n">
         <v>897</v>
@@ -2341,7 +2341,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G68" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H68" t="n">
         <v>11</v>
@@ -2370,7 +2370,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G70" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G72" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H72" t="n">
         <v>450</v>
@@ -2486,7 +2486,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H73" t="n">
         <v>1650</v>
@@ -2515,7 +2515,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G74" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H75" t="n">
         <v>170</v>
@@ -2573,7 +2573,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G79" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H79" t="n">
         <v>125</v>
@@ -2689,7 +2689,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H80" t="n">
         <v>500</v>
@@ -2718,7 +2718,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G81" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H81" t="n">
         <v>10765</v>
@@ -2776,7 +2776,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H83" t="n">
         <v>3017</v>
@@ -2805,7 +2805,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G91" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H91" t="n">
         <v>16459</v>
@@ -3124,7 +3124,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H95" t="n">
         <v>2618</v>
@@ -3153,7 +3153,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H97" t="n">
         <v>351</v>
@@ -3211,7 +3211,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H98" t="n">
         <v>481</v>
@@ -3240,7 +3240,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H99" t="n">
         <v>8</v>
@@ -3269,7 +3269,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H100" t="n">
         <v>186</v>
@@ -3298,7 +3298,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H101" t="n">
         <v>350</v>
@@ -3327,7 +3327,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G102" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H102" t="n">
         <v>1756</v>
@@ -3356,7 +3356,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H103" t="n">
         <v>8600</v>
@@ -3385,7 +3385,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G104" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H104" t="n">
         <v>19209</v>
@@ -3414,7 +3414,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G105" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H105" t="n">
         <v>1750</v>
@@ -3443,7 +3443,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H106" t="n">
         <v>145</v>
@@ -3472,7 +3472,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H107" t="n">
         <v>667</v>
@@ -3501,7 +3501,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H109" t="n">
         <v>250</v>
@@ -3559,7 +3559,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H110" t="n">
         <v>3650</v>
@@ -3588,7 +3588,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H111" t="n">
         <v>35917</v>
@@ -3617,7 +3617,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H112" t="n">
         <v>15359</v>
@@ -3646,7 +3646,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G114" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H114" t="n">
         <v>1000</v>
@@ -3704,7 +3704,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H115" t="n">
         <v>65929</v>
@@ -3733,7 +3733,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G116" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H116" t="n">
         <v>1167</v>
@@ -3762,7 +3762,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H117" t="n">
         <v>134765</v>
@@ -3791,7 +3791,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H121" t="n">
         <v>8</v>
@@ -3907,7 +3907,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H122" t="n">
         <v>5</v>
@@ -4023,7 +4023,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G126" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H126" t="n">
         <v>3450</v>
@@ -4052,7 +4052,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H127" t="n">
         <v>6918</v>
@@ -4081,7 +4081,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G128" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H128" t="n">
         <v>214</v>
@@ -4110,7 +4110,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H129" t="n">
         <v>3454</v>
@@ -4139,7 +4139,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H130" t="n">
         <v>4648</v>
@@ -4168,7 +4168,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H131" t="n">
         <v>2050</v>
@@ -4197,7 +4197,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H132" t="n">
         <v>1700</v>
@@ -4226,7 +4226,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H133" t="n">
         <v>14468</v>
@@ -4284,7 +4284,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>5.66900539398193</v>
+        <v>5.66900587081909</v>
       </c>
       <c r="H135" t="n">
         <v>15568</v>
@@ -4313,7 +4313,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>5.66900539398193</v>
+        <v>5.66900587081909</v>
       </c>
       <c r="H136" t="n">
         <v>14819</v>
@@ -4342,7 +4342,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H137" t="n">
         <v>1286</v>
@@ -4371,7 +4371,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H138" t="n">
         <v>7627</v>
@@ -4400,7 +4400,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H139" t="n">
         <v>31688</v>
@@ -4429,7 +4429,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H140" t="n">
         <v>2500</v>
@@ -4458,7 +4458,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H144" t="n">
         <v>80</v>
@@ -4748,7 +4748,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H151" t="n">
         <v>1390</v>
@@ -4777,7 +4777,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H152" t="n">
         <v>10236</v>
@@ -4806,7 +4806,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H153" t="n">
         <v>14392</v>
@@ -4835,7 +4835,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G154" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H154" t="n">
         <v>1564</v>
@@ -4864,7 +4864,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H155" t="n">
         <v>23103</v>
@@ -4951,7 +4951,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H158" t="n">
         <v>10088</v>
@@ -4980,7 +4980,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H159" t="n">
         <v>2979</v>
@@ -5038,7 +5038,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H161" t="n">
         <v>2050</v>
@@ -5067,7 +5067,7 @@
         <v>7.5</v>
       </c>
       <c r="G162" t="n">
-        <v>6.09133863449097</v>
+        <v>6.09133815765381</v>
       </c>
       <c r="H162" t="n">
         <v>81003</v>
@@ -5125,7 +5125,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>6.27001714706421</v>
+        <v>6.27001762390137</v>
       </c>
       <c r="H164" t="n">
         <v>62015</v>
@@ -5183,7 +5183,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G166" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H166" t="n">
         <v>5498</v>
@@ -5299,7 +5299,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G170" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H170" t="n">
         <v>3020</v>
@@ -5328,7 +5328,7 @@
         <v>8</v>
       </c>
       <c r="G171" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H171" t="n">
         <v>1700</v>
@@ -5357,7 +5357,7 @@
         <v>8</v>
       </c>
       <c r="G172" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H172" t="n">
         <v>2792</v>
@@ -5386,7 +5386,7 @@
         <v>8</v>
       </c>
       <c r="G173" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H173" t="n">
         <v>1700</v>
@@ -5415,7 +5415,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>6.41620969772339</v>
+        <v>6.41621017456055</v>
       </c>
       <c r="H174" t="n">
         <v>550</v>
@@ -5444,7 +5444,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>6.41620969772339</v>
+        <v>6.41621017456055</v>
       </c>
       <c r="H175" t="n">
         <v>7100</v>
@@ -5473,7 +5473,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H176" t="n">
         <v>3660</v>
@@ -5502,7 +5502,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G177" t="n">
-        <v>6.20504379272461</v>
+        <v>6.20504331588745</v>
       </c>
       <c r="H177" t="n">
         <v>2825</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H179" t="n">
         <v>2200</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H182" t="n">
         <v>3383</v>
@@ -5676,7 +5676,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G183" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H183" t="n">
         <v>559</v>
@@ -5734,7 +5734,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>6.52991437911987</v>
+        <v>6.52991485595703</v>
       </c>
       <c r="H185" t="n">
         <v>625</v>
@@ -5763,7 +5763,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G186" t="n">
-        <v>6.51367139816284</v>
+        <v>6.513671875</v>
       </c>
       <c r="H186" t="n">
         <v>1000</v>
@@ -5792,7 +5792,7 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>6.49742746353149</v>
+        <v>6.49742794036865</v>
       </c>
       <c r="H187" t="n">
         <v>10818</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H188" t="n">
         <v>5815</v>
@@ -5850,7 +5850,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483777999878</v>
+        <v>6.72483730316162</v>
       </c>
       <c r="H189" t="n">
         <v>12503</v>
@@ -5879,7 +5879,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64362001419067</v>
+        <v>6.64362049102783</v>
       </c>
       <c r="H190" t="n">
         <v>15454</v>
@@ -5908,7 +5908,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G191" t="n">
-        <v>6.7898120880127</v>
+        <v>6.78981161117554</v>
       </c>
       <c r="H191" t="n">
         <v>35519</v>
@@ -6082,7 +6082,7 @@
         <v>8</v>
       </c>
       <c r="G197" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H197" t="n">
         <v>1992</v>
@@ -6140,7 +6140,7 @@
         <v>8</v>
       </c>
       <c r="G199" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H199" t="n">
         <v>22095</v>
@@ -6169,7 +6169,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G200" t="n">
-        <v>6.97704172134399</v>
+        <v>6.97704124450684</v>
       </c>
       <c r="H200" t="n">
         <v>10206</v>
@@ -6198,7 +6198,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G201" t="n">
-        <v>6.97704172134399</v>
+        <v>6.97704124450684</v>
       </c>
       <c r="H201" t="n">
         <v>5622</v>
@@ -6227,7 +6227,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H202" t="n">
         <v>1380</v>
@@ -6343,7 +6343,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H206" t="n">
         <v>250</v>
@@ -6372,7 +6372,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H207" t="n">
         <v>924</v>
@@ -6430,7 +6430,7 @@
         <v>8</v>
       </c>
       <c r="G209" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H209" t="n">
         <v>6000</v>
@@ -6459,7 +6459,7 @@
         <v>8</v>
       </c>
       <c r="G210" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H210" t="n">
         <v>1453</v>
@@ -6488,7 +6488,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H211" t="n">
         <v>1850</v>
@@ -6546,7 +6546,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H213" t="n">
         <v>2900</v>
@@ -6575,7 +6575,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H214" t="n">
         <v>4315</v>
@@ -6604,7 +6604,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H215" t="n">
         <v>4753</v>
@@ -6633,7 +6633,7 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H230" t="n">
         <v>1340</v>
@@ -7097,7 +7097,7 @@
         <v>8</v>
       </c>
       <c r="G232" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H232" t="n">
         <v>5</v>
@@ -7126,7 +7126,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H234" t="n">
         <v>800</v>
@@ -7184,7 +7184,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180593490601</v>
+        <v>6.59180641174316</v>
       </c>
       <c r="H237" t="n">
         <v>5618</v>
@@ -7300,7 +7300,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H239" t="n">
         <v>10600</v>
@@ -7358,7 +7358,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H241" t="n">
         <v>500</v>
@@ -7387,7 +7387,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H242" t="n">
         <v>200</v>
@@ -7416,7 +7416,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H243" t="n">
         <v>32675</v>
@@ -7445,7 +7445,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G244" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H247" t="n">
         <v>5100</v>
@@ -7561,7 +7561,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H248" t="n">
         <v>5000</v>
@@ -7648,7 +7648,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H251" t="n">
         <v>4818</v>
@@ -7706,7 +7706,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H253" t="n">
         <v>3985</v>
@@ -7764,7 +7764,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H255" t="n">
         <v>851</v>
@@ -7793,7 +7793,7 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>8</v>
       </c>
       <c r="G257" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H257" t="n">
         <v>1200</v>
@@ -7851,7 +7851,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H258" t="n">
         <v>7352</v>
@@ -7880,7 +7880,7 @@
         <v>8</v>
       </c>
       <c r="G259" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H260" t="n">
         <v>5</v>
@@ -7938,7 +7938,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G261" t="n">
-        <v>6.97704172134399</v>
+        <v>6.97704124450684</v>
       </c>
       <c r="H261" t="n">
         <v>800</v>
@@ -8025,7 +8025,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H264" t="n">
         <v>5125</v>
@@ -8112,7 +8112,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H267" t="n">
         <v>1357</v>
@@ -8141,7 +8141,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>8</v>
       </c>
       <c r="G270" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H270" t="n">
         <v>169</v>
@@ -8257,7 +8257,7 @@
         <v>8</v>
       </c>
       <c r="G272" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H272" t="n">
         <v>2337</v>
@@ -8286,7 +8286,7 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H278" t="n">
         <v>2218</v>
@@ -8489,7 +8489,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H280" t="n">
         <v>1214</v>
@@ -8547,7 +8547,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H282" t="n">
         <v>715</v>
@@ -8576,7 +8576,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>8</v>
       </c>
       <c r="G287" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H287" t="n">
         <v>125</v>
@@ -8721,7 +8721,7 @@
         <v>8</v>
       </c>
       <c r="G288" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>8</v>
       </c>
       <c r="G294" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H294" t="n">
         <v>5</v>
@@ -8924,7 +8924,7 @@
         <v>8</v>
       </c>
       <c r="G295" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H295" t="n">
         <v>3</v>
@@ -8953,7 +8953,7 @@
         <v>8</v>
       </c>
       <c r="G296" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H296" t="n">
         <v>12625</v>
@@ -8982,7 +8982,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H297" t="n">
         <v>6500</v>
@@ -9069,7 +9069,7 @@
         <v>8</v>
       </c>
       <c r="G300" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H300" t="n">
         <v>4713</v>
@@ -9504,7 +9504,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H315" t="n">
         <v>4634</v>
@@ -9794,7 +9794,7 @@
         <v>8</v>
       </c>
       <c r="G325" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H325" t="n">
         <v>45107</v>
@@ -10026,7 +10026,7 @@
         <v>8.25</v>
       </c>
       <c r="G333" t="n">
-        <v>7.06264925003052</v>
+        <v>7.06264972686768</v>
       </c>
       <c r="H333" t="n">
         <v>2000</v>
@@ -10287,7 +10287,7 @@
         <v>8.25</v>
       </c>
       <c r="G342" t="n">
-        <v>7.06264925003052</v>
+        <v>7.06264972686768</v>
       </c>
       <c r="H342" t="n">
         <v>250</v>
@@ -10490,7 +10490,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G349" t="n">
-        <v>7.36227703094482</v>
+        <v>7.36227750778198</v>
       </c>
       <c r="H349" t="n">
         <v>18029</v>
@@ -10519,7 +10519,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G350" t="n">
-        <v>7.36227703094482</v>
+        <v>7.36227750778198</v>
       </c>
       <c r="H350" t="n">
         <v>4020</v>
@@ -10780,7 +10780,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83312034606934</v>
+        <v>7.83312082290649</v>
       </c>
       <c r="H359" t="n">
         <v>11764</v>
@@ -10867,7 +10867,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H362" t="n">
         <v>13708</v>
@@ -10896,7 +10896,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H363" t="n">
         <v>19547</v>
@@ -10954,7 +10954,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H365" t="n">
         <v>6680</v>
@@ -10983,7 +10983,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H366" t="n">
         <v>4623</v>
@@ -11099,7 +11099,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H370" t="n">
         <v>4568</v>
@@ -11128,7 +11128,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H371" t="n">
         <v>1661</v>
@@ -11157,7 +11157,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H372" t="n">
         <v>1094</v>
@@ -11186,7 +11186,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H373" t="n">
         <v>1893</v>
@@ -11215,7 +11215,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H374" t="n">
         <v>3549</v>
@@ -11273,7 +11273,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H376" t="n">
         <v>19650</v>
@@ -11302,7 +11302,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H377" t="n">
         <v>1925</v>
@@ -11331,7 +11331,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H378" t="n">
         <v>4890</v>
@@ -11360,7 +11360,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H379" t="n">
         <v>1750</v>
@@ -11389,7 +11389,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H380" t="n">
         <v>2479</v>
@@ -11418,7 +11418,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H381" t="n">
         <v>955</v>
@@ -11447,7 +11447,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G382" t="n">
-        <v>8.00433731079102</v>
+        <v>8.0043363571167</v>
       </c>
       <c r="H382" t="n">
         <v>62</v>
@@ -11476,7 +11476,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H383" t="n">
         <v>500</v>
@@ -11505,7 +11505,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H384" t="n">
         <v>1430</v>
@@ -11621,7 +11621,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H388" t="n">
         <v>2450</v>
@@ -11650,7 +11650,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H389" t="n">
         <v>2705</v>
@@ -11679,7 +11679,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H390" t="n">
         <v>830</v>
@@ -11708,7 +11708,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H391" t="n">
         <v>4396</v>
@@ -11766,7 +11766,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H393" t="n">
         <v>2075</v>
@@ -11940,7 +11940,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H399" t="n">
         <v>4059</v>
@@ -11969,7 +11969,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H401" t="n">
         <v>2000</v>
@@ -12114,7 +12114,7 @@
         <v>10</v>
       </c>
       <c r="G405" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H405" t="n">
         <v>6672</v>
@@ -12143,7 +12143,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G406" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H406" t="n">
         <v>60586</v>
@@ -12462,7 +12462,7 @@
         <v>9.75</v>
       </c>
       <c r="G417" t="n">
-        <v>8.34676742553711</v>
+        <v>8.34676837921143</v>
       </c>
       <c r="H417" t="n">
         <v>5344</v>
@@ -12723,7 +12723,7 @@
         <v>10</v>
       </c>
       <c r="G426" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H426" t="n">
         <v>4148</v>
@@ -12752,7 +12752,7 @@
         <v>10.5</v>
       </c>
       <c r="G427" t="n">
-        <v>8.9888277053833</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H427" t="n">
         <v>14779</v>
@@ -12810,7 +12810,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.9888277053833</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H429" t="n">
         <v>39883</v>
@@ -12839,7 +12839,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H430" t="n">
         <v>16073</v>
@@ -12868,7 +12868,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H431" t="n">
         <v>3285</v>
@@ -12897,7 +12897,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H432" t="n">
         <v>8576</v>
@@ -13013,7 +13013,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H436" t="n">
         <v>11201</v>
@@ -13071,7 +13071,7 @@
         <v>10</v>
       </c>
       <c r="G438" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H438" t="n">
         <v>11185</v>
@@ -13100,7 +13100,7 @@
         <v>10</v>
       </c>
       <c r="G439" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H439" t="n">
         <v>15109</v>
@@ -13129,7 +13129,7 @@
         <v>10</v>
       </c>
       <c r="G440" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H440" t="n">
         <v>6043</v>
@@ -13274,7 +13274,7 @@
         <v>10</v>
       </c>
       <c r="G445" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H445" t="n">
         <v>9128</v>
@@ -13303,7 +13303,7 @@
         <v>10</v>
       </c>
       <c r="G446" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H446" t="n">
         <v>7831</v>
@@ -13361,7 +13361,7 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H448" t="n">
         <v>4670</v>
@@ -13419,7 +13419,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.86041450500488</v>
+        <v>8.8604154586792</v>
       </c>
       <c r="H450" t="n">
         <v>18892</v>
@@ -13448,7 +13448,7 @@
         <v>10.5</v>
       </c>
       <c r="G451" t="n">
-        <v>8.9888277053833</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H451" t="n">
         <v>20478</v>
@@ -31927,6 +31927,64 @@
         <v>8528</v>
       </c>
       <c r="I1088" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1089" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1089" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>28417</v>
+      </c>
+      <c r="I1089" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1090" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>17.5499992370605</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>17.1499996185303</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>12161</v>
+      </c>
+      <c r="I1090" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -514,7 +514,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H5" t="n">
         <v>2179</v>
@@ -978,7 +978,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G21" t="n">
-        <v>5.83956289291382</v>
+        <v>5.83956336975098</v>
       </c>
       <c r="H21" t="n">
         <v>1450</v>
@@ -1152,7 +1152,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G27" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H27" t="n">
         <v>20931</v>
@@ -1181,7 +1181,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H28" t="n">
         <v>15424</v>
@@ -1210,7 +1210,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H29" t="n">
         <v>8815</v>
@@ -1790,7 +1790,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.79083204269409</v>
+        <v>5.79083251953125</v>
       </c>
       <c r="H49" t="n">
         <v>628</v>
@@ -1819,7 +1819,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G50" t="n">
-        <v>5.79083204269409</v>
+        <v>5.79083251953125</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>5.79083204269409</v>
+        <v>5.79083251953125</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>5.70149278640747</v>
+        <v>5.70149230957031</v>
       </c>
       <c r="H57" t="n">
         <v>650</v>
@@ -2747,7 +2747,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524885177612</v>
       </c>
       <c r="H82" t="n">
         <v>1650</v>
@@ -2834,7 +2834,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524885177612</v>
       </c>
       <c r="H85" t="n">
         <v>6618</v>
@@ -2921,7 +2921,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>5.89641618728638</v>
+        <v>5.89641571044922</v>
       </c>
       <c r="H88" t="n">
         <v>22052</v>
@@ -2979,7 +2979,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G90" t="n">
-        <v>5.89641618728638</v>
+        <v>5.89641571044922</v>
       </c>
       <c r="H90" t="n">
         <v>5891</v>
@@ -3820,7 +3820,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524885177612</v>
       </c>
       <c r="H119" t="n">
         <v>5694</v>
@@ -4255,7 +4255,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>5.71773624420166</v>
+        <v>5.71773672103882</v>
       </c>
       <c r="H134" t="n">
         <v>9200</v>
@@ -5067,7 +5067,7 @@
         <v>7.5</v>
       </c>
       <c r="G162" t="n">
-        <v>6.09133815765381</v>
+        <v>6.09133863449097</v>
       </c>
       <c r="H162" t="n">
         <v>81003</v>
@@ -5125,7 +5125,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>6.27001762390137</v>
+        <v>6.27001714706421</v>
       </c>
       <c r="H164" t="n">
         <v>62015</v>
@@ -5502,7 +5502,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G177" t="n">
-        <v>6.20504331588745</v>
+        <v>6.20504379272461</v>
       </c>
       <c r="H177" t="n">
         <v>2825</v>
@@ -5850,7 +5850,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483730316162</v>
+        <v>6.72483777999878</v>
       </c>
       <c r="H189" t="n">
         <v>12503</v>
@@ -5879,7 +5879,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64362049102783</v>
+        <v>6.64362001419067</v>
       </c>
       <c r="H190" t="n">
         <v>15454</v>
@@ -31985,6 +31985,35 @@
         <v>12161</v>
       </c>
       <c r="I1090" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1091" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>17.4500007629395</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>8496</v>
+      </c>
+      <c r="I1091" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -833,7 +833,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7745885848999</v>
+        <v>5.77458906173706</v>
       </c>
       <c r="H16" t="n">
         <v>4639</v>
@@ -862,7 +862,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>5.85580730438232</v>
+        <v>5.85580682754517</v>
       </c>
       <c r="H17" t="n">
         <v>1221</v>
@@ -949,7 +949,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G20" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H20" t="n">
         <v>1000</v>
@@ -978,7 +978,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G21" t="n">
-        <v>5.83956336975098</v>
+        <v>5.83956289291382</v>
       </c>
       <c r="H21" t="n">
         <v>1450</v>
@@ -1094,7 +1094,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H25" t="n">
         <v>308</v>
@@ -1268,7 +1268,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G31" t="n">
-        <v>5.82331991195679</v>
+        <v>5.82331943511963</v>
       </c>
       <c r="H31" t="n">
         <v>2124</v>
@@ -1297,7 +1297,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>5.85580730438232</v>
+        <v>5.85580682754517</v>
       </c>
       <c r="H32" t="n">
         <v>379</v>
@@ -1877,7 +1877,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>5.85580730438232</v>
+        <v>5.85580682754517</v>
       </c>
       <c r="H52" t="n">
         <v>11</v>
@@ -1935,7 +1935,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G54" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H54" t="n">
         <v>6012</v>
@@ -2051,7 +2051,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64463996887207</v>
+        <v>5.64464044570923</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -2254,7 +2254,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>5.85580730438232</v>
+        <v>5.85580682754517</v>
       </c>
       <c r="H65" t="n">
         <v>1000</v>
@@ -2283,7 +2283,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>5.85580730438232</v>
+        <v>5.85580682754517</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H67" t="n">
         <v>897</v>
@@ -2486,7 +2486,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H73" t="n">
         <v>1650</v>
@@ -2515,7 +2515,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G74" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H75" t="n">
         <v>170</v>
@@ -2573,7 +2573,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524885177612</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H82" t="n">
         <v>1650</v>
@@ -2776,7 +2776,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H83" t="n">
         <v>3017</v>
@@ -2805,7 +2805,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524885177612</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H85" t="n">
         <v>6618</v>
@@ -2863,7 +2863,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H86" t="n">
         <v>750</v>
@@ -2892,7 +2892,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H87" t="n">
         <v>2590</v>
@@ -2921,7 +2921,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>5.89641571044922</v>
+        <v>5.89641618728638</v>
       </c>
       <c r="H88" t="n">
         <v>22052</v>
@@ -2979,7 +2979,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G90" t="n">
-        <v>5.89641571044922</v>
+        <v>5.89641618728638</v>
       </c>
       <c r="H90" t="n">
         <v>5891</v>
@@ -3356,7 +3356,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H103" t="n">
         <v>8600</v>
@@ -3385,7 +3385,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G104" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H104" t="n">
         <v>19209</v>
@@ -3704,7 +3704,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H115" t="n">
         <v>65929</v>
@@ -3820,7 +3820,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524885177612</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H119" t="n">
         <v>5694</v>
@@ -3849,7 +3849,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G120" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H120" t="n">
         <v>359</v>
@@ -3936,7 +3936,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G123" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H123" t="n">
         <v>1400</v>
@@ -3965,7 +3965,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H124" t="n">
         <v>500</v>
@@ -3994,7 +3994,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G125" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H125" t="n">
         <v>3720</v>
@@ -4052,7 +4052,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H127" t="n">
         <v>6918</v>
@@ -4081,7 +4081,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G128" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H128" t="n">
         <v>214</v>
@@ -4110,7 +4110,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H129" t="n">
         <v>3454</v>
@@ -4255,7 +4255,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>5.71773672103882</v>
+        <v>5.71773624420166</v>
       </c>
       <c r="H134" t="n">
         <v>9200</v>
@@ -4284,7 +4284,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>5.66900587081909</v>
+        <v>5.66900539398193</v>
       </c>
       <c r="H135" t="n">
         <v>15568</v>
@@ -4313,7 +4313,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>5.66900587081909</v>
+        <v>5.66900539398193</v>
       </c>
       <c r="H136" t="n">
         <v>14819</v>
@@ -4342,7 +4342,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H137" t="n">
         <v>1286</v>
@@ -4371,7 +4371,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H138" t="n">
         <v>7627</v>
@@ -4574,7 +4574,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G145" t="n">
-        <v>5.73397970199585</v>
+        <v>5.73398065567017</v>
       </c>
       <c r="H145" t="n">
         <v>3077</v>
@@ -4603,7 +4603,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G146" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H146" t="n">
         <v>8497</v>
@@ -4632,7 +4632,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H147" t="n">
         <v>1510</v>
@@ -4661,7 +4661,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H148" t="n">
         <v>2120</v>
@@ -4690,7 +4690,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H150" t="n">
         <v>110</v>
@@ -4777,7 +4777,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H152" t="n">
         <v>10236</v>
@@ -4893,7 +4893,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G156" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H156" t="n">
         <v>3175</v>
@@ -4922,7 +4922,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G157" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H157" t="n">
         <v>10385</v>
@@ -4951,7 +4951,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H158" t="n">
         <v>10088</v>
@@ -5009,7 +5009,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H160" t="n">
         <v>4793</v>
@@ -5038,7 +5038,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H161" t="n">
         <v>2050</v>
@@ -5096,7 +5096,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>6.46494102478027</v>
+        <v>6.46494054794312</v>
       </c>
       <c r="H163" t="n">
         <v>157736</v>
@@ -5125,7 +5125,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>6.27001714706421</v>
+        <v>6.27001762390137</v>
       </c>
       <c r="H164" t="n">
         <v>62015</v>
@@ -5241,7 +5241,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G168" t="n">
-        <v>6.43245363235474</v>
+        <v>6.43245315551758</v>
       </c>
       <c r="H168" t="n">
         <v>7392</v>
@@ -5415,7 +5415,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>6.41621017456055</v>
+        <v>6.41620969772339</v>
       </c>
       <c r="H174" t="n">
         <v>550</v>
@@ -5444,7 +5444,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>6.41621017456055</v>
+        <v>6.41620969772339</v>
       </c>
       <c r="H175" t="n">
         <v>7100</v>
@@ -5502,7 +5502,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G177" t="n">
-        <v>6.20504379272461</v>
+        <v>6.20504331588745</v>
       </c>
       <c r="H177" t="n">
         <v>2825</v>
@@ -5647,7 +5647,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>6.57864570617676</v>
+        <v>6.57864618301392</v>
       </c>
       <c r="H182" t="n">
         <v>3383</v>
@@ -5676,7 +5676,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G183" t="n">
-        <v>6.57864570617676</v>
+        <v>6.57864618301392</v>
       </c>
       <c r="H183" t="n">
         <v>559</v>
@@ -5705,7 +5705,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>6.43245363235474</v>
+        <v>6.43245315551758</v>
       </c>
       <c r="H184" t="n">
         <v>3432</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.57864570617676</v>
+        <v>6.57864618301392</v>
       </c>
       <c r="H188" t="n">
         <v>5815</v>
@@ -5850,7 +5850,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483777999878</v>
+        <v>6.72483730316162</v>
       </c>
       <c r="H189" t="n">
         <v>12503</v>
@@ -6082,7 +6082,7 @@
         <v>8</v>
       </c>
       <c r="G197" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H197" t="n">
         <v>1992</v>
@@ -6140,7 +6140,7 @@
         <v>8</v>
       </c>
       <c r="G199" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H199" t="n">
         <v>22095</v>
@@ -6169,7 +6169,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G200" t="n">
-        <v>6.97704124450684</v>
+        <v>6.97704172134399</v>
       </c>
       <c r="H200" t="n">
         <v>10206</v>
@@ -6198,7 +6198,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G201" t="n">
-        <v>6.97704124450684</v>
+        <v>6.97704172134399</v>
       </c>
       <c r="H201" t="n">
         <v>5622</v>
@@ -6227,7 +6227,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H202" t="n">
         <v>1380</v>
@@ -6343,7 +6343,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H206" t="n">
         <v>250</v>
@@ -6372,7 +6372,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H207" t="n">
         <v>924</v>
@@ -6430,7 +6430,7 @@
         <v>8</v>
       </c>
       <c r="G209" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H209" t="n">
         <v>6000</v>
@@ -6459,7 +6459,7 @@
         <v>8</v>
       </c>
       <c r="G210" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H210" t="n">
         <v>1453</v>
@@ -6488,7 +6488,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H211" t="n">
         <v>1850</v>
@@ -6546,7 +6546,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H213" t="n">
         <v>2900</v>
@@ -6575,7 +6575,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H214" t="n">
         <v>4315</v>
@@ -6604,7 +6604,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H215" t="n">
         <v>4753</v>
@@ -6633,7 +6633,7 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H230" t="n">
         <v>1340</v>
@@ -7097,7 +7097,7 @@
         <v>8</v>
       </c>
       <c r="G232" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H232" t="n">
         <v>5</v>
@@ -7126,7 +7126,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H234" t="n">
         <v>800</v>
@@ -7184,7 +7184,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180641174316</v>
+        <v>6.59180593490601</v>
       </c>
       <c r="H237" t="n">
         <v>5618</v>
@@ -7300,7 +7300,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H239" t="n">
         <v>10600</v>
@@ -7358,7 +7358,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H241" t="n">
         <v>500</v>
@@ -7387,7 +7387,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H242" t="n">
         <v>200</v>
@@ -7416,7 +7416,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H243" t="n">
         <v>32675</v>
@@ -7445,7 +7445,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G244" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H247" t="n">
         <v>5100</v>
@@ -7561,7 +7561,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H248" t="n">
         <v>5000</v>
@@ -7648,7 +7648,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H251" t="n">
         <v>4818</v>
@@ -7706,7 +7706,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H253" t="n">
         <v>3985</v>
@@ -7764,7 +7764,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H255" t="n">
         <v>851</v>
@@ -7793,7 +7793,7 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>8</v>
       </c>
       <c r="G257" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H257" t="n">
         <v>1200</v>
@@ -7851,7 +7851,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H258" t="n">
         <v>7352</v>
@@ -7880,7 +7880,7 @@
         <v>8</v>
       </c>
       <c r="G259" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H260" t="n">
         <v>5</v>
@@ -7938,7 +7938,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G261" t="n">
-        <v>6.97704124450684</v>
+        <v>6.97704172134399</v>
       </c>
       <c r="H261" t="n">
         <v>800</v>
@@ -8025,7 +8025,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H264" t="n">
         <v>5125</v>
@@ -8112,7 +8112,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H267" t="n">
         <v>1357</v>
@@ -8141,7 +8141,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>8</v>
       </c>
       <c r="G270" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H270" t="n">
         <v>169</v>
@@ -8257,7 +8257,7 @@
         <v>8</v>
       </c>
       <c r="G272" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H272" t="n">
         <v>2337</v>
@@ -8286,7 +8286,7 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H278" t="n">
         <v>2218</v>
@@ -8489,7 +8489,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H280" t="n">
         <v>1214</v>
@@ -8547,7 +8547,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H282" t="n">
         <v>715</v>
@@ -8576,7 +8576,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>8</v>
       </c>
       <c r="G287" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H287" t="n">
         <v>125</v>
@@ -8721,7 +8721,7 @@
         <v>8</v>
       </c>
       <c r="G288" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>8</v>
       </c>
       <c r="G294" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H294" t="n">
         <v>5</v>
@@ -8924,7 +8924,7 @@
         <v>8</v>
       </c>
       <c r="G295" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H295" t="n">
         <v>3</v>
@@ -8953,7 +8953,7 @@
         <v>8</v>
       </c>
       <c r="G296" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H296" t="n">
         <v>12625</v>
@@ -8982,7 +8982,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H297" t="n">
         <v>6500</v>
@@ -9069,7 +9069,7 @@
         <v>8</v>
       </c>
       <c r="G300" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H300" t="n">
         <v>4713</v>
@@ -9504,7 +9504,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H315" t="n">
         <v>4634</v>
@@ -9794,7 +9794,7 @@
         <v>8</v>
       </c>
       <c r="G325" t="n">
-        <v>6.84862995147705</v>
+        <v>6.84862947463989</v>
       </c>
       <c r="H325" t="n">
         <v>45107</v>
@@ -10026,7 +10026,7 @@
         <v>8.25</v>
       </c>
       <c r="G333" t="n">
-        <v>7.06264972686768</v>
+        <v>7.06264925003052</v>
       </c>
       <c r="H333" t="n">
         <v>2000</v>
@@ -10287,7 +10287,7 @@
         <v>8.25</v>
       </c>
       <c r="G342" t="n">
-        <v>7.06264972686768</v>
+        <v>7.06264925003052</v>
       </c>
       <c r="H342" t="n">
         <v>250</v>
@@ -10490,7 +10490,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G349" t="n">
-        <v>7.36227750778198</v>
+        <v>7.36227703094482</v>
       </c>
       <c r="H349" t="n">
         <v>18029</v>
@@ -10519,7 +10519,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G350" t="n">
-        <v>7.36227750778198</v>
+        <v>7.36227703094482</v>
       </c>
       <c r="H350" t="n">
         <v>4020</v>
@@ -10780,7 +10780,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83312082290649</v>
+        <v>7.83312034606934</v>
       </c>
       <c r="H359" t="n">
         <v>11764</v>
@@ -10867,7 +10867,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H362" t="n">
         <v>13708</v>
@@ -10896,7 +10896,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H363" t="n">
         <v>19547</v>
@@ -10954,7 +10954,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.38957118988037</v>
+        <v>8.38957214355469</v>
       </c>
       <c r="H365" t="n">
         <v>6680</v>
@@ -10983,7 +10983,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.38957118988037</v>
+        <v>8.38957214355469</v>
       </c>
       <c r="H366" t="n">
         <v>4623</v>
@@ -11099,7 +11099,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H370" t="n">
         <v>4568</v>
@@ -11128,7 +11128,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H371" t="n">
         <v>1661</v>
@@ -11157,7 +11157,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H372" t="n">
         <v>1094</v>
@@ -11186,7 +11186,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H373" t="n">
         <v>1893</v>
@@ -11215,7 +11215,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H374" t="n">
         <v>3549</v>
@@ -11273,7 +11273,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H376" t="n">
         <v>19650</v>
@@ -11302,7 +11302,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H377" t="n">
         <v>1925</v>
@@ -11331,7 +11331,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H378" t="n">
         <v>4890</v>
@@ -11360,7 +11360,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H379" t="n">
         <v>1750</v>
@@ -11389,7 +11389,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H380" t="n">
         <v>2479</v>
@@ -11418,7 +11418,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H381" t="n">
         <v>955</v>
@@ -11447,7 +11447,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G382" t="n">
-        <v>8.0043363571167</v>
+        <v>8.00433731079102</v>
       </c>
       <c r="H382" t="n">
         <v>62</v>
@@ -11476,7 +11476,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H383" t="n">
         <v>500</v>
@@ -11505,7 +11505,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153211593628</v>
       </c>
       <c r="H384" t="n">
         <v>1430</v>
@@ -11621,7 +11621,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H388" t="n">
         <v>2450</v>
@@ -11650,7 +11650,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H389" t="n">
         <v>2705</v>
@@ -11679,7 +11679,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H390" t="n">
         <v>830</v>
@@ -11708,7 +11708,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H391" t="n">
         <v>4396</v>
@@ -11766,7 +11766,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H393" t="n">
         <v>2075</v>
@@ -11940,7 +11940,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H399" t="n">
         <v>4059</v>
@@ -11969,7 +11969,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H401" t="n">
         <v>2000</v>
@@ -12114,7 +12114,7 @@
         <v>10</v>
       </c>
       <c r="G405" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H405" t="n">
         <v>6672</v>
@@ -12143,7 +12143,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G406" t="n">
-        <v>8.17555141448975</v>
+        <v>8.17555236816406</v>
       </c>
       <c r="H406" t="n">
         <v>60586</v>
@@ -12462,7 +12462,7 @@
         <v>9.75</v>
       </c>
       <c r="G417" t="n">
-        <v>8.34676837921143</v>
+        <v>8.34676742553711</v>
       </c>
       <c r="H417" t="n">
         <v>5344</v>
@@ -12723,7 +12723,7 @@
         <v>10</v>
       </c>
       <c r="G426" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H426" t="n">
         <v>4148</v>
@@ -12752,7 +12752,7 @@
         <v>10.5</v>
       </c>
       <c r="G427" t="n">
-        <v>8.98882579803467</v>
+        <v>8.9888277053833</v>
       </c>
       <c r="H427" t="n">
         <v>14779</v>
@@ -12810,7 +12810,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.98882579803467</v>
+        <v>8.9888277053833</v>
       </c>
       <c r="H429" t="n">
         <v>39883</v>
@@ -12839,7 +12839,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H430" t="n">
         <v>16073</v>
@@ -12868,7 +12868,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H431" t="n">
         <v>3285</v>
@@ -12897,7 +12897,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H432" t="n">
         <v>8576</v>
@@ -13013,7 +13013,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H436" t="n">
         <v>11201</v>
@@ -13071,7 +13071,7 @@
         <v>10</v>
       </c>
       <c r="G438" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H438" t="n">
         <v>11185</v>
@@ -13100,7 +13100,7 @@
         <v>10</v>
       </c>
       <c r="G439" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H439" t="n">
         <v>15109</v>
@@ -13129,7 +13129,7 @@
         <v>10</v>
       </c>
       <c r="G440" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H440" t="n">
         <v>6043</v>
@@ -13274,7 +13274,7 @@
         <v>10</v>
       </c>
       <c r="G445" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H445" t="n">
         <v>9128</v>
@@ -13303,7 +13303,7 @@
         <v>10</v>
       </c>
       <c r="G446" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H446" t="n">
         <v>7831</v>
@@ -13361,7 +13361,7 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H448" t="n">
         <v>4670</v>
@@ -13419,7 +13419,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.8604154586792</v>
+        <v>8.86041450500488</v>
       </c>
       <c r="H450" t="n">
         <v>18892</v>
@@ -13448,7 +13448,7 @@
         <v>10.5</v>
       </c>
       <c r="G451" t="n">
-        <v>8.98882579803467</v>
+        <v>8.9888277053833</v>
       </c>
       <c r="H451" t="n">
         <v>20478</v>
@@ -32011,9 +32011,38 @@
         <v>17.25</v>
       </c>
       <c r="H1091" t="n">
-        <v>8496</v>
+        <v>8928</v>
       </c>
       <c r="I1091" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1092" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>14774</v>
+      </c>
+      <c r="I1092" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -514,7 +514,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H5" t="n">
         <v>2179</v>
@@ -572,7 +572,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8070764541626</v>
+        <v>5.80707597732544</v>
       </c>
       <c r="H7" t="n">
         <v>10000</v>
@@ -746,7 +746,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G13" t="n">
-        <v>5.86392879486084</v>
+        <v>5.86392831802368</v>
       </c>
       <c r="H13" t="n">
         <v>217</v>
@@ -1036,7 +1036,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>5.8070764541626</v>
+        <v>5.80707597732544</v>
       </c>
       <c r="H23" t="n">
         <v>681</v>
@@ -1152,7 +1152,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G27" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H27" t="n">
         <v>20931</v>
@@ -1181,7 +1181,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H28" t="n">
         <v>15424</v>
@@ -1210,7 +1210,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H29" t="n">
         <v>8815</v>
@@ -1384,7 +1384,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>5.8070764541626</v>
+        <v>5.80707597732544</v>
       </c>
       <c r="H35" t="n">
         <v>20</v>
@@ -1442,7 +1442,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>5.8070764541626</v>
+        <v>5.80707597732544</v>
       </c>
       <c r="H37" t="n">
         <v>300</v>
@@ -1471,7 +1471,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>5.8070764541626</v>
+        <v>5.80707597732544</v>
       </c>
       <c r="H38" t="n">
         <v>2870</v>
@@ -1500,7 +1500,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G39" t="n">
-        <v>5.8070764541626</v>
+        <v>5.80707597732544</v>
       </c>
       <c r="H39" t="n">
         <v>169</v>
@@ -2022,7 +2022,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>5.70149230957031</v>
+        <v>5.70149278640747</v>
       </c>
       <c r="H57" t="n">
         <v>650</v>
@@ -2051,7 +2051,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64464044570923</v>
+        <v>5.64463996887207</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -2747,7 +2747,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H82" t="n">
         <v>1650</v>
@@ -2776,7 +2776,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H83" t="n">
         <v>3017</v>
@@ -2805,7 +2805,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H85" t="n">
         <v>6618</v>
@@ -3037,7 +3037,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>5.86392879486084</v>
+        <v>5.86392831802368</v>
       </c>
       <c r="H92" t="n">
         <v>800</v>
@@ -3356,7 +3356,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H103" t="n">
         <v>8600</v>
@@ -3385,7 +3385,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G104" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H104" t="n">
         <v>19209</v>
@@ -3820,7 +3820,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H119" t="n">
         <v>5694</v>
@@ -3878,7 +3878,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>5.78271055221558</v>
+        <v>5.78271102905273</v>
       </c>
       <c r="H121" t="n">
         <v>8</v>
@@ -4052,7 +4052,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H127" t="n">
         <v>6918</v>
@@ -4081,7 +4081,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G128" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H128" t="n">
         <v>214</v>
@@ -4168,7 +4168,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>5.78271055221558</v>
+        <v>5.78271102905273</v>
       </c>
       <c r="H131" t="n">
         <v>2050</v>
@@ -4284,7 +4284,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>5.66900539398193</v>
+        <v>5.66900634765625</v>
       </c>
       <c r="H135" t="n">
         <v>15568</v>
@@ -4313,7 +4313,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>5.66900539398193</v>
+        <v>5.66900634765625</v>
       </c>
       <c r="H136" t="n">
         <v>14819</v>
@@ -4342,7 +4342,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H137" t="n">
         <v>1286</v>
@@ -4371,7 +4371,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H138" t="n">
         <v>7627</v>
@@ -4400,7 +4400,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>5.78271055221558</v>
+        <v>5.78271102905273</v>
       </c>
       <c r="H139" t="n">
         <v>31688</v>
@@ -4574,7 +4574,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G145" t="n">
-        <v>5.73398065567017</v>
+        <v>5.73398017883301</v>
       </c>
       <c r="H145" t="n">
         <v>3077</v>
@@ -5096,7 +5096,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>6.46494054794312</v>
+        <v>6.46494102478027</v>
       </c>
       <c r="H163" t="n">
         <v>157736</v>
@@ -5154,7 +5154,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H165" t="n">
         <v>10198</v>
@@ -5212,7 +5212,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H167" t="n">
         <v>7616</v>
@@ -5241,7 +5241,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G168" t="n">
-        <v>6.43245315551758</v>
+        <v>6.43245363235474</v>
       </c>
       <c r="H168" t="n">
         <v>7392</v>
@@ -5415,7 +5415,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>6.41620969772339</v>
+        <v>6.41621017456055</v>
       </c>
       <c r="H174" t="n">
         <v>550</v>
@@ -5444,7 +5444,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>6.41620969772339</v>
+        <v>6.41621017456055</v>
       </c>
       <c r="H175" t="n">
         <v>7100</v>
@@ -5531,7 +5531,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G178" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H178" t="n">
         <v>3628</v>
@@ -5705,7 +5705,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>6.43245315551758</v>
+        <v>6.43245363235474</v>
       </c>
       <c r="H184" t="n">
         <v>3432</v>
@@ -5850,7 +5850,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483730316162</v>
+        <v>6.72483777999878</v>
       </c>
       <c r="H189" t="n">
         <v>12503</v>
@@ -5908,7 +5908,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G191" t="n">
-        <v>6.78981161117554</v>
+        <v>6.7898120880127</v>
       </c>
       <c r="H191" t="n">
         <v>35519</v>
@@ -6082,7 +6082,7 @@
         <v>8</v>
       </c>
       <c r="G197" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H197" t="n">
         <v>1992</v>
@@ -6140,7 +6140,7 @@
         <v>8</v>
       </c>
       <c r="G199" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H199" t="n">
         <v>22095</v>
@@ -6169,7 +6169,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G200" t="n">
-        <v>6.97704172134399</v>
+        <v>6.97704124450684</v>
       </c>
       <c r="H200" t="n">
         <v>10206</v>
@@ -6198,7 +6198,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G201" t="n">
-        <v>6.97704172134399</v>
+        <v>6.97704124450684</v>
       </c>
       <c r="H201" t="n">
         <v>5622</v>
@@ -6227,7 +6227,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H202" t="n">
         <v>1380</v>
@@ -6343,7 +6343,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H206" t="n">
         <v>250</v>
@@ -6372,7 +6372,7 @@
         <v>8</v>
       </c>
       <c r="G207" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H207" t="n">
         <v>924</v>
@@ -6430,7 +6430,7 @@
         <v>8</v>
       </c>
       <c r="G209" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H209" t="n">
         <v>6000</v>
@@ -6459,7 +6459,7 @@
         <v>8</v>
       </c>
       <c r="G210" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H210" t="n">
         <v>1453</v>
@@ -6488,7 +6488,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H211" t="n">
         <v>1850</v>
@@ -6546,7 +6546,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H213" t="n">
         <v>2900</v>
@@ -6575,7 +6575,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H214" t="n">
         <v>4315</v>
@@ -6604,7 +6604,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H215" t="n">
         <v>4753</v>
@@ -6633,7 +6633,7 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H230" t="n">
         <v>1340</v>
@@ -7097,7 +7097,7 @@
         <v>8</v>
       </c>
       <c r="G232" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H232" t="n">
         <v>5</v>
@@ -7126,7 +7126,7 @@
         <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H234" t="n">
         <v>800</v>
@@ -7184,7 +7184,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180593490601</v>
+        <v>6.59180641174316</v>
       </c>
       <c r="H237" t="n">
         <v>5618</v>
@@ -7300,7 +7300,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H239" t="n">
         <v>10600</v>
@@ -7358,7 +7358,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H241" t="n">
         <v>500</v>
@@ -7387,7 +7387,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H242" t="n">
         <v>200</v>
@@ -7416,7 +7416,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H243" t="n">
         <v>32675</v>
@@ -7445,7 +7445,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G244" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H247" t="n">
         <v>5100</v>
@@ -7561,7 +7561,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H248" t="n">
         <v>5000</v>
@@ -7648,7 +7648,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H251" t="n">
         <v>4818</v>
@@ -7706,7 +7706,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H253" t="n">
         <v>3985</v>
@@ -7764,7 +7764,7 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H255" t="n">
         <v>851</v>
@@ -7793,7 +7793,7 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>8</v>
       </c>
       <c r="G257" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H257" t="n">
         <v>1200</v>
@@ -7851,7 +7851,7 @@
         <v>8</v>
       </c>
       <c r="G258" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H258" t="n">
         <v>7352</v>
@@ -7880,7 +7880,7 @@
         <v>8</v>
       </c>
       <c r="G259" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H260" t="n">
         <v>5</v>
@@ -7938,7 +7938,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G261" t="n">
-        <v>6.97704172134399</v>
+        <v>6.97704124450684</v>
       </c>
       <c r="H261" t="n">
         <v>800</v>
@@ -8025,7 +8025,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H264" t="n">
         <v>5125</v>
@@ -8112,7 +8112,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H267" t="n">
         <v>1357</v>
@@ -8141,7 +8141,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>8</v>
       </c>
       <c r="G270" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H270" t="n">
         <v>169</v>
@@ -8257,7 +8257,7 @@
         <v>8</v>
       </c>
       <c r="G272" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H272" t="n">
         <v>2337</v>
@@ -8286,7 +8286,7 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H278" t="n">
         <v>2218</v>
@@ -8489,7 +8489,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H280" t="n">
         <v>1214</v>
@@ -8547,7 +8547,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H282" t="n">
         <v>715</v>
@@ -8576,7 +8576,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>8</v>
       </c>
       <c r="G287" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H287" t="n">
         <v>125</v>
@@ -8721,7 +8721,7 @@
         <v>8</v>
       </c>
       <c r="G288" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>8</v>
       </c>
       <c r="G294" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H294" t="n">
         <v>5</v>
@@ -8924,7 +8924,7 @@
         <v>8</v>
       </c>
       <c r="G295" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H295" t="n">
         <v>3</v>
@@ -8953,7 +8953,7 @@
         <v>8</v>
       </c>
       <c r="G296" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H296" t="n">
         <v>12625</v>
@@ -8982,7 +8982,7 @@
         <v>8</v>
       </c>
       <c r="G297" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H297" t="n">
         <v>6500</v>
@@ -9069,7 +9069,7 @@
         <v>8</v>
       </c>
       <c r="G300" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H300" t="n">
         <v>4713</v>
@@ -9504,7 +9504,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H315" t="n">
         <v>4634</v>
@@ -9794,7 +9794,7 @@
         <v>8</v>
       </c>
       <c r="G325" t="n">
-        <v>6.84862947463989</v>
+        <v>6.84862995147705</v>
       </c>
       <c r="H325" t="n">
         <v>45107</v>
@@ -10026,7 +10026,7 @@
         <v>8.25</v>
       </c>
       <c r="G333" t="n">
-        <v>7.06264925003052</v>
+        <v>7.06264972686768</v>
       </c>
       <c r="H333" t="n">
         <v>2000</v>
@@ -10287,7 +10287,7 @@
         <v>8.25</v>
       </c>
       <c r="G342" t="n">
-        <v>7.06264925003052</v>
+        <v>7.06264972686768</v>
       </c>
       <c r="H342" t="n">
         <v>250</v>
@@ -10490,7 +10490,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G349" t="n">
-        <v>7.36227703094482</v>
+        <v>7.36227750778198</v>
       </c>
       <c r="H349" t="n">
         <v>18029</v>
@@ -10519,7 +10519,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G350" t="n">
-        <v>7.36227703094482</v>
+        <v>7.36227750778198</v>
       </c>
       <c r="H350" t="n">
         <v>4020</v>
@@ -10780,7 +10780,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83312034606934</v>
+        <v>7.83312082290649</v>
       </c>
       <c r="H359" t="n">
         <v>11764</v>
@@ -10867,7 +10867,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H362" t="n">
         <v>13708</v>
@@ -10896,7 +10896,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H363" t="n">
         <v>19547</v>
@@ -10954,7 +10954,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H365" t="n">
         <v>6680</v>
@@ -10983,7 +10983,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H366" t="n">
         <v>4623</v>
@@ -11099,7 +11099,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H370" t="n">
         <v>4568</v>
@@ -11128,7 +11128,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H371" t="n">
         <v>1661</v>
@@ -11157,7 +11157,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H372" t="n">
         <v>1094</v>
@@ -11186,7 +11186,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H373" t="n">
         <v>1893</v>
@@ -11215,7 +11215,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H374" t="n">
         <v>3549</v>
@@ -11273,7 +11273,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H376" t="n">
         <v>19650</v>
@@ -11302,7 +11302,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H377" t="n">
         <v>1925</v>
@@ -11331,7 +11331,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H378" t="n">
         <v>4890</v>
@@ -11360,7 +11360,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H379" t="n">
         <v>1750</v>
@@ -11389,7 +11389,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H380" t="n">
         <v>2479</v>
@@ -11418,7 +11418,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H381" t="n">
         <v>955</v>
@@ -11447,7 +11447,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G382" t="n">
-        <v>8.00433731079102</v>
+        <v>8.0043363571167</v>
       </c>
       <c r="H382" t="n">
         <v>62</v>
@@ -11476,7 +11476,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H383" t="n">
         <v>500</v>
@@ -11505,7 +11505,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153211593628</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H384" t="n">
         <v>1430</v>
@@ -11621,7 +11621,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H388" t="n">
         <v>2450</v>
@@ -11650,7 +11650,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H389" t="n">
         <v>2705</v>
@@ -11679,7 +11679,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H390" t="n">
         <v>830</v>
@@ -11708,7 +11708,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H391" t="n">
         <v>4396</v>
@@ -11766,7 +11766,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H393" t="n">
         <v>2075</v>
@@ -11940,7 +11940,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H399" t="n">
         <v>4059</v>
@@ -11969,7 +11969,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H401" t="n">
         <v>2000</v>
@@ -12114,7 +12114,7 @@
         <v>10</v>
       </c>
       <c r="G405" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H405" t="n">
         <v>6672</v>
@@ -12143,7 +12143,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G406" t="n">
-        <v>8.17555236816406</v>
+        <v>8.17555141448975</v>
       </c>
       <c r="H406" t="n">
         <v>60586</v>
@@ -12462,7 +12462,7 @@
         <v>9.75</v>
       </c>
       <c r="G417" t="n">
-        <v>8.34676742553711</v>
+        <v>8.34676837921143</v>
       </c>
       <c r="H417" t="n">
         <v>5344</v>
@@ -12723,7 +12723,7 @@
         <v>10</v>
       </c>
       <c r="G426" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H426" t="n">
         <v>4148</v>
@@ -12752,7 +12752,7 @@
         <v>10.5</v>
       </c>
       <c r="G427" t="n">
-        <v>8.9888277053833</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H427" t="n">
         <v>14779</v>
@@ -12810,7 +12810,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.9888277053833</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H429" t="n">
         <v>39883</v>
@@ -12839,7 +12839,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H430" t="n">
         <v>16073</v>
@@ -12868,7 +12868,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H431" t="n">
         <v>3285</v>
@@ -12897,7 +12897,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H432" t="n">
         <v>8576</v>
@@ -13013,7 +13013,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H436" t="n">
         <v>11201</v>
@@ -13071,7 +13071,7 @@
         <v>10</v>
       </c>
       <c r="G438" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H438" t="n">
         <v>11185</v>
@@ -13100,7 +13100,7 @@
         <v>10</v>
       </c>
       <c r="G439" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H439" t="n">
         <v>15109</v>
@@ -13129,7 +13129,7 @@
         <v>10</v>
       </c>
       <c r="G440" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H440" t="n">
         <v>6043</v>
@@ -13274,7 +13274,7 @@
         <v>10</v>
       </c>
       <c r="G445" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H445" t="n">
         <v>9128</v>
@@ -13303,7 +13303,7 @@
         <v>10</v>
       </c>
       <c r="G446" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H446" t="n">
         <v>7831</v>
@@ -13361,7 +13361,7 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H448" t="n">
         <v>4670</v>
@@ -13419,7 +13419,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.86041450500488</v>
+        <v>8.8604154586792</v>
       </c>
       <c r="H450" t="n">
         <v>18892</v>
@@ -13448,7 +13448,7 @@
         <v>10.5</v>
       </c>
       <c r="G451" t="n">
-        <v>8.9888277053833</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H451" t="n">
         <v>20478</v>
@@ -32043,6 +32043,35 @@
         <v>14774</v>
       </c>
       <c r="I1092" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1093" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>17.1499996185303</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>17.1499996185303</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>16.5499992370605</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>60801</v>
+      </c>
+      <c r="I1093" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -514,7 +514,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H5" t="n">
         <v>2179</v>
@@ -775,7 +775,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H14" t="n">
         <v>22</v>
@@ -891,7 +891,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H18" t="n">
         <v>22</v>
@@ -949,7 +949,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G20" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H20" t="n">
         <v>1000</v>
@@ -978,7 +978,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G21" t="n">
-        <v>5.83956289291382</v>
+        <v>5.83956336975098</v>
       </c>
       <c r="H21" t="n">
         <v>1450</v>
@@ -1152,7 +1152,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G27" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H27" t="n">
         <v>20931</v>
@@ -1181,7 +1181,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H28" t="n">
         <v>15424</v>
@@ -1210,7 +1210,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H29" t="n">
         <v>8815</v>
@@ -1558,7 +1558,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G41" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H41" t="n">
         <v>271</v>
@@ -1935,7 +1935,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G54" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H54" t="n">
         <v>6012</v>
@@ -1964,7 +1964,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H55" t="n">
         <v>3500</v>
@@ -2022,7 +2022,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>5.70149278640747</v>
+        <v>5.70149230957031</v>
       </c>
       <c r="H57" t="n">
         <v>650</v>
@@ -2051,7 +2051,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64463996887207</v>
+        <v>5.64464092254639</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -2747,7 +2747,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H82" t="n">
         <v>1650</v>
@@ -2776,7 +2776,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H83" t="n">
         <v>3017</v>
@@ -2805,7 +2805,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H85" t="n">
         <v>6618</v>
@@ -2863,7 +2863,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H86" t="n">
         <v>750</v>
@@ -2892,7 +2892,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H87" t="n">
         <v>2590</v>
@@ -2921,7 +2921,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>5.89641618728638</v>
+        <v>5.89641571044922</v>
       </c>
       <c r="H88" t="n">
         <v>22052</v>
@@ -2950,7 +2950,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>5.88017225265503</v>
+        <v>5.88017177581787</v>
       </c>
       <c r="H89" t="n">
         <v>846</v>
@@ -2979,7 +2979,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G90" t="n">
-        <v>5.89641618728638</v>
+        <v>5.89641571044922</v>
       </c>
       <c r="H90" t="n">
         <v>5891</v>
@@ -3066,7 +3066,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G93" t="n">
-        <v>5.88017225265503</v>
+        <v>5.88017177581787</v>
       </c>
       <c r="H93" t="n">
         <v>1382</v>
@@ -3095,7 +3095,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>5.88017225265503</v>
+        <v>5.88017177581787</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H95" t="n">
         <v>2618</v>
@@ -3153,7 +3153,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H98" t="n">
         <v>481</v>
@@ -3240,7 +3240,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H99" t="n">
         <v>8</v>
@@ -3269,7 +3269,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H100" t="n">
         <v>186</v>
@@ -3356,7 +3356,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H103" t="n">
         <v>8600</v>
@@ -3385,7 +3385,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G104" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H104" t="n">
         <v>19209</v>
@@ -3443,7 +3443,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H106" t="n">
         <v>145</v>
@@ -3472,7 +3472,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H107" t="n">
         <v>667</v>
@@ -3501,7 +3501,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G116" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H116" t="n">
         <v>1167</v>
@@ -3820,7 +3820,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524980545044</v>
+        <v>5.68524932861328</v>
       </c>
       <c r="H119" t="n">
         <v>5694</v>
@@ -3849,7 +3849,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G120" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H120" t="n">
         <v>359</v>
@@ -3878,7 +3878,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H121" t="n">
         <v>8</v>
@@ -3936,7 +3936,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G123" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H123" t="n">
         <v>1400</v>
@@ -3965,7 +3965,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H124" t="n">
         <v>500</v>
@@ -3994,7 +3994,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G125" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H125" t="n">
         <v>3720</v>
@@ -4052,7 +4052,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H127" t="n">
         <v>6918</v>
@@ -4081,7 +4081,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G128" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H128" t="n">
         <v>214</v>
@@ -4139,7 +4139,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H130" t="n">
         <v>4648</v>
@@ -4168,7 +4168,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H131" t="n">
         <v>2050</v>
@@ -4197,7 +4197,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H132" t="n">
         <v>1700</v>
@@ -4226,7 +4226,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H133" t="n">
         <v>14468</v>
@@ -4284,7 +4284,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>5.66900634765625</v>
+        <v>5.66900587081909</v>
       </c>
       <c r="H135" t="n">
         <v>15568</v>
@@ -4313,7 +4313,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>5.66900634765625</v>
+        <v>5.66900587081909</v>
       </c>
       <c r="H136" t="n">
         <v>14819</v>
@@ -4342,7 +4342,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H137" t="n">
         <v>1286</v>
@@ -4371,7 +4371,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>5.75022315979004</v>
+        <v>5.7502236366272</v>
       </c>
       <c r="H138" t="n">
         <v>7627</v>
@@ -4400,7 +4400,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>5.78271102905273</v>
+        <v>5.78271055221558</v>
       </c>
       <c r="H139" t="n">
         <v>31688</v>
@@ -4429,7 +4429,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H140" t="n">
         <v>2500</v>
@@ -4458,7 +4458,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H144" t="n">
         <v>80</v>
@@ -4574,7 +4574,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G145" t="n">
-        <v>5.73398017883301</v>
+        <v>5.73397970199585</v>
       </c>
       <c r="H145" t="n">
         <v>3077</v>
@@ -4603,7 +4603,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G146" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H146" t="n">
         <v>8497</v>
@@ -4632,7 +4632,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H147" t="n">
         <v>1510</v>
@@ -4661,7 +4661,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H148" t="n">
         <v>2120</v>
@@ -4690,7 +4690,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H150" t="n">
         <v>110</v>
@@ -4893,7 +4893,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G156" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H156" t="n">
         <v>3175</v>
@@ -4922,7 +4922,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G157" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H157" t="n">
         <v>10385</v>
@@ -4980,7 +4980,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>5.76646709442139</v>
+        <v>5.76646661758423</v>
       </c>
       <c r="H159" t="n">
         <v>2979</v>
@@ -5009,7 +5009,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H160" t="n">
         <v>4793</v>
@@ -5183,7 +5183,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G166" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H166" t="n">
         <v>5498</v>
@@ -5299,7 +5299,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G170" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H170" t="n">
         <v>3020</v>
@@ -5415,7 +5415,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>6.41621017456055</v>
+        <v>6.41620969772339</v>
       </c>
       <c r="H174" t="n">
         <v>550</v>
@@ -5444,7 +5444,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>6.41621017456055</v>
+        <v>6.41620969772339</v>
       </c>
       <c r="H175" t="n">
         <v>7100</v>
@@ -5473,7 +5473,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H176" t="n">
         <v>3660</v>
@@ -5502,7 +5502,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G177" t="n">
-        <v>6.20504331588745</v>
+        <v>6.20504379272461</v>
       </c>
       <c r="H177" t="n">
         <v>2825</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H179" t="n">
         <v>2200</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>6.52991485595703</v>
+        <v>6.52991533279419</v>
       </c>
       <c r="H185" t="n">
         <v>625</v>
@@ -5763,7 +5763,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G186" t="n">
-        <v>6.513671875</v>
+        <v>6.51367139816284</v>
       </c>
       <c r="H186" t="n">
         <v>1000</v>
@@ -5850,7 +5850,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483777999878</v>
+        <v>6.72483825683594</v>
       </c>
       <c r="H189" t="n">
         <v>12503</v>
@@ -5879,7 +5879,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64362001419067</v>
+        <v>6.64362049102783</v>
       </c>
       <c r="H190" t="n">
         <v>15454</v>
@@ -5908,7 +5908,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G191" t="n">
-        <v>6.7898120880127</v>
+        <v>6.78981161117554</v>
       </c>
       <c r="H191" t="n">
         <v>35519</v>
@@ -5937,7 +5937,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G192" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H192" t="n">
         <v>19653</v>
@@ -5966,7 +5966,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G193" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H193" t="n">
         <v>9223</v>
@@ -5995,7 +5995,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G194" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H194" t="n">
         <v>11641</v>
@@ -6024,7 +6024,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G195" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H195" t="n">
         <v>5819</v>
@@ -6053,7 +6053,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G196" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H196" t="n">
         <v>4800</v>
@@ -6227,7 +6227,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H202" t="n">
         <v>1380</v>
@@ -6343,7 +6343,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H206" t="n">
         <v>250</v>
@@ -6488,7 +6488,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H211" t="n">
         <v>1850</v>
@@ -6517,7 +6517,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G212" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H212" t="n">
         <v>2457</v>
@@ -6662,7 +6662,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G217" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H217" t="n">
         <v>6686</v>
@@ -7039,7 +7039,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H230" t="n">
         <v>1340</v>
@@ -7155,7 +7155,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H234" t="n">
         <v>800</v>
@@ -7184,7 +7184,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G236" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H236" t="n">
         <v>1250</v>
@@ -7242,7 +7242,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180641174316</v>
+        <v>6.59180545806885</v>
       </c>
       <c r="H237" t="n">
         <v>5618</v>
@@ -7300,7 +7300,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H239" t="n">
         <v>10600</v>
@@ -7358,7 +7358,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H241" t="n">
         <v>500</v>
@@ -7387,7 +7387,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H242" t="n">
         <v>200</v>
@@ -7416,7 +7416,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H243" t="n">
         <v>32675</v>
@@ -7445,7 +7445,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G244" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H247" t="n">
         <v>5100</v>
@@ -7561,7 +7561,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H248" t="n">
         <v>5000</v>
@@ -7619,7 +7619,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H250" t="n">
         <v>1818</v>
@@ -7648,7 +7648,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H251" t="n">
         <v>4818</v>
@@ -7677,7 +7677,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H252" t="n">
         <v>1000</v>
@@ -7706,7 +7706,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H253" t="n">
         <v>3985</v>
@@ -7909,7 +7909,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H260" t="n">
         <v>5</v>
@@ -8025,7 +8025,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H264" t="n">
         <v>5125</v>
@@ -8054,7 +8054,7 @@
         <v>7.75</v>
       </c>
       <c r="G265" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H265" t="n">
         <v>10500</v>
@@ -8083,7 +8083,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H266" t="n">
         <v>3382</v>
@@ -8112,7 +8112,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H267" t="n">
         <v>1357</v>
@@ -8141,7 +8141,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H274" t="n">
         <v>250</v>
@@ -8344,7 +8344,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G276" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H276" t="n">
         <v>5210</v>
@@ -8489,7 +8489,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H280" t="n">
         <v>1214</v>
@@ -8518,7 +8518,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G281" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H281" t="n">
         <v>286</v>
@@ -9011,7 +9011,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G298" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H298" t="n">
         <v>1867</v>
@@ -9040,7 +9040,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H299" t="n">
         <v>1915</v>
@@ -9417,7 +9417,7 @@
         <v>7.75</v>
       </c>
       <c r="G312" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H312" t="n">
         <v>3450</v>
@@ -9446,7 +9446,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G313" t="n">
-        <v>6.37778663635254</v>
+        <v>6.37778615951538</v>
       </c>
       <c r="H313" t="n">
         <v>12049</v>
@@ -9475,7 +9475,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>6.50619792938232</v>
+        <v>6.50619840621948</v>
       </c>
       <c r="H314" t="n">
         <v>10065</v>
@@ -9504,7 +9504,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H315" t="n">
         <v>4634</v>
@@ -9533,7 +9533,7 @@
         <v>7.75</v>
       </c>
       <c r="G316" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H316" t="n">
         <v>3144</v>
@@ -9562,7 +9562,7 @@
         <v>7.75</v>
       </c>
       <c r="G317" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H317" t="n">
         <v>3850</v>
@@ -9591,7 +9591,7 @@
         <v>7.75</v>
       </c>
       <c r="G318" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>7.75</v>
       </c>
       <c r="G319" t="n">
-        <v>6.63461017608643</v>
+        <v>6.63460969924927</v>
       </c>
       <c r="H319" t="n">
         <v>1200</v>
@@ -9707,7 +9707,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>6.80582571029663</v>
+        <v>6.80582523345947</v>
       </c>
       <c r="H322" t="n">
         <v>1193</v>
@@ -9765,7 +9765,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H324" t="n">
         <v>7290</v>
@@ -9852,7 +9852,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G327" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H327" t="n">
         <v>10572</v>
@@ -9910,7 +9910,7 @@
         <v>8.5</v>
       </c>
       <c r="G329" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H329" t="n">
         <v>4383</v>
@@ -10142,7 +10142,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G337" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H337" t="n">
         <v>19514</v>
@@ -10171,7 +10171,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H339" t="n">
         <v>50</v>
@@ -10229,7 +10229,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H340" t="n">
         <v>850</v>
@@ -10316,7 +10316,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H343" t="n">
         <v>1537</v>
@@ -10345,7 +10345,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>7.0198450088501</v>
+        <v>7.01984548568726</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>8.5</v>
       </c>
       <c r="G351" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H351" t="n">
         <v>441</v>
@@ -10577,7 +10577,7 @@
         <v>8.5</v>
       </c>
       <c r="G352" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>8.5</v>
       </c>
       <c r="G353" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>7.44788455963135</v>
+        <v>7.44788408279419</v>
       </c>
       <c r="H354" t="n">
         <v>990</v>
@@ -10664,7 +10664,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>7.44788455963135</v>
+        <v>7.44788408279419</v>
       </c>
       <c r="H355" t="n">
         <v>2665</v>
@@ -10693,7 +10693,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>7.53349304199219</v>
+        <v>7.53349256515503</v>
       </c>
       <c r="H356" t="n">
         <v>24746</v>
@@ -10722,7 +10722,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>7.79031658172607</v>
+        <v>7.79031610488892</v>
       </c>
       <c r="H357" t="n">
         <v>4994</v>
@@ -10780,7 +10780,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83312082290649</v>
+        <v>7.83312034606934</v>
       </c>
       <c r="H359" t="n">
         <v>11764</v>
@@ -10867,7 +10867,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H362" t="n">
         <v>13708</v>
@@ -10896,7 +10896,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H363" t="n">
         <v>19547</v>
@@ -10954,7 +10954,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.38957118988037</v>
+        <v>8.38957214355469</v>
       </c>
       <c r="H365" t="n">
         <v>6680</v>
@@ -10983,7 +10983,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.38957118988037</v>
+        <v>8.38957214355469</v>
       </c>
       <c r="H366" t="n">
         <v>4623</v>
@@ -11186,7 +11186,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H373" t="n">
         <v>1893</v>
@@ -11273,7 +11273,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H376" t="n">
         <v>19650</v>
@@ -11302,7 +11302,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H377" t="n">
         <v>1925</v>
@@ -11331,7 +11331,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H378" t="n">
         <v>4890</v>
@@ -11360,7 +11360,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H379" t="n">
         <v>1750</v>
@@ -11389,7 +11389,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H380" t="n">
         <v>2479</v>
@@ -11418,7 +11418,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H381" t="n">
         <v>955</v>
@@ -11476,7 +11476,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H383" t="n">
         <v>500</v>
@@ -11505,7 +11505,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H384" t="n">
         <v>1430</v>
@@ -11534,7 +11534,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H385" t="n">
         <v>1674</v>
@@ -11563,7 +11563,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G386" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H386" t="n">
         <v>802</v>
@@ -11708,7 +11708,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H391" t="n">
         <v>4396</v>
@@ -11737,7 +11737,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G392" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H392" t="n">
         <v>1080</v>
@@ -11940,7 +11940,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H399" t="n">
         <v>4059</v>
@@ -11969,7 +11969,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H401" t="n">
         <v>2000</v>
@@ -12114,7 +12114,7 @@
         <v>10</v>
       </c>
       <c r="G405" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H405" t="n">
         <v>6672</v>
@@ -12172,7 +12172,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G407" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H407" t="n">
         <v>9607</v>
@@ -12201,7 +12201,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H408" t="n">
         <v>1750</v>
@@ -12230,7 +12230,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G409" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H409" t="n">
         <v>6250</v>
@@ -12259,7 +12259,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G410" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H410" t="n">
         <v>1015</v>
@@ -12288,7 +12288,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G411" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H411" t="n">
         <v>1334</v>
@@ -12317,7 +12317,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H412" t="n">
         <v>1176</v>
@@ -12346,7 +12346,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H413" t="n">
         <v>1223</v>
@@ -12375,7 +12375,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H414" t="n">
         <v>225</v>
@@ -12433,7 +12433,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>8.21835613250732</v>
+        <v>8.21835708618164</v>
       </c>
       <c r="H416" t="n">
         <v>4708</v>
@@ -12462,7 +12462,7 @@
         <v>9.75</v>
       </c>
       <c r="G417" t="n">
-        <v>8.34676837921143</v>
+        <v>8.34676742553711</v>
       </c>
       <c r="H417" t="n">
         <v>5344</v>
@@ -12491,7 +12491,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H418" t="n">
         <v>4587</v>
@@ -12520,7 +12520,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H419" t="n">
         <v>3997</v>
@@ -12549,7 +12549,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>8.90321826934814</v>
+        <v>8.90321731567383</v>
       </c>
       <c r="H420" t="n">
         <v>20523</v>
@@ -12578,7 +12578,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>8.90321826934814</v>
+        <v>8.90321731567383</v>
       </c>
       <c r="H421" t="n">
         <v>7784</v>
@@ -12607,7 +12607,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G422" t="n">
-        <v>8.81761169433594</v>
+        <v>8.81761074066162</v>
       </c>
       <c r="H422" t="n">
         <v>5583</v>
@@ -12694,7 +12694,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H425" t="n">
         <v>3177</v>
@@ -12723,7 +12723,7 @@
         <v>10</v>
       </c>
       <c r="G426" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H426" t="n">
         <v>4148</v>
@@ -12752,7 +12752,7 @@
         <v>10.5</v>
       </c>
       <c r="G427" t="n">
-        <v>8.98882579803467</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H427" t="n">
         <v>14779</v>
@@ -12781,7 +12781,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90321826934814</v>
+        <v>8.90321731567383</v>
       </c>
       <c r="H428" t="n">
         <v>7048</v>
@@ -12810,7 +12810,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.98882579803467</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H429" t="n">
         <v>39883</v>
@@ -13042,7 +13042,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>8.90321826934814</v>
+        <v>8.90321731567383</v>
       </c>
       <c r="H437" t="n">
         <v>4532</v>
@@ -13071,7 +13071,7 @@
         <v>10</v>
       </c>
       <c r="G438" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H438" t="n">
         <v>11185</v>
@@ -13100,7 +13100,7 @@
         <v>10</v>
       </c>
       <c r="G439" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H439" t="n">
         <v>15109</v>
@@ -13129,7 +13129,7 @@
         <v>10</v>
       </c>
       <c r="G440" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H440" t="n">
         <v>6043</v>
@@ -13187,7 +13187,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H442" t="n">
         <v>90803</v>
@@ -13216,7 +13216,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H443" t="n">
         <v>7339</v>
@@ -13245,7 +13245,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G444" t="n">
-        <v>8.54366588592529</v>
+        <v>8.54366493225098</v>
       </c>
       <c r="H444" t="n">
         <v>5918</v>
@@ -13274,7 +13274,7 @@
         <v>10</v>
       </c>
       <c r="G445" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H445" t="n">
         <v>9128</v>
@@ -13303,7 +13303,7 @@
         <v>10</v>
       </c>
       <c r="G446" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H446" t="n">
         <v>7831</v>
@@ -13361,7 +13361,7 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H448" t="n">
         <v>4670</v>
@@ -13419,7 +13419,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.8604154586792</v>
+        <v>8.86041450500488</v>
       </c>
       <c r="H450" t="n">
         <v>18892</v>
@@ -13448,7 +13448,7 @@
         <v>10.5</v>
       </c>
       <c r="G451" t="n">
-        <v>8.98882579803467</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H451" t="n">
         <v>20478</v>
@@ -13477,7 +13477,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>9.28845500946045</v>
+        <v>9.28845405578613</v>
       </c>
       <c r="H452" t="n">
         <v>71285</v>
@@ -13564,7 +13564,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>9.14202404022217</v>
+        <v>9.14202308654785</v>
       </c>
       <c r="H455" t="n">
         <v>31996</v>
@@ -13767,7 +13767,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H462" t="n">
         <v>2003</v>
@@ -13854,7 +13854,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H465" t="n">
         <v>14331</v>
@@ -13883,7 +13883,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H466" t="n">
         <v>15525</v>
@@ -13912,7 +13912,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H467" t="n">
         <v>4027</v>
@@ -14173,7 +14173,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H476" t="n">
         <v>4298</v>
@@ -14202,7 +14202,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H477" t="n">
         <v>8570</v>
@@ -14231,7 +14231,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H478" t="n">
         <v>208</v>
@@ -14260,7 +14260,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H479" t="n">
         <v>1263</v>
@@ -14318,7 +14318,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H481" t="n">
         <v>1124</v>
@@ -14463,7 +14463,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H486" t="n">
         <v>1373</v>
@@ -14579,7 +14579,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H490" t="n">
         <v>758</v>
@@ -14666,7 +14666,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H493" t="n">
         <v>524</v>
@@ -14695,7 +14695,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H494" t="n">
         <v>3075</v>
@@ -14869,7 +14869,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H500" t="n">
         <v>4578</v>
@@ -15362,7 +15362,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H517" t="n">
         <v>542</v>
@@ -15449,7 +15449,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G520" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H520" t="n">
         <v>1778</v>
@@ -15884,7 +15884,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H535" t="n">
         <v>2389</v>
@@ -15913,7 +15913,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G536" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H536" t="n">
         <v>150</v>
@@ -16087,7 +16087,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H542" t="n">
         <v>1350</v>
@@ -16232,7 +16232,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G547" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H547" t="n">
         <v>5100</v>
@@ -16348,7 +16348,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H551" t="n">
         <v>2999</v>
@@ -16377,7 +16377,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H552" t="n">
         <v>155</v>
@@ -16406,7 +16406,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H553" t="n">
         <v>128</v>
@@ -16435,7 +16435,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H554" t="n">
         <v>208</v>
@@ -16464,7 +16464,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H555" t="n">
         <v>1378</v>
@@ -16493,7 +16493,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H556" t="n">
         <v>9590</v>
@@ -16522,7 +16522,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H557" t="n">
         <v>2253</v>
@@ -16609,7 +16609,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H560" t="n">
         <v>575</v>
@@ -16899,7 +16899,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H570" t="n">
         <v>560</v>
@@ -16928,7 +16928,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H571" t="n">
         <v>390</v>
@@ -17189,7 +17189,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H580" t="n">
         <v>2025</v>
@@ -17276,7 +17276,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H583" t="n">
         <v>373</v>
@@ -17363,7 +17363,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G586" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H586" t="n">
         <v>237736</v>
@@ -17392,7 +17392,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H587" t="n">
         <v>4477</v>
@@ -17624,7 +17624,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G595" t="n">
-        <v>10.6807804107666</v>
+        <v>10.6807794570923</v>
       </c>
       <c r="H595" t="n">
         <v>972</v>
@@ -17653,7 +17653,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G596" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H596" t="n">
         <v>2317</v>
@@ -17682,7 +17682,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H597" t="n">
         <v>4064</v>
@@ -17914,7 +17914,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H605" t="n">
         <v>7786</v>
@@ -17943,7 +17943,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H606" t="n">
         <v>5869</v>
@@ -17972,7 +17972,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H607" t="n">
         <v>3504</v>
@@ -18001,7 +18001,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H608" t="n">
         <v>650</v>
@@ -18030,7 +18030,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H609" t="n">
         <v>2810</v>
@@ -18059,7 +18059,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H610" t="n">
         <v>2274</v>
@@ -18088,7 +18088,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H611" t="n">
         <v>530</v>
@@ -18117,7 +18117,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>10.4544925689697</v>
+        <v>10.4544916152954</v>
       </c>
       <c r="H612" t="n">
         <v>1300</v>
@@ -18204,7 +18204,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>10.4544925689697</v>
+        <v>10.4544916152954</v>
       </c>
       <c r="H615" t="n">
         <v>6497</v>
@@ -18233,7 +18233,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H616" t="n">
         <v>954</v>
@@ -18262,7 +18262,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H617" t="n">
         <v>668</v>
@@ -18291,7 +18291,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H618" t="n">
         <v>458</v>
@@ -18349,7 +18349,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>11.495415687561</v>
+        <v>11.4954147338867</v>
       </c>
       <c r="H620" t="n">
         <v>18194</v>
@@ -18378,7 +18378,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H621" t="n">
         <v>3478</v>
@@ -18407,7 +18407,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H622" t="n">
         <v>1875</v>
@@ -18494,7 +18494,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H625" t="n">
         <v>550</v>
@@ -18610,7 +18610,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H629" t="n">
         <v>849</v>
@@ -18639,7 +18639,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H630" t="n">
         <v>1274</v>
@@ -18668,7 +18668,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>11.133355140686</v>
+        <v>11.1333560943604</v>
       </c>
       <c r="H631" t="n">
         <v>50</v>
@@ -18697,7 +18697,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H632" t="n">
         <v>919</v>
@@ -18726,7 +18726,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H633" t="n">
         <v>630</v>
@@ -18755,7 +18755,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H634" t="n">
         <v>529</v>
@@ -18784,7 +18784,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H635" t="n">
         <v>2833</v>
@@ -18900,7 +18900,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H639" t="n">
         <v>7525</v>
@@ -18929,7 +18929,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H640" t="n">
         <v>5598</v>
@@ -19016,7 +19016,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H643" t="n">
         <v>1624</v>
@@ -19074,7 +19074,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H645" t="n">
         <v>8997</v>
@@ -19103,7 +19103,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H646" t="n">
         <v>1298</v>
@@ -19132,7 +19132,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H647" t="n">
         <v>1027</v>
@@ -19161,7 +19161,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G648" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H648" t="n">
         <v>2656</v>
@@ -19248,7 +19248,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H651" t="n">
         <v>2853</v>
@@ -19277,7 +19277,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H652" t="n">
         <v>201</v>
@@ -19306,7 +19306,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H653" t="n">
         <v>2152</v>
@@ -19364,7 +19364,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G655" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H655" t="n">
         <v>1923</v>
@@ -19393,7 +19393,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H656" t="n">
         <v>3358</v>
@@ -19422,7 +19422,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H657" t="n">
         <v>2271</v>
@@ -19451,7 +19451,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H658" t="n">
         <v>3130</v>
@@ -19480,7 +19480,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H659" t="n">
         <v>1473</v>
@@ -19509,7 +19509,7 @@
         <v>12.75</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H660" t="n">
         <v>6035</v>
@@ -19538,7 +19538,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H661" t="n">
         <v>51639</v>
@@ -19654,7 +19654,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H665" t="n">
         <v>655</v>
@@ -19683,7 +19683,7 @@
         <v>12.75</v>
       </c>
       <c r="G666" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H666" t="n">
         <v>3045</v>
@@ -19712,7 +19712,7 @@
         <v>12.75</v>
       </c>
       <c r="G667" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H667" t="n">
         <v>2279</v>
@@ -19886,7 +19886,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G673" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H673" t="n">
         <v>17329</v>
@@ -19915,7 +19915,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H674" t="n">
         <v>6333</v>
@@ -19944,7 +19944,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>12.8078842163086</v>
+        <v>12.8078832626343</v>
       </c>
       <c r="H675" t="n">
         <v>6880</v>
@@ -20089,7 +20089,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>13.4867477416992</v>
+        <v>13.4867467880249</v>
       </c>
       <c r="H680" t="n">
         <v>11651</v>
@@ -20147,7 +20147,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>12.8531408309937</v>
+        <v>12.853141784668</v>
       </c>
       <c r="H682" t="n">
         <v>7422</v>
@@ -20176,7 +20176,7 @@
         <v>14</v>
       </c>
       <c r="G683" t="n">
-        <v>12.6721115112305</v>
+        <v>12.6721124649048</v>
       </c>
       <c r="H683" t="n">
         <v>6279</v>
@@ -20205,7 +20205,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>12.8531408309937</v>
+        <v>12.853141784668</v>
       </c>
       <c r="H684" t="n">
         <v>7438</v>
@@ -20321,7 +20321,7 @@
         <v>15</v>
       </c>
       <c r="G688" t="n">
-        <v>13.5772619247437</v>
+        <v>13.577262878418</v>
       </c>
       <c r="H688" t="n">
         <v>15723</v>
@@ -20437,7 +20437,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>14.5729293823242</v>
+        <v>14.5729284286499</v>
       </c>
       <c r="H692" t="n">
         <v>25981</v>
@@ -20669,7 +20669,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>14.1203536987305</v>
+        <v>14.1203527450562</v>
       </c>
       <c r="H700" t="n">
         <v>6735</v>
@@ -20727,7 +20727,7 @@
         <v>15.5</v>
       </c>
       <c r="G702" t="n">
-        <v>14.0298385620117</v>
+        <v>14.0298376083374</v>
       </c>
       <c r="H702" t="n">
         <v>16297</v>
@@ -20756,7 +20756,7 @@
         <v>15.5</v>
       </c>
       <c r="G703" t="n">
-        <v>14.0298385620117</v>
+        <v>14.0298376083374</v>
       </c>
       <c r="H703" t="n">
         <v>6474</v>
@@ -32072,6 +32072,35 @@
         <v>60801</v>
       </c>
       <c r="I1093" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1094" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>17.1000003814697</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>17.1000003814697</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>19174</v>
+      </c>
+      <c r="I1094" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H2" t="n">
         <v>1480</v>
@@ -456,7 +456,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G3" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H3" t="n">
         <v>2424</v>
@@ -485,7 +485,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H4" t="n">
         <v>1025</v>
@@ -514,7 +514,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H5" t="n">
         <v>2179</v>
@@ -543,7 +543,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H6" t="n">
         <v>1022</v>
@@ -601,7 +601,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G8" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H8" t="n">
         <v>6867</v>
@@ -630,7 +630,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H9" t="n">
         <v>1638</v>
@@ -659,7 +659,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H10" t="n">
         <v>2500</v>
@@ -688,7 +688,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G11" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H11" t="n">
         <v>827</v>
@@ -717,7 +717,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G12" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H12" t="n">
         <v>6225</v>
@@ -746,7 +746,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G13" t="n">
-        <v>5.86392831802368</v>
+        <v>5.86392879486084</v>
       </c>
       <c r="H13" t="n">
         <v>217</v>
@@ -775,7 +775,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895448684692</v>
       </c>
       <c r="H14" t="n">
         <v>22</v>
@@ -804,7 +804,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H15" t="n">
         <v>216</v>
@@ -920,7 +920,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H19" t="n">
         <v>137</v>
@@ -978,7 +978,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G21" t="n">
-        <v>5.83956336975098</v>
+        <v>5.83956289291382</v>
       </c>
       <c r="H21" t="n">
         <v>1450</v>
@@ -1007,7 +1007,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H22" t="n">
         <v>66</v>
@@ -1065,7 +1065,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H24" t="n">
         <v>6743</v>
@@ -1094,7 +1094,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H25" t="n">
         <v>308</v>
@@ -1123,7 +1123,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H26" t="n">
         <v>1045</v>
@@ -1152,7 +1152,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G27" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H27" t="n">
         <v>20931</v>
@@ -1181,7 +1181,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H28" t="n">
         <v>15424</v>
@@ -1210,7 +1210,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H29" t="n">
         <v>8815</v>
@@ -1239,7 +1239,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1326,7 +1326,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>5.72585821151733</v>
+        <v>5.72585868835449</v>
       </c>
       <c r="H33" t="n">
         <v>420</v>
@@ -1355,7 +1355,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H34" t="n">
         <v>3359</v>
@@ -1413,7 +1413,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G36" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H36" t="n">
         <v>80</v>
@@ -1529,7 +1529,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H40" t="n">
         <v>310</v>
@@ -1558,7 +1558,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G41" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895448684692</v>
       </c>
       <c r="H41" t="n">
         <v>271</v>
@@ -1587,7 +1587,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G42" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H42" t="n">
         <v>4000</v>
@@ -1616,7 +1616,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H43" t="n">
         <v>1983</v>
@@ -1645,7 +1645,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H46" t="n">
         <v>1100</v>
@@ -1732,7 +1732,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H47" t="n">
         <v>2065</v>
@@ -1761,7 +1761,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H48" t="n">
         <v>500</v>
@@ -1906,7 +1906,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G53" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H53" t="n">
         <v>500</v>
@@ -1993,7 +1993,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H56" t="n">
         <v>1500</v>
@@ -2051,7 +2051,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64464092254639</v>
+        <v>5.64463996887207</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -2080,7 +2080,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>5.72585821151733</v>
+        <v>5.72585868835449</v>
       </c>
       <c r="H59" t="n">
         <v>150</v>
@@ -2109,7 +2109,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>5.72585821151733</v>
+        <v>5.72585868835449</v>
       </c>
       <c r="H60" t="n">
         <v>278</v>
@@ -2138,7 +2138,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>5.72585821151733</v>
+        <v>5.72585868835449</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G62" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H62" t="n">
         <v>1100</v>
@@ -2196,7 +2196,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H63" t="n">
         <v>2557</v>
@@ -2225,7 +2225,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H67" t="n">
         <v>897</v>
@@ -2341,7 +2341,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G68" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H68" t="n">
         <v>11</v>
@@ -2370,7 +2370,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G70" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G72" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H72" t="n">
         <v>450</v>
@@ -2486,7 +2486,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H73" t="n">
         <v>1650</v>
@@ -2515,7 +2515,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G74" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H75" t="n">
         <v>170</v>
@@ -2573,7 +2573,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G79" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H79" t="n">
         <v>125</v>
@@ -2689,7 +2689,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H80" t="n">
         <v>500</v>
@@ -2718,7 +2718,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G81" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H81" t="n">
         <v>10765</v>
@@ -2776,7 +2776,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H83" t="n">
         <v>3017</v>
@@ -2805,7 +2805,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G84" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G91" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H91" t="n">
         <v>16459</v>
@@ -3037,7 +3037,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>5.86392831802368</v>
+        <v>5.86392879486084</v>
       </c>
       <c r="H92" t="n">
         <v>800</v>
@@ -3182,7 +3182,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H97" t="n">
         <v>351</v>
@@ -3298,7 +3298,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H101" t="n">
         <v>350</v>
@@ -3327,7 +3327,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G102" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H102" t="n">
         <v>1756</v>
@@ -3356,7 +3356,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H103" t="n">
         <v>8600</v>
@@ -3385,7 +3385,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G104" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H104" t="n">
         <v>19209</v>
@@ -3414,7 +3414,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G105" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H105" t="n">
         <v>1750</v>
@@ -3530,7 +3530,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H109" t="n">
         <v>250</v>
@@ -3559,7 +3559,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H110" t="n">
         <v>3650</v>
@@ -3588,7 +3588,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H111" t="n">
         <v>35917</v>
@@ -3617,7 +3617,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H112" t="n">
         <v>15359</v>
@@ -3646,7 +3646,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G114" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H114" t="n">
         <v>1000</v>
@@ -3704,7 +3704,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H115" t="n">
         <v>65929</v>
@@ -3733,7 +3733,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G116" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895448684692</v>
       </c>
       <c r="H116" t="n">
         <v>1167</v>
@@ -3762,7 +3762,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H117" t="n">
         <v>134765</v>
@@ -3791,7 +3791,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H122" t="n">
         <v>5</v>
@@ -4023,7 +4023,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G126" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H126" t="n">
         <v>3450</v>
@@ -4052,7 +4052,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H127" t="n">
         <v>6918</v>
@@ -4081,7 +4081,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G128" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H128" t="n">
         <v>214</v>
@@ -4110,7 +4110,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H129" t="n">
         <v>3454</v>
@@ -4139,7 +4139,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895448684692</v>
       </c>
       <c r="H130" t="n">
         <v>4648</v>
@@ -4197,7 +4197,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>5.79895353317261</v>
+        <v>5.79895448684692</v>
       </c>
       <c r="H132" t="n">
         <v>1700</v>
@@ -4255,7 +4255,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>5.71773624420166</v>
+        <v>5.71773672103882</v>
       </c>
       <c r="H134" t="n">
         <v>9200</v>
@@ -4342,7 +4342,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H137" t="n">
         <v>1286</v>
@@ -4371,7 +4371,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>5.7502236366272</v>
+        <v>5.75022315979004</v>
       </c>
       <c r="H138" t="n">
         <v>7627</v>
@@ -4748,7 +4748,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H151" t="n">
         <v>1390</v>
@@ -4777,7 +4777,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H152" t="n">
         <v>10236</v>
@@ -4806,7 +4806,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H153" t="n">
         <v>14392</v>
@@ -4835,7 +4835,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G154" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H154" t="n">
         <v>1564</v>
@@ -4864,7 +4864,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>5.84768486022949</v>
+        <v>5.84768438339233</v>
       </c>
       <c r="H155" t="n">
         <v>23103</v>
@@ -4951,7 +4951,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H158" t="n">
         <v>10088</v>
@@ -5038,7 +5038,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H161" t="n">
         <v>2050</v>
@@ -5067,7 +5067,7 @@
         <v>7.5</v>
       </c>
       <c r="G162" t="n">
-        <v>6.09133863449097</v>
+        <v>6.09133815765381</v>
       </c>
       <c r="H162" t="n">
         <v>81003</v>
@@ -5096,7 +5096,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>6.46494102478027</v>
+        <v>6.46494054794312</v>
       </c>
       <c r="H163" t="n">
         <v>157736</v>
@@ -5154,7 +5154,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>6.3999662399292</v>
+        <v>6.39996671676636</v>
       </c>
       <c r="H165" t="n">
         <v>10198</v>
@@ -5183,7 +5183,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G166" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H166" t="n">
         <v>5498</v>
@@ -5212,7 +5212,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>6.3999662399292</v>
+        <v>6.39996671676636</v>
       </c>
       <c r="H167" t="n">
         <v>7616</v>
@@ -5299,7 +5299,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G170" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H170" t="n">
         <v>3020</v>
@@ -5415,7 +5415,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>6.41620969772339</v>
+        <v>6.41621017456055</v>
       </c>
       <c r="H174" t="n">
         <v>550</v>
@@ -5444,7 +5444,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>6.41620969772339</v>
+        <v>6.41621017456055</v>
       </c>
       <c r="H175" t="n">
         <v>7100</v>
@@ -5473,7 +5473,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H176" t="n">
         <v>3660</v>
@@ -5502,7 +5502,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G177" t="n">
-        <v>6.20504379272461</v>
+        <v>6.20504331588745</v>
       </c>
       <c r="H177" t="n">
         <v>2825</v>
@@ -5531,7 +5531,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G178" t="n">
-        <v>6.3999662399292</v>
+        <v>6.39996671676636</v>
       </c>
       <c r="H178" t="n">
         <v>3628</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H179" t="n">
         <v>2200</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.33499240875244</v>
+        <v>6.33499193191528</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>6.52991533279419</v>
+        <v>6.52991485595703</v>
       </c>
       <c r="H185" t="n">
         <v>625</v>
@@ -5850,7 +5850,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483825683594</v>
+        <v>6.72483777999878</v>
       </c>
       <c r="H189" t="n">
         <v>12503</v>
@@ -5879,7 +5879,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64362049102783</v>
+        <v>6.64362001419067</v>
       </c>
       <c r="H190" t="n">
         <v>15454</v>
@@ -5937,7 +5937,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G192" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H192" t="n">
         <v>19653</v>
@@ -5966,7 +5966,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G193" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H193" t="n">
         <v>9223</v>
@@ -6691,7 +6691,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H218" t="n">
         <v>1060</v>
@@ -6720,7 +6720,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H219" t="n">
         <v>500</v>
@@ -6749,7 +6749,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H221" t="n">
         <v>10070</v>
@@ -6807,7 +6807,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H223" t="n">
         <v>1370</v>
@@ -6865,7 +6865,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H225" t="n">
         <v>474</v>
@@ -6923,7 +6923,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H229" t="n">
         <v>550</v>
@@ -7242,7 +7242,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180545806885</v>
+        <v>6.59180641174316</v>
       </c>
       <c r="H237" t="n">
         <v>5618</v>
@@ -7271,7 +7271,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H238" t="n">
         <v>425</v>
@@ -7329,7 +7329,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G240" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H240" t="n">
         <v>30</v>
@@ -7474,7 +7474,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H245" t="n">
         <v>720</v>
@@ -7503,7 +7503,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H249" t="n">
         <v>3130</v>
@@ -7735,7 +7735,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G254" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H254" t="n">
         <v>501</v>
@@ -7967,7 +7967,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H262" t="n">
         <v>1000</v>
@@ -7996,7 +7996,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>7.75</v>
       </c>
       <c r="G265" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H265" t="n">
         <v>10500</v>
@@ -8402,7 +8402,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H277" t="n">
         <v>972</v>
@@ -8779,7 +8779,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H290" t="n">
         <v>760</v>
@@ -8808,7 +8808,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H292" t="n">
         <v>15</v>
@@ -8866,7 +8866,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H293" t="n">
         <v>655</v>
@@ -9098,7 +9098,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H301" t="n">
         <v>350</v>
@@ -9156,7 +9156,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H303" t="n">
         <v>4525</v>
@@ -9185,7 +9185,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H304" t="n">
         <v>300</v>
@@ -9214,7 +9214,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G307" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H307" t="n">
         <v>300</v>
@@ -9301,7 +9301,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G308" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H308" t="n">
         <v>1000</v>
@@ -9330,7 +9330,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H309" t="n">
         <v>1104</v>
@@ -9388,7 +9388,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H311" t="n">
         <v>2460</v>
@@ -9417,7 +9417,7 @@
         <v>7.75</v>
       </c>
       <c r="G312" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H312" t="n">
         <v>3450</v>
@@ -9446,7 +9446,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G313" t="n">
-        <v>6.37778615951538</v>
+        <v>6.37778663635254</v>
       </c>
       <c r="H313" t="n">
         <v>12049</v>
@@ -9475,7 +9475,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>6.50619840621948</v>
+        <v>6.50619792938232</v>
       </c>
       <c r="H314" t="n">
         <v>10065</v>
@@ -9533,7 +9533,7 @@
         <v>7.75</v>
       </c>
       <c r="G316" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H316" t="n">
         <v>3144</v>
@@ -9562,7 +9562,7 @@
         <v>7.75</v>
       </c>
       <c r="G317" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H317" t="n">
         <v>3850</v>
@@ -9591,7 +9591,7 @@
         <v>7.75</v>
       </c>
       <c r="G318" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>7.75</v>
       </c>
       <c r="G319" t="n">
-        <v>6.63460969924927</v>
+        <v>6.63461017608643</v>
       </c>
       <c r="H319" t="n">
         <v>1200</v>
@@ -9649,7 +9649,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H320" t="n">
         <v>1420013</v>
@@ -9678,7 +9678,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302146911621</v>
       </c>
       <c r="H321" t="n">
         <v>17270</v>
@@ -9765,7 +9765,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G324" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H324" t="n">
         <v>7290</v>
@@ -9852,7 +9852,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G327" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H327" t="n">
         <v>10572</v>
@@ -9910,7 +9910,7 @@
         <v>8.5</v>
       </c>
       <c r="G329" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H329" t="n">
         <v>4383</v>
@@ -9997,7 +9997,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>7.1482572555542</v>
+        <v>7.14825773239136</v>
       </c>
       <c r="H332" t="n">
         <v>11892</v>
@@ -10026,7 +10026,7 @@
         <v>8.25</v>
       </c>
       <c r="G333" t="n">
-        <v>7.06264972686768</v>
+        <v>7.06264925003052</v>
       </c>
       <c r="H333" t="n">
         <v>2000</v>
@@ -10142,7 +10142,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G337" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H337" t="n">
         <v>19514</v>
@@ -10171,7 +10171,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H339" t="n">
         <v>50</v>
@@ -10229,7 +10229,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H340" t="n">
         <v>850</v>
@@ -10287,7 +10287,7 @@
         <v>8.25</v>
       </c>
       <c r="G342" t="n">
-        <v>7.06264972686768</v>
+        <v>7.06264925003052</v>
       </c>
       <c r="H342" t="n">
         <v>250</v>
@@ -10316,7 +10316,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H343" t="n">
         <v>1537</v>
@@ -10345,7 +10345,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>7.01984548568726</v>
+        <v>7.0198450088501</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G349" t="n">
-        <v>7.36227750778198</v>
+        <v>7.36227703094482</v>
       </c>
       <c r="H349" t="n">
         <v>18029</v>
@@ -10519,7 +10519,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G350" t="n">
-        <v>7.36227750778198</v>
+        <v>7.36227703094482</v>
       </c>
       <c r="H350" t="n">
         <v>4020</v>
@@ -10548,7 +10548,7 @@
         <v>8.5</v>
       </c>
       <c r="G351" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H351" t="n">
         <v>441</v>
@@ -10577,7 +10577,7 @@
         <v>8.5</v>
       </c>
       <c r="G352" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>8.5</v>
       </c>
       <c r="G353" t="n">
-        <v>7.2766695022583</v>
+        <v>7.27666902542114</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>7.44788408279419</v>
+        <v>7.44788455963135</v>
       </c>
       <c r="H354" t="n">
         <v>990</v>
@@ -10664,7 +10664,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>7.44788408279419</v>
+        <v>7.44788455963135</v>
       </c>
       <c r="H355" t="n">
         <v>2665</v>
@@ -10693,7 +10693,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>7.53349256515503</v>
+        <v>7.53349304199219</v>
       </c>
       <c r="H356" t="n">
         <v>24746</v>
@@ -10722,7 +10722,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>7.79031610488892</v>
+        <v>7.79031658172607</v>
       </c>
       <c r="H357" t="n">
         <v>4994</v>
@@ -10780,7 +10780,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83312034606934</v>
+        <v>7.83311986923218</v>
       </c>
       <c r="H359" t="n">
         <v>11764</v>
@@ -10867,7 +10867,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H362" t="n">
         <v>13708</v>
@@ -11186,7 +11186,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H373" t="n">
         <v>1893</v>
@@ -11273,7 +11273,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H376" t="n">
         <v>19650</v>
@@ -11302,7 +11302,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H377" t="n">
         <v>1925</v>
@@ -11331,7 +11331,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H378" t="n">
         <v>4890</v>
@@ -11360,7 +11360,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H379" t="n">
         <v>1750</v>
@@ -11389,7 +11389,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H380" t="n">
         <v>2479</v>
@@ -11418,7 +11418,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H381" t="n">
         <v>955</v>
@@ -11447,7 +11447,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G382" t="n">
-        <v>8.0043363571167</v>
+        <v>8.00433731079102</v>
       </c>
       <c r="H382" t="n">
         <v>62</v>
@@ -11476,7 +11476,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H383" t="n">
         <v>500</v>
@@ -11505,7 +11505,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153259277344</v>
+        <v>7.96153163909912</v>
       </c>
       <c r="H384" t="n">
         <v>1430</v>
@@ -11534,7 +11534,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H385" t="n">
         <v>1674</v>
@@ -11563,7 +11563,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G386" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H386" t="n">
         <v>802</v>
@@ -11708,7 +11708,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H391" t="n">
         <v>4396</v>
@@ -11737,7 +11737,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G392" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H392" t="n">
         <v>1080</v>
@@ -11940,7 +11940,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H399" t="n">
         <v>4059</v>
@@ -11969,7 +11969,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.13274765014648</v>
+        <v>8.1327486038208</v>
       </c>
       <c r="H401" t="n">
         <v>2000</v>
@@ -12172,7 +12172,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G407" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H407" t="n">
         <v>9607</v>
@@ -12201,7 +12201,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H408" t="n">
         <v>1750</v>
@@ -12230,7 +12230,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G409" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H409" t="n">
         <v>6250</v>
@@ -12259,7 +12259,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G410" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H410" t="n">
         <v>1015</v>
@@ -12288,7 +12288,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G411" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H411" t="n">
         <v>1334</v>
@@ -12317,7 +12317,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H412" t="n">
         <v>1176</v>
@@ -12346,7 +12346,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H413" t="n">
         <v>1223</v>
@@ -12375,7 +12375,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>8.26115989685059</v>
+        <v>8.26115894317627</v>
       </c>
       <c r="H414" t="n">
         <v>225</v>
@@ -12433,7 +12433,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>8.21835708618164</v>
+        <v>8.21835613250732</v>
       </c>
       <c r="H416" t="n">
         <v>4708</v>
@@ -12549,7 +12549,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H420" t="n">
         <v>20523</v>
@@ -12578,7 +12578,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H421" t="n">
         <v>7784</v>
@@ -12636,7 +12636,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>8.73200225830078</v>
+        <v>8.7320032119751</v>
       </c>
       <c r="H423" t="n">
         <v>22640</v>
@@ -12781,7 +12781,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H428" t="n">
         <v>7048</v>
@@ -12839,7 +12839,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H430" t="n">
         <v>16073</v>
@@ -12868,7 +12868,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H431" t="n">
         <v>3285</v>
@@ -12897,7 +12897,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H432" t="n">
         <v>8576</v>
@@ -13013,7 +13013,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>9.07443523406982</v>
+        <v>9.07443428039551</v>
       </c>
       <c r="H436" t="n">
         <v>11201</v>
@@ -13042,7 +13042,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>8.90321731567383</v>
+        <v>8.90321826934814</v>
       </c>
       <c r="H437" t="n">
         <v>4532</v>
@@ -13245,7 +13245,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G444" t="n">
-        <v>8.54366493225098</v>
+        <v>8.54366588592529</v>
       </c>
       <c r="H444" t="n">
         <v>5918</v>
@@ -13390,7 +13390,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G449" t="n">
-        <v>8.73200225830078</v>
+        <v>8.7320032119751</v>
       </c>
       <c r="H449" t="n">
         <v>6569</v>
@@ -13419,7 +13419,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.86041450500488</v>
+        <v>8.8604154586792</v>
       </c>
       <c r="H450" t="n">
         <v>18892</v>
@@ -13477,7 +13477,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>9.28845405578613</v>
+        <v>9.28845500946045</v>
       </c>
       <c r="H452" t="n">
         <v>71285</v>
@@ -13564,7 +13564,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>9.14202308654785</v>
+        <v>9.14202404022217</v>
       </c>
       <c r="H455" t="n">
         <v>31996</v>
@@ -13767,7 +13767,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H462" t="n">
         <v>2003</v>
@@ -13854,7 +13854,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H465" t="n">
         <v>14331</v>
@@ -13883,7 +13883,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H466" t="n">
         <v>15525</v>
@@ -13912,7 +13912,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H467" t="n">
         <v>4027</v>
@@ -14173,7 +14173,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H476" t="n">
         <v>4298</v>
@@ -14202,7 +14202,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H477" t="n">
         <v>8570</v>
@@ -14231,7 +14231,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H478" t="n">
         <v>208</v>
@@ -14260,7 +14260,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H479" t="n">
         <v>1263</v>
@@ -14318,7 +14318,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H481" t="n">
         <v>1124</v>
@@ -14463,7 +14463,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H486" t="n">
         <v>1373</v>
@@ -14579,7 +14579,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H490" t="n">
         <v>758</v>
@@ -14666,7 +14666,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H493" t="n">
         <v>524</v>
@@ -14695,7 +14695,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H494" t="n">
         <v>3075</v>
@@ -14869,7 +14869,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H500" t="n">
         <v>4578</v>
@@ -15362,7 +15362,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H517" t="n">
         <v>542</v>
@@ -15449,7 +15449,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G520" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H520" t="n">
         <v>1778</v>
@@ -15884,7 +15884,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H535" t="n">
         <v>2389</v>
@@ -15913,7 +15913,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G536" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H536" t="n">
         <v>150</v>
@@ -16087,7 +16087,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H542" t="n">
         <v>1350</v>
@@ -16232,7 +16232,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G547" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H547" t="n">
         <v>5100</v>
@@ -16348,7 +16348,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H551" t="n">
         <v>2999</v>
@@ -16377,7 +16377,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H552" t="n">
         <v>155</v>
@@ -16406,7 +16406,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H553" t="n">
         <v>128</v>
@@ -16435,7 +16435,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H554" t="n">
         <v>208</v>
@@ -16464,7 +16464,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H555" t="n">
         <v>1378</v>
@@ -16493,7 +16493,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H556" t="n">
         <v>9590</v>
@@ -16522,7 +16522,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H557" t="n">
         <v>2253</v>
@@ -16609,7 +16609,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H560" t="n">
         <v>575</v>
@@ -16899,7 +16899,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H570" t="n">
         <v>560</v>
@@ -16928,7 +16928,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>10.0924320220947</v>
+        <v>10.0924310684204</v>
       </c>
       <c r="H571" t="n">
         <v>390</v>
@@ -17189,7 +17189,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H580" t="n">
         <v>2025</v>
@@ -17276,7 +17276,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H583" t="n">
         <v>373</v>
@@ -17363,7 +17363,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G586" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H586" t="n">
         <v>237736</v>
@@ -17392,7 +17392,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H587" t="n">
         <v>4477</v>
@@ -17624,7 +17624,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G595" t="n">
-        <v>10.6807794570923</v>
+        <v>10.6807804107666</v>
       </c>
       <c r="H595" t="n">
         <v>972</v>
@@ -17653,7 +17653,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G596" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H596" t="n">
         <v>2317</v>
@@ -17682,7 +17682,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>9.82088661193848</v>
+        <v>9.82088756561279</v>
       </c>
       <c r="H597" t="n">
         <v>4064</v>
@@ -17914,7 +17914,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H605" t="n">
         <v>7786</v>
@@ -17943,7 +17943,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H606" t="n">
         <v>5869</v>
@@ -17972,7 +17972,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H607" t="n">
         <v>3504</v>
@@ -18001,7 +18001,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>9.91140174865723</v>
+        <v>9.91140079498291</v>
       </c>
       <c r="H608" t="n">
         <v>650</v>
@@ -18030,7 +18030,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H609" t="n">
         <v>2810</v>
@@ -18059,7 +18059,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>10.3639764785767</v>
+        <v>10.363977432251</v>
       </c>
       <c r="H610" t="n">
         <v>2274</v>
@@ -18088,7 +18088,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>10.2282047271729</v>
+        <v>10.2282037734985</v>
       </c>
       <c r="H611" t="n">
         <v>530</v>
@@ -18117,7 +18117,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>10.4544916152954</v>
+        <v>10.4544925689697</v>
       </c>
       <c r="H612" t="n">
         <v>1300</v>
@@ -18204,7 +18204,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>10.4544916152954</v>
+        <v>10.4544925689697</v>
       </c>
       <c r="H615" t="n">
         <v>6497</v>
@@ -18233,7 +18233,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H616" t="n">
         <v>954</v>
@@ -18262,7 +18262,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H617" t="n">
         <v>668</v>
@@ -18291,7 +18291,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>10.5450067520142</v>
+        <v>10.5450077056885</v>
       </c>
       <c r="H618" t="n">
         <v>458</v>
@@ -18349,7 +18349,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>11.4954147338867</v>
+        <v>11.495415687561</v>
       </c>
       <c r="H620" t="n">
         <v>18194</v>
@@ -18378,7 +18378,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H621" t="n">
         <v>3478</v>
@@ -18407,7 +18407,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H622" t="n">
         <v>1875</v>
@@ -18494,7 +18494,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H625" t="n">
         <v>550</v>
@@ -18610,7 +18610,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H629" t="n">
         <v>849</v>
@@ -18639,7 +18639,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H630" t="n">
         <v>1274</v>
@@ -18668,7 +18668,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>11.1333560943604</v>
+        <v>11.133355140686</v>
       </c>
       <c r="H631" t="n">
         <v>50</v>
@@ -18697,7 +18697,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H632" t="n">
         <v>919</v>
@@ -18726,7 +18726,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H633" t="n">
         <v>630</v>
@@ -18755,7 +18755,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H634" t="n">
         <v>529</v>
@@ -18784,7 +18784,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H635" t="n">
         <v>2833</v>
@@ -18900,7 +18900,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H639" t="n">
         <v>7525</v>
@@ -18929,7 +18929,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>11.4501581192017</v>
+        <v>11.4501571655273</v>
       </c>
       <c r="H640" t="n">
         <v>5598</v>
@@ -19016,7 +19016,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H643" t="n">
         <v>1624</v>
@@ -19074,7 +19074,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>11.1786136627197</v>
+        <v>11.1786127090454</v>
       </c>
       <c r="H645" t="n">
         <v>8997</v>
@@ -19103,7 +19103,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H646" t="n">
         <v>1298</v>
@@ -19132,7 +19132,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H647" t="n">
         <v>1027</v>
@@ -19161,7 +19161,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G648" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H648" t="n">
         <v>2656</v>
@@ -19248,7 +19248,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H651" t="n">
         <v>2853</v>
@@ -19277,7 +19277,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H652" t="n">
         <v>201</v>
@@ -19306,7 +19306,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H653" t="n">
         <v>2152</v>
@@ -19364,7 +19364,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G655" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H655" t="n">
         <v>1923</v>
@@ -19393,7 +19393,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H656" t="n">
         <v>3358</v>
@@ -19422,7 +19422,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H657" t="n">
         <v>2271</v>
@@ -19451,7 +19451,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H658" t="n">
         <v>3130</v>
@@ -19480,7 +19480,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>11.2691278457642</v>
+        <v>11.2691268920898</v>
       </c>
       <c r="H659" t="n">
         <v>1473</v>
@@ -19509,7 +19509,7 @@
         <v>12.75</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H660" t="n">
         <v>6035</v>
@@ -19538,7 +19538,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>11.3596439361572</v>
+        <v>11.3596429824829</v>
       </c>
       <c r="H661" t="n">
         <v>51639</v>
@@ -19654,7 +19654,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H665" t="n">
         <v>655</v>
@@ -19683,7 +19683,7 @@
         <v>12.75</v>
       </c>
       <c r="G666" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H666" t="n">
         <v>3045</v>
@@ -19712,7 +19712,7 @@
         <v>12.75</v>
       </c>
       <c r="G667" t="n">
-        <v>11.5406723022461</v>
+        <v>11.5406732559204</v>
       </c>
       <c r="H667" t="n">
         <v>2279</v>
@@ -19886,7 +19886,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G673" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H673" t="n">
         <v>17329</v>
@@ -19915,7 +19915,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>11.7217025756836</v>
+        <v>11.7217035293579</v>
       </c>
       <c r="H674" t="n">
         <v>6333</v>
@@ -19944,7 +19944,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>12.8078832626343</v>
+        <v>12.8078842163086</v>
       </c>
       <c r="H675" t="n">
         <v>6880</v>
@@ -20089,7 +20089,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>13.4867467880249</v>
+        <v>13.4867477416992</v>
       </c>
       <c r="H680" t="n">
         <v>11651</v>
@@ -20147,7 +20147,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>12.853141784668</v>
+        <v>12.8531408309937</v>
       </c>
       <c r="H682" t="n">
         <v>7422</v>
@@ -20176,7 +20176,7 @@
         <v>14</v>
       </c>
       <c r="G683" t="n">
-        <v>12.6721124649048</v>
+        <v>12.6721115112305</v>
       </c>
       <c r="H683" t="n">
         <v>6279</v>
@@ -20205,7 +20205,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>12.853141784668</v>
+        <v>12.8531408309937</v>
       </c>
       <c r="H684" t="n">
         <v>7438</v>
@@ -20321,7 +20321,7 @@
         <v>15</v>
       </c>
       <c r="G688" t="n">
-        <v>13.577262878418</v>
+        <v>13.5772619247437</v>
       </c>
       <c r="H688" t="n">
         <v>15723</v>
@@ -20437,7 +20437,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>14.5729284286499</v>
+        <v>14.5729293823242</v>
       </c>
       <c r="H692" t="n">
         <v>25981</v>
@@ -20669,7 +20669,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>14.1203527450562</v>
+        <v>14.1203536987305</v>
       </c>
       <c r="H700" t="n">
         <v>6735</v>
@@ -20727,7 +20727,7 @@
         <v>15.5</v>
       </c>
       <c r="G702" t="n">
-        <v>14.0298376083374</v>
+        <v>14.0298385620117</v>
       </c>
       <c r="H702" t="n">
         <v>16297</v>
@@ -20756,7 +20756,7 @@
         <v>15.5</v>
       </c>
       <c r="G703" t="n">
-        <v>14.0298376083374</v>
+        <v>14.0298385620117</v>
       </c>
       <c r="H703" t="n">
         <v>6474</v>
@@ -32101,6 +32101,35 @@
         <v>19174</v>
       </c>
       <c r="I1094" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1095" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>17.4500007629395</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>17.3500003814697</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>16539</v>
+      </c>
+      <c r="I1095" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H2" t="n">
         <v>1480</v>
@@ -456,7 +456,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G3" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H3" t="n">
         <v>2424</v>
@@ -485,7 +485,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H4" t="n">
         <v>1025</v>
@@ -514,7 +514,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H5" t="n">
         <v>2179</v>
@@ -543,7 +543,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H6" t="n">
         <v>1022</v>
@@ -572,7 +572,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H7" t="n">
         <v>10000</v>
@@ -601,7 +601,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G8" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H8" t="n">
         <v>6867</v>
@@ -630,7 +630,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G9" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H9" t="n">
         <v>1638</v>
@@ -659,7 +659,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H10" t="n">
         <v>2500</v>
@@ -688,7 +688,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G11" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H11" t="n">
         <v>827</v>
@@ -717,7 +717,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G12" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H12" t="n">
         <v>6225</v>
@@ -746,7 +746,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G13" t="n">
-        <v>5.86392879486084</v>
+        <v>5.86392831802368</v>
       </c>
       <c r="H13" t="n">
         <v>217</v>
@@ -775,7 +775,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H14" t="n">
         <v>22</v>
@@ -804,7 +804,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H15" t="n">
         <v>216</v>
@@ -862,7 +862,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H17" t="n">
         <v>1221</v>
@@ -891,7 +891,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H18" t="n">
         <v>22</v>
@@ -920,7 +920,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H19" t="n">
         <v>137</v>
@@ -949,7 +949,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G20" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H20" t="n">
         <v>1000</v>
@@ -1007,7 +1007,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G22" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H22" t="n">
         <v>66</v>
@@ -1036,7 +1036,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H23" t="n">
         <v>681</v>
@@ -1065,7 +1065,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H24" t="n">
         <v>6743</v>
@@ -1094,7 +1094,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H25" t="n">
         <v>308</v>
@@ -1123,7 +1123,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H26" t="n">
         <v>1045</v>
@@ -1152,7 +1152,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G27" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H27" t="n">
         <v>20931</v>
@@ -1181,7 +1181,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H28" t="n">
         <v>15424</v>
@@ -1210,7 +1210,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.87205076217651</v>
+        <v>5.87205028533936</v>
       </c>
       <c r="H29" t="n">
         <v>8815</v>
@@ -1239,7 +1239,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H32" t="n">
         <v>379</v>
@@ -1326,7 +1326,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>5.72585868835449</v>
+        <v>5.72585821151733</v>
       </c>
       <c r="H33" t="n">
         <v>420</v>
@@ -1355,7 +1355,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G34" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H34" t="n">
         <v>3359</v>
@@ -1384,7 +1384,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H35" t="n">
         <v>20</v>
@@ -1413,7 +1413,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G36" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H36" t="n">
         <v>80</v>
@@ -1442,7 +1442,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G37" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H37" t="n">
         <v>300</v>
@@ -1471,7 +1471,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H38" t="n">
         <v>2870</v>
@@ -1500,7 +1500,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G39" t="n">
-        <v>5.80707597732544</v>
+        <v>5.8070764541626</v>
       </c>
       <c r="H39" t="n">
         <v>169</v>
@@ -1529,7 +1529,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H40" t="n">
         <v>310</v>
@@ -1558,7 +1558,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G41" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H41" t="n">
         <v>271</v>
@@ -1587,7 +1587,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G42" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H42" t="n">
         <v>4000</v>
@@ -1616,7 +1616,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H43" t="n">
         <v>1983</v>
@@ -1645,7 +1645,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G45" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G46" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H46" t="n">
         <v>1100</v>
@@ -1732,7 +1732,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H47" t="n">
         <v>2065</v>
@@ -1761,7 +1761,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G48" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H48" t="n">
         <v>500</v>
@@ -1877,7 +1877,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H52" t="n">
         <v>11</v>
@@ -1906,7 +1906,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G53" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H53" t="n">
         <v>500</v>
@@ -1935,7 +1935,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G54" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H54" t="n">
         <v>6012</v>
@@ -1964,7 +1964,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H55" t="n">
         <v>3500</v>
@@ -1993,7 +1993,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H56" t="n">
         <v>1500</v>
@@ -2022,7 +2022,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>5.70149230957031</v>
+        <v>5.70149278640747</v>
       </c>
       <c r="H57" t="n">
         <v>650</v>
@@ -2051,7 +2051,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64463996887207</v>
+        <v>5.64463949203491</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -2080,7 +2080,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>5.72585868835449</v>
+        <v>5.72585821151733</v>
       </c>
       <c r="H59" t="n">
         <v>150</v>
@@ -2109,7 +2109,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>5.72585868835449</v>
+        <v>5.72585821151733</v>
       </c>
       <c r="H60" t="n">
         <v>278</v>
@@ -2138,7 +2138,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>5.72585868835449</v>
+        <v>5.72585821151733</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G62" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H62" t="n">
         <v>1100</v>
@@ -2196,7 +2196,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H63" t="n">
         <v>2557</v>
@@ -2225,7 +2225,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H65" t="n">
         <v>1000</v>
@@ -2283,7 +2283,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>5.85580682754517</v>
+        <v>5.85580730438232</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H67" t="n">
         <v>897</v>
@@ -2341,7 +2341,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G68" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H68" t="n">
         <v>11</v>
@@ -2370,7 +2370,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G70" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G71" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G72" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H72" t="n">
         <v>450</v>
@@ -2486,7 +2486,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H73" t="n">
         <v>1650</v>
@@ -2515,7 +2515,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G74" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H75" t="n">
         <v>170</v>
@@ -2573,7 +2573,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G79" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H79" t="n">
         <v>125</v>
@@ -2689,7 +2689,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H80" t="n">
         <v>500</v>
@@ -2718,7 +2718,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G81" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H81" t="n">
         <v>10765</v>
@@ -2863,7 +2863,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H86" t="n">
         <v>750</v>
@@ -2892,7 +2892,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H87" t="n">
         <v>2590</v>
@@ -2921,7 +2921,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>5.89641571044922</v>
+        <v>5.89641618728638</v>
       </c>
       <c r="H88" t="n">
         <v>22052</v>
@@ -2950,7 +2950,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>5.88017177581787</v>
+        <v>5.88017225265503</v>
       </c>
       <c r="H89" t="n">
         <v>846</v>
@@ -2979,7 +2979,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G90" t="n">
-        <v>5.89641571044922</v>
+        <v>5.89641618728638</v>
       </c>
       <c r="H90" t="n">
         <v>5891</v>
@@ -3008,7 +3008,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G91" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H91" t="n">
         <v>16459</v>
@@ -3037,7 +3037,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>5.86392879486084</v>
+        <v>5.86392831802368</v>
       </c>
       <c r="H92" t="n">
         <v>800</v>
@@ -3066,7 +3066,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G93" t="n">
-        <v>5.88017177581787</v>
+        <v>5.88017225265503</v>
       </c>
       <c r="H93" t="n">
         <v>1382</v>
@@ -3095,7 +3095,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>5.88017177581787</v>
+        <v>5.88017225265503</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H95" t="n">
         <v>2618</v>
@@ -3153,7 +3153,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G97" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H97" t="n">
         <v>351</v>
@@ -3211,7 +3211,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H98" t="n">
         <v>481</v>
@@ -3240,7 +3240,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H99" t="n">
         <v>8</v>
@@ -3269,7 +3269,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H100" t="n">
         <v>186</v>
@@ -3298,7 +3298,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G101" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H101" t="n">
         <v>350</v>
@@ -3327,7 +3327,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G102" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H102" t="n">
         <v>1756</v>
@@ -3414,7 +3414,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G105" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H105" t="n">
         <v>1750</v>
@@ -3443,7 +3443,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H106" t="n">
         <v>145</v>
@@ -3472,7 +3472,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H107" t="n">
         <v>667</v>
@@ -3501,7 +3501,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H109" t="n">
         <v>250</v>
@@ -3559,7 +3559,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H110" t="n">
         <v>3650</v>
@@ -3588,7 +3588,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H111" t="n">
         <v>35917</v>
@@ -3617,7 +3617,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G112" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H112" t="n">
         <v>15359</v>
@@ -3646,7 +3646,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G114" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H114" t="n">
         <v>1000</v>
@@ -3704,7 +3704,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H115" t="n">
         <v>65929</v>
@@ -3733,7 +3733,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G116" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H116" t="n">
         <v>1167</v>
@@ -3762,7 +3762,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G117" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H117" t="n">
         <v>134765</v>
@@ -3791,7 +3791,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G120" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H120" t="n">
         <v>359</v>
@@ -3907,7 +3907,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G122" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H122" t="n">
         <v>5</v>
@@ -3936,7 +3936,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G123" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H123" t="n">
         <v>1400</v>
@@ -3965,7 +3965,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H124" t="n">
         <v>500</v>
@@ -3994,7 +3994,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G125" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H125" t="n">
         <v>3720</v>
@@ -4023,7 +4023,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G126" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H126" t="n">
         <v>3450</v>
@@ -4110,7 +4110,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H129" t="n">
         <v>3454</v>
@@ -4139,7 +4139,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H130" t="n">
         <v>4648</v>
@@ -4197,7 +4197,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>5.79895448684692</v>
+        <v>5.79895401000977</v>
       </c>
       <c r="H132" t="n">
         <v>1700</v>
@@ -4226,7 +4226,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H133" t="n">
         <v>14468</v>
@@ -4284,7 +4284,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>5.66900587081909</v>
+        <v>5.66900634765625</v>
       </c>
       <c r="H135" t="n">
         <v>15568</v>
@@ -4313,7 +4313,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>5.66900587081909</v>
+        <v>5.66900634765625</v>
       </c>
       <c r="H136" t="n">
         <v>14819</v>
@@ -4429,7 +4429,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H140" t="n">
         <v>2500</v>
@@ -4458,7 +4458,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H144" t="n">
         <v>80</v>
@@ -4603,7 +4603,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G146" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H146" t="n">
         <v>8497</v>
@@ -4632,7 +4632,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H147" t="n">
         <v>1510</v>
@@ -4661,7 +4661,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H148" t="n">
         <v>2120</v>
@@ -4690,7 +4690,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H150" t="n">
         <v>110</v>
@@ -4748,7 +4748,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H151" t="n">
         <v>1390</v>
@@ -4777,7 +4777,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H152" t="n">
         <v>10236</v>
@@ -4806,7 +4806,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G153" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H153" t="n">
         <v>14392</v>
@@ -4835,7 +4835,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G154" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H154" t="n">
         <v>1564</v>
@@ -4864,7 +4864,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>5.84768438339233</v>
+        <v>5.84768486022949</v>
       </c>
       <c r="H155" t="n">
         <v>23103</v>
@@ -4893,7 +4893,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G156" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H156" t="n">
         <v>3175</v>
@@ -4922,7 +4922,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G157" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H157" t="n">
         <v>10385</v>
@@ -4951,7 +4951,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H158" t="n">
         <v>10088</v>
@@ -4980,7 +4980,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>5.76646661758423</v>
+        <v>5.76646757125854</v>
       </c>
       <c r="H159" t="n">
         <v>2979</v>
@@ -5009,7 +5009,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H160" t="n">
         <v>4793</v>
@@ -5038,7 +5038,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H161" t="n">
         <v>2050</v>
@@ -5096,7 +5096,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>6.46494054794312</v>
+        <v>6.46494102478027</v>
       </c>
       <c r="H163" t="n">
         <v>157736</v>
@@ -5154,7 +5154,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H165" t="n">
         <v>10198</v>
@@ -5212,7 +5212,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H167" t="n">
         <v>7616</v>
@@ -5531,7 +5531,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G178" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H178" t="n">
         <v>3628</v>
@@ -5647,7 +5647,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H182" t="n">
         <v>3383</v>
@@ -5676,7 +5676,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G183" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H183" t="n">
         <v>559</v>
@@ -5821,7 +5821,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G188" t="n">
-        <v>6.57864618301392</v>
+        <v>6.57864570617676</v>
       </c>
       <c r="H188" t="n">
         <v>5815</v>
@@ -5879,7 +5879,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64362001419067</v>
+        <v>6.64362049102783</v>
       </c>
       <c r="H190" t="n">
         <v>15454</v>
@@ -5995,7 +5995,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G194" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H194" t="n">
         <v>11641</v>
@@ -6024,7 +6024,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G195" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H195" t="n">
         <v>5819</v>
@@ -6053,7 +6053,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G196" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H196" t="n">
         <v>4800</v>
@@ -6227,7 +6227,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H202" t="n">
         <v>1380</v>
@@ -6343,7 +6343,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H206" t="n">
         <v>250</v>
@@ -6488,7 +6488,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H211" t="n">
         <v>1850</v>
@@ -6517,7 +6517,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G212" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H212" t="n">
         <v>2457</v>
@@ -6662,7 +6662,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G217" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H217" t="n">
         <v>6686</v>
@@ -6691,7 +6691,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H218" t="n">
         <v>1060</v>
@@ -6720,7 +6720,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H219" t="n">
         <v>500</v>
@@ -6749,7 +6749,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H221" t="n">
         <v>10070</v>
@@ -6807,7 +6807,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H223" t="n">
         <v>1370</v>
@@ -6865,7 +6865,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H225" t="n">
         <v>474</v>
@@ -6923,7 +6923,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H229" t="n">
         <v>550</v>
@@ -7039,7 +7039,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H230" t="n">
         <v>1340</v>
@@ -7155,7 +7155,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H234" t="n">
         <v>800</v>
@@ -7184,7 +7184,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G236" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H236" t="n">
         <v>1250</v>
@@ -7271,7 +7271,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H238" t="n">
         <v>425</v>
@@ -7300,7 +7300,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H239" t="n">
         <v>10600</v>
@@ -7329,7 +7329,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G240" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H240" t="n">
         <v>30</v>
@@ -7358,7 +7358,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H241" t="n">
         <v>500</v>
@@ -7387,7 +7387,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H242" t="n">
         <v>200</v>
@@ -7416,7 +7416,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H243" t="n">
         <v>32675</v>
@@ -7445,7 +7445,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G244" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H245" t="n">
         <v>720</v>
@@ -7503,7 +7503,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H247" t="n">
         <v>5100</v>
@@ -7561,7 +7561,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H248" t="n">
         <v>5000</v>
@@ -7590,7 +7590,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H249" t="n">
         <v>3130</v>
@@ -7619,7 +7619,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H250" t="n">
         <v>1818</v>
@@ -7648,7 +7648,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H251" t="n">
         <v>4818</v>
@@ -7677,7 +7677,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H252" t="n">
         <v>1000</v>
@@ -7706,7 +7706,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H253" t="n">
         <v>3985</v>
@@ -7735,7 +7735,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G254" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H254" t="n">
         <v>501</v>
@@ -7909,7 +7909,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H260" t="n">
         <v>5</v>
@@ -7967,7 +7967,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H262" t="n">
         <v>1000</v>
@@ -7996,7 +7996,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H264" t="n">
         <v>5125</v>
@@ -8083,7 +8083,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G266" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H266" t="n">
         <v>3382</v>
@@ -8112,7 +8112,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H267" t="n">
         <v>1357</v>
@@ -8141,7 +8141,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H274" t="n">
         <v>250</v>
@@ -8344,7 +8344,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G276" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H276" t="n">
         <v>5210</v>
@@ -8402,7 +8402,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H277" t="n">
         <v>972</v>
@@ -8489,7 +8489,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>6.89143419265747</v>
+        <v>6.89143371582031</v>
       </c>
       <c r="H280" t="n">
         <v>1214</v>
@@ -8518,7 +8518,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G281" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H281" t="n">
         <v>286</v>
@@ -8779,7 +8779,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H290" t="n">
         <v>760</v>
@@ -8808,7 +8808,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H292" t="n">
         <v>15</v>
@@ -8866,7 +8866,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H293" t="n">
         <v>655</v>
@@ -9011,7 +9011,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G298" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H298" t="n">
         <v>1867</v>
@@ -9040,7 +9040,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H299" t="n">
         <v>1915</v>
@@ -9098,7 +9098,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H301" t="n">
         <v>350</v>
@@ -9156,7 +9156,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H303" t="n">
         <v>4525</v>
@@ -9185,7 +9185,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H304" t="n">
         <v>300</v>
@@ -9214,7 +9214,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G307" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H307" t="n">
         <v>300</v>
@@ -9301,7 +9301,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G308" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H308" t="n">
         <v>1000</v>
@@ -9330,7 +9330,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H309" t="n">
         <v>1104</v>
@@ -9388,7 +9388,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H311" t="n">
         <v>2460</v>
@@ -9504,7 +9504,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>6.67741441726685</v>
+        <v>6.67741394042969</v>
       </c>
       <c r="H315" t="n">
         <v>4634</v>
@@ -9649,7 +9649,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H320" t="n">
         <v>1420013</v>
@@ -9678,7 +9678,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>6.76302146911621</v>
+        <v>6.76302194595337</v>
       </c>
       <c r="H321" t="n">
         <v>17270</v>
@@ -9707,7 +9707,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>6.80582523345947</v>
+        <v>6.80582571029663</v>
       </c>
       <c r="H322" t="n">
         <v>1193</v>
@@ -9997,7 +9997,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>7.14825773239136</v>
+        <v>7.1482572555542</v>
       </c>
       <c r="H332" t="n">
         <v>11892</v>
@@ -10026,7 +10026,7 @@
         <v>8.25</v>
       </c>
       <c r="G333" t="n">
-        <v>7.06264925003052</v>
+        <v>7.06264972686768</v>
       </c>
       <c r="H333" t="n">
         <v>2000</v>
@@ -10287,7 +10287,7 @@
         <v>8.25</v>
       </c>
       <c r="G342" t="n">
-        <v>7.06264925003052</v>
+        <v>7.06264972686768</v>
       </c>
       <c r="H342" t="n">
         <v>250</v>
@@ -10490,7 +10490,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G349" t="n">
-        <v>7.36227703094482</v>
+        <v>7.36227750778198</v>
       </c>
       <c r="H349" t="n">
         <v>18029</v>
@@ -10519,7 +10519,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G350" t="n">
-        <v>7.36227703094482</v>
+        <v>7.36227750778198</v>
       </c>
       <c r="H350" t="n">
         <v>4020</v>
@@ -10780,7 +10780,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83311986923218</v>
+        <v>7.83312082290649</v>
       </c>
       <c r="H359" t="n">
         <v>11764</v>
@@ -10896,7 +10896,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H363" t="n">
         <v>19547</v>
@@ -10954,7 +10954,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H365" t="n">
         <v>6680</v>
@@ -10983,7 +10983,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G366" t="n">
-        <v>8.38957214355469</v>
+        <v>8.38957118988037</v>
       </c>
       <c r="H366" t="n">
         <v>4623</v>
@@ -11447,7 +11447,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G382" t="n">
-        <v>8.00433731079102</v>
+        <v>8.0043363571167</v>
       </c>
       <c r="H382" t="n">
         <v>62</v>
@@ -12114,7 +12114,7 @@
         <v>10</v>
       </c>
       <c r="G405" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H405" t="n">
         <v>6672</v>
@@ -12462,7 +12462,7 @@
         <v>9.75</v>
       </c>
       <c r="G417" t="n">
-        <v>8.34676742553711</v>
+        <v>8.34676837921143</v>
       </c>
       <c r="H417" t="n">
         <v>5344</v>
@@ -12491,7 +12491,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H418" t="n">
         <v>4587</v>
@@ -12520,7 +12520,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H419" t="n">
         <v>3997</v>
@@ -12607,7 +12607,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G422" t="n">
-        <v>8.81761074066162</v>
+        <v>8.81761169433594</v>
       </c>
       <c r="H422" t="n">
         <v>5583</v>
@@ -12636,7 +12636,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G423" t="n">
-        <v>8.7320032119751</v>
+        <v>8.73200225830078</v>
       </c>
       <c r="H423" t="n">
         <v>22640</v>
@@ -12694,7 +12694,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H425" t="n">
         <v>3177</v>
@@ -12723,7 +12723,7 @@
         <v>10</v>
       </c>
       <c r="G426" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H426" t="n">
         <v>4148</v>
@@ -12752,7 +12752,7 @@
         <v>10.5</v>
       </c>
       <c r="G427" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H427" t="n">
         <v>14779</v>
@@ -12810,7 +12810,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H429" t="n">
         <v>39883</v>
@@ -12839,7 +12839,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H430" t="n">
         <v>16073</v>
@@ -12868,7 +12868,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H431" t="n">
         <v>3285</v>
@@ -12897,7 +12897,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H432" t="n">
         <v>8576</v>
@@ -13013,7 +13013,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>9.07443428039551</v>
+        <v>9.07443523406982</v>
       </c>
       <c r="H436" t="n">
         <v>11201</v>
@@ -13071,7 +13071,7 @@
         <v>10</v>
       </c>
       <c r="G438" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H438" t="n">
         <v>11185</v>
@@ -13100,7 +13100,7 @@
         <v>10</v>
       </c>
       <c r="G439" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H439" t="n">
         <v>15109</v>
@@ -13129,7 +13129,7 @@
         <v>10</v>
       </c>
       <c r="G440" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H440" t="n">
         <v>6043</v>
@@ -13187,7 +13187,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H442" t="n">
         <v>90803</v>
@@ -13216,7 +13216,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>8.51798343658447</v>
+        <v>8.51798248291016</v>
       </c>
       <c r="H443" t="n">
         <v>7339</v>
@@ -13274,7 +13274,7 @@
         <v>10</v>
       </c>
       <c r="G445" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H445" t="n">
         <v>9128</v>
@@ -13303,7 +13303,7 @@
         <v>10</v>
       </c>
       <c r="G446" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H446" t="n">
         <v>7831</v>
@@ -13361,7 +13361,7 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>8.56078720092773</v>
+        <v>8.56078815460205</v>
       </c>
       <c r="H448" t="n">
         <v>4670</v>
@@ -13390,7 +13390,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G449" t="n">
-        <v>8.7320032119751</v>
+        <v>8.73200225830078</v>
       </c>
       <c r="H449" t="n">
         <v>6569</v>
@@ -13448,7 +13448,7 @@
         <v>10.5</v>
       </c>
       <c r="G451" t="n">
-        <v>8.98882675170898</v>
+        <v>8.98882579803467</v>
       </c>
       <c r="H451" t="n">
         <v>20478</v>
@@ -32130,6 +32130,35 @@
         <v>16539</v>
       </c>
       <c r="I1095" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1096" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>5379</v>
+      </c>
+      <c r="I1096" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -514,7 +514,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H5" t="n">
         <v>2179</v>
@@ -746,7 +746,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G13" t="n">
-        <v>5.86392831802368</v>
+        <v>5.86392879486084</v>
       </c>
       <c r="H13" t="n">
         <v>217</v>
@@ -833,7 +833,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>5.77458906173706</v>
+        <v>5.7745885848999</v>
       </c>
       <c r="H16" t="n">
         <v>4639</v>
@@ -891,7 +891,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H18" t="n">
         <v>22</v>
@@ -949,7 +949,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G20" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H20" t="n">
         <v>1000</v>
@@ -1094,7 +1094,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H25" t="n">
         <v>308</v>
@@ -1152,7 +1152,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G27" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H27" t="n">
         <v>20931</v>
@@ -1181,7 +1181,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G28" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H28" t="n">
         <v>15424</v>
@@ -1210,7 +1210,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.87205028533936</v>
+        <v>5.87205076217651</v>
       </c>
       <c r="H29" t="n">
         <v>8815</v>
@@ -1268,7 +1268,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G31" t="n">
-        <v>5.82331943511963</v>
+        <v>5.82331991195679</v>
       </c>
       <c r="H31" t="n">
         <v>2124</v>
@@ -1790,7 +1790,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.79083251953125</v>
+        <v>5.79083204269409</v>
       </c>
       <c r="H49" t="n">
         <v>628</v>
@@ -1819,7 +1819,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G50" t="n">
-        <v>5.79083251953125</v>
+        <v>5.79083204269409</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>5.79083251953125</v>
+        <v>5.79083204269409</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G54" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H54" t="n">
         <v>6012</v>
@@ -1964,7 +1964,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H55" t="n">
         <v>3500</v>
@@ -2051,7 +2051,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>5.64463949203491</v>
+        <v>5.64463996887207</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -2312,7 +2312,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H67" t="n">
         <v>897</v>
@@ -2486,7 +2486,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H73" t="n">
         <v>1650</v>
@@ -2515,7 +2515,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G74" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H75" t="n">
         <v>170</v>
@@ -2573,7 +2573,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H86" t="n">
         <v>750</v>
@@ -2892,7 +2892,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H87" t="n">
         <v>2590</v>
@@ -3037,7 +3037,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>5.86392831802368</v>
+        <v>5.86392879486084</v>
       </c>
       <c r="H92" t="n">
         <v>800</v>
@@ -3124,7 +3124,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H95" t="n">
         <v>2618</v>
@@ -3153,7 +3153,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G98" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H98" t="n">
         <v>481</v>
@@ -3240,7 +3240,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H99" t="n">
         <v>8</v>
@@ -3269,7 +3269,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G100" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H100" t="n">
         <v>186</v>
@@ -3443,7 +3443,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H106" t="n">
         <v>145</v>
@@ -3472,7 +3472,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H107" t="n">
         <v>667</v>
@@ -3501,7 +3501,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G108" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H115" t="n">
         <v>65929</v>
@@ -3849,7 +3849,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G120" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H120" t="n">
         <v>359</v>
@@ -3936,7 +3936,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G123" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H123" t="n">
         <v>1400</v>
@@ -3965,7 +3965,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H124" t="n">
         <v>500</v>
@@ -3994,7 +3994,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G125" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H125" t="n">
         <v>3720</v>
@@ -4110,7 +4110,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H129" t="n">
         <v>3454</v>
@@ -4226,7 +4226,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H133" t="n">
         <v>14468</v>
@@ -4255,7 +4255,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>5.71773672103882</v>
+        <v>5.71773624420166</v>
       </c>
       <c r="H134" t="n">
         <v>9200</v>
@@ -4284,7 +4284,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>5.66900634765625</v>
+        <v>5.66900587081909</v>
       </c>
       <c r="H135" t="n">
         <v>15568</v>
@@ -4313,7 +4313,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>5.66900634765625</v>
+        <v>5.66900587081909</v>
       </c>
       <c r="H136" t="n">
         <v>14819</v>
@@ -4429,7 +4429,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H140" t="n">
         <v>2500</v>
@@ -4458,7 +4458,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H144" t="n">
         <v>80</v>
@@ -4603,7 +4603,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G146" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H146" t="n">
         <v>8497</v>
@@ -4632,7 +4632,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H147" t="n">
         <v>1510</v>
@@ -4661,7 +4661,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H148" t="n">
         <v>2120</v>
@@ -4690,7 +4690,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H150" t="n">
         <v>110</v>
@@ -4777,7 +4777,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H152" t="n">
         <v>10236</v>
@@ -4893,7 +4893,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G156" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H156" t="n">
         <v>3175</v>
@@ -4922,7 +4922,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G157" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H157" t="n">
         <v>10385</v>
@@ -4951,7 +4951,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H158" t="n">
         <v>10088</v>
@@ -4980,7 +4980,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>5.76646757125854</v>
+        <v>5.76646709442139</v>
       </c>
       <c r="H159" t="n">
         <v>2979</v>
@@ -5009,7 +5009,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>5.83144092559814</v>
+        <v>5.8314414024353</v>
       </c>
       <c r="H160" t="n">
         <v>4793</v>
@@ -5038,7 +5038,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>5.81519746780396</v>
+        <v>5.81519794464111</v>
       </c>
       <c r="H161" t="n">
         <v>2050</v>
@@ -5154,7 +5154,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>6.3999662399292</v>
+        <v>6.39996671676636</v>
       </c>
       <c r="H165" t="n">
         <v>10198</v>
@@ -5212,7 +5212,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>6.3999662399292</v>
+        <v>6.39996671676636</v>
       </c>
       <c r="H167" t="n">
         <v>7616</v>
@@ -5531,7 +5531,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G178" t="n">
-        <v>6.3999662399292</v>
+        <v>6.39996671676636</v>
       </c>
       <c r="H178" t="n">
         <v>3628</v>
@@ -5763,7 +5763,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G186" t="n">
-        <v>6.51367139816284</v>
+        <v>6.513671875</v>
       </c>
       <c r="H186" t="n">
         <v>1000</v>
@@ -5850,7 +5850,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483777999878</v>
+        <v>6.72483730316162</v>
       </c>
       <c r="H189" t="n">
         <v>12503</v>
@@ -32144,7 +32144,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="D1096" t="n">
-        <v>17.9500007629395</v>
+        <v>18</v>
       </c>
       <c r="E1096" t="n">
         <v>17.7000007629395</v>
@@ -32159,6 +32159,35 @@
         <v>5379</v>
       </c>
       <c r="I1096" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1097" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1097" t="n">
+        <v>17.8500003814697</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>18</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>3475</v>
+      </c>
+      <c r="I1097" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GF.MI.xlsx
+++ b/data/GF.MI.xlsx
@@ -746,7 +746,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G13" t="n">
-        <v>5.86392879486084</v>
+        <v>5.86392831802368</v>
       </c>
       <c r="H13" t="n">
         <v>217</v>
@@ -775,7 +775,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G14" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H14" t="n">
         <v>22</v>
@@ -833,7 +833,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7745885848999</v>
+        <v>5.77458906173706</v>
       </c>
       <c r="H16" t="n">
         <v>4639</v>
@@ -949,7 +949,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G20" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H20" t="n">
         <v>1000</v>
@@ -1094,7 +1094,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G25" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H25" t="n">
         <v>308</v>
@@ -1268,7 +1268,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G31" t="n">
-        <v>5.82331991195679</v>
+        <v>5.82331943511963</v>
       </c>
       <c r="H31" t="n">
         <v>2124</v>
@@ -1326,7 +1326,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>5.72585821151733</v>
+        <v>5.72585868835449</v>
       </c>
       <c r="H33" t="n">
         <v>420</v>
@@ -1558,7 +1558,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G41" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H41" t="n">
         <v>271</v>
@@ -1790,7 +1790,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G49" t="n">
-        <v>5.79083204269409</v>
+        <v>5.79083251953125</v>
       </c>
       <c r="H49" t="n">
         <v>628</v>
@@ -1819,7 +1819,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G50" t="n">
-        <v>5.79083204269409</v>
+        <v>5.79083251953125</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>5.79083204269409</v>
+        <v>5.79083251953125</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G54" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H54" t="n">
         <v>6012</v>
@@ -2080,7 +2080,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>5.72585821151733</v>
+        <v>5.72585868835449</v>
       </c>
       <c r="H59" t="n">
         <v>150</v>
@@ -2109,7 +2109,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G60" t="n">
-        <v>5.72585821151733</v>
+        <v>5.72585868835449</v>
       </c>
       <c r="H60" t="n">
         <v>278</v>
@@ -2138,7 +2138,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G61" t="n">
-        <v>5.72585821151733</v>
+        <v>5.72585868835449</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H67" t="n">
         <v>897</v>
@@ -2486,7 +2486,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G73" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H73" t="n">
         <v>1650</v>
@@ -2515,7 +2515,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G74" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G75" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H75" t="n">
         <v>170</v>
@@ -2573,7 +2573,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G78" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H82" t="n">
         <v>1650</v>
@@ -2834,7 +2834,7 @@
         <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H85" t="n">
         <v>6618</v>
@@ -2863,7 +2863,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G86" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H86" t="n">
         <v>750</v>
@@ -2892,7 +2892,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H87" t="n">
         <v>2590</v>
@@ -2950,7 +2950,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>5.88017225265503</v>
+        <v>5.88017177581787</v>
       </c>
       <c r="H89" t="n">
         <v>846</v>
@@ -3037,7 +3037,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G92" t="n">
-        <v>5.86392879486084</v>
+        <v>5.86392831802368</v>
       </c>
       <c r="H92" t="n">
         <v>800</v>
@@ -3066,7 +3066,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G93" t="n">
-        <v>5.88017225265503</v>
+        <v>5.88017177581787</v>
       </c>
       <c r="H93" t="n">
         <v>1382</v>
@@ -3095,7 +3095,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>5.88017225265503</v>
+        <v>5.88017177581787</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H115" t="n">
         <v>65929</v>
@@ -3733,7 +3733,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G116" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H116" t="n">
         <v>1167</v>
@@ -3820,7 +3820,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>5.68524932861328</v>
+        <v>5.68524980545044</v>
       </c>
       <c r="H119" t="n">
         <v>5694</v>
@@ -3849,7 +3849,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G120" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H120" t="n">
         <v>359</v>
@@ -3936,7 +3936,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G123" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H123" t="n">
         <v>1400</v>
@@ -3965,7 +3965,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H124" t="n">
         <v>500</v>
@@ -3994,7 +3994,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G125" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H125" t="n">
         <v>3720</v>
@@ -4110,7 +4110,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H129" t="n">
         <v>3454</v>
@@ -4139,7 +4139,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G130" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H130" t="n">
         <v>4648</v>
@@ -4197,7 +4197,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>5.79895401000977</v>
+        <v>5.79895353317261</v>
       </c>
       <c r="H132" t="n">
         <v>1700</v>
@@ -4255,7 +4255,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>5.71773624420166</v>
+        <v>5.71773672103882</v>
       </c>
       <c r="H134" t="n">
         <v>9200</v>
@@ -4574,7 +4574,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G145" t="n">
-        <v>5.73397970199585</v>
+        <v>5.73398017883301</v>
       </c>
       <c r="H145" t="n">
         <v>3077</v>
@@ -4603,7 +4603,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G146" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H146" t="n">
         <v>8497</v>
@@ -4632,7 +4632,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G147" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H147" t="n">
         <v>1510</v>
@@ -4661,7 +4661,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H148" t="n">
         <v>2120</v>
@@ -4690,7 +4690,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G149" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G150" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H150" t="n">
         <v>110</v>
@@ -4777,7 +4777,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G152" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H152" t="n">
         <v>10236</v>
@@ -4893,7 +4893,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G156" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H156" t="n">
         <v>3175</v>
@@ -4922,7 +4922,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G157" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H157" t="n">
         <v>10385</v>
@@ -4951,7 +4951,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H158" t="n">
         <v>10088</v>
@@ -5009,7 +5009,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>5.8314414024353</v>
+        <v>5.83144092559814</v>
       </c>
       <c r="H160" t="n">
         <v>4793</v>
@@ -5038,7 +5038,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>5.81519794464111</v>
+        <v>5.81519746780396</v>
       </c>
       <c r="H161" t="n">
         <v>2050</v>
@@ -5067,7 +5067,7 @@
         <v>7.5</v>
       </c>
       <c r="G162" t="n">
-        <v>6.09133815765381</v>
+        <v>6.09133863449097</v>
       </c>
       <c r="H162" t="n">
         <v>81003</v>
@@ -5125,7 +5125,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G164" t="n">
-        <v>6.27001762390137</v>
+        <v>6.27001714706421</v>
       </c>
       <c r="H164" t="n">
         <v>62015</v>
@@ -5154,7 +5154,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H165" t="n">
         <v>10198</v>
@@ -5183,7 +5183,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G166" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H166" t="n">
         <v>5498</v>
@@ -5212,7 +5212,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H167" t="n">
         <v>7616</v>
@@ -5299,7 +5299,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G170" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H170" t="n">
         <v>3020</v>
@@ -5415,7 +5415,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>6.41621017456055</v>
+        <v>6.41621065139771</v>
       </c>
       <c r="H174" t="n">
         <v>550</v>
@@ -5444,7 +5444,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>6.41621017456055</v>
+        <v>6.41621065139771</v>
       </c>
       <c r="H175" t="n">
         <v>7100</v>
@@ -5473,7 +5473,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H176" t="n">
         <v>3660</v>
@@ -5531,7 +5531,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G178" t="n">
-        <v>6.39996671676636</v>
+        <v>6.3999662399292</v>
       </c>
       <c r="H178" t="n">
         <v>3628</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H179" t="n">
         <v>2200</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>6.33499193191528</v>
+        <v>6.33499240875244</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G189" t="n">
-        <v>6.72483730316162</v>
+        <v>6.72483777999878</v>
       </c>
       <c r="H189" t="n">
         <v>12503</v>
@@ -5879,7 +5879,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64362049102783</v>
+        <v>6.64362001419067</v>
       </c>
       <c r="H190" t="n">
         <v>15454</v>
@@ -5908,7 +5908,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G191" t="n">
-        <v>6.78981161117554</v>
+        <v>6.7898120880127</v>
       </c>
       <c r="H191" t="n">
         <v>35519</v>
@@ -6227,7 +6227,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H202" t="n">
         <v>1380</v>
@@ -6256,7 +6256,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G203" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H203" t="n">
         <v>1156</v>
@@ -6285,7 +6285,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G204" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H204" t="n">
         <v>725</v>
@@ -6314,7 +6314,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G205" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H205" t="n">
         <v>65</v>
@@ -6343,7 +6343,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H206" t="n">
         <v>250</v>
@@ -6401,7 +6401,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G208" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H208" t="n">
         <v>2722</v>
@@ -6488,7 +6488,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G211" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H211" t="n">
         <v>1850</v>
@@ -6691,7 +6691,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H218" t="n">
         <v>1060</v>
@@ -6720,7 +6720,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H219" t="n">
         <v>500</v>
@@ -6749,7 +6749,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H221" t="n">
         <v>10070</v>
@@ -6807,7 +6807,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G223" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H223" t="n">
         <v>1370</v>
@@ -6865,7 +6865,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H225" t="n">
         <v>474</v>
@@ -6923,7 +6923,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H229" t="n">
         <v>550</v>
@@ -7039,7 +7039,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G230" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H230" t="n">
         <v>1340</v>
@@ -7155,7 +7155,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H234" t="n">
         <v>800</v>
@@ -7184,7 +7184,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G237" t="n">
-        <v>6.59180641174316</v>
+        <v>6.59180593490601</v>
       </c>
       <c r="H237" t="n">
         <v>5618</v>
@@ -7271,7 +7271,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H238" t="n">
         <v>425</v>
@@ -7300,7 +7300,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H239" t="n">
         <v>10600</v>
@@ -7329,7 +7329,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G240" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H240" t="n">
         <v>30</v>
@@ -7358,7 +7358,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G241" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H241" t="n">
         <v>500</v>
@@ -7387,7 +7387,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G242" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H242" t="n">
         <v>200</v>
@@ -7416,7 +7416,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H243" t="n">
         <v>32675</v>
@@ -7445,7 +7445,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G244" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H245" t="n">
         <v>720</v>
@@ -7503,7 +7503,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H247" t="n">
         <v>5100</v>
@@ -7561,7 +7561,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H248" t="n">
         <v>5000</v>
@@ -7590,7 +7590,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H249" t="n">
         <v>3130</v>
@@ -7648,7 +7648,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H251" t="n">
         <v>4818</v>
@@ -7706,7 +7706,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H253" t="n">
         <v>3985</v>
@@ -7735,7 +7735,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G254" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H254" t="n">
         <v>501</v>
@@ -7909,7 +7909,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H260" t="n">
         <v>5</v>
@@ -7967,7 +7967,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H262" t="n">
         <v>1000</v>
@@ -7996,7 +7996,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H264" t="n">
         <v>5125</v>
@@ -8112,7 +8112,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H267" t="n">
         <v>1357</v>
@@ -8141,7 +8141,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H269" t="n">
         <v>331</v>
@@ -8228,7 +8228,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G271" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H271" t="n">
         <v>110</v>
@@ -8402,7 +8402,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H277" t="n">
         <v>972</v>
@@ -8460,7 +8460,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G279" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H279" t="n">
         <v>314</v>
@@ -8489,7 +8489,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>6.89143371582031</v>
+        <v>6.89143419265747</v>
       </c>
       <c r="H280" t="n">
         <v>1214</v>
@@ -8779,7 +8779,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H290" t="n">
         <v>760</v>
@@ -8808,7 +8808,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H292" t="n">
         <v>15</v>
@@ -8866,7 +8866,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H293" t="n">
         <v>655</v>
@@ -9098,7 +9098,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H301" t="n">
         <v>350</v>
@@ -9156,7 +9156,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H303" t="n">
         <v>4525</v>
@@ -9185,7 +9185,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H304" t="n">
         <v>300</v>
@@ -9214,7 +9214,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G307" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H307" t="n">
         <v>300</v>
@@ -9301,7 +9301,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G308" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H308" t="n">
         <v>1000</v>
@@ -9330,7 +9330,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H309" t="n">
         <v>1104</v>
@@ -9388,7 +9388,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H311" t="n">
         <v>2460</v>
@@ -9446,7 +9446,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G313" t="n">
-        <v>6.37778663635254</v>
+        <v>6.37778615951538</v>
       </c>
       <c r="H313" t="n">
         <v>12049</v>
@@ -9504,7 +9504,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>6.67741394042969</v>
+        <v>6.67741441726685</v>
       </c>
       <c r="H315" t="n">
         <v>4634</v>
@@ -9649,7 +9649,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H320" t="n">
         <v>1420013</v>
@@ -9678,7 +9678,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>6.76302194595337</v>
+        <v>6.76302242279053</v>
       </c>
       <c r="H321" t="n">
         <v>17270</v>
@@ -9823,7 +9823,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G326" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H326" t="n">
         <v>35969</v>
@@ -9910,7 +9910,7 @@
         <v>8.5</v>
       </c>
       <c r="G329" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H329" t="n">
         <v>4383</v>
@@ -10026,7 +10026,7 @@
         <v>8.25</v>
       </c>
       <c r="G333" t="n">
-        <v>7.06264972686768</v>
+        <v>7.06264925003052</v>
       </c>
       <c r="H333" t="n">
         <v>2000</v>
@@ -10055,7 +10055,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G334" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H334" t="n">
         <v>600</v>
@@ -10258,7 +10258,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G341" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H341" t="n">
         <v>444</v>
@@ -10287,7 +10287,7 @@
         <v>8.25</v>
       </c>
       <c r="G342" t="n">
-        <v>7.06264972686768</v>
+        <v>7.06264925003052</v>
       </c>
       <c r="H342" t="n">
         <v>250</v>
@@ -10374,7 +10374,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G345" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H345" t="n">
         <v>3340</v>
@@ -10403,7 +10403,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G346" t="n">
-        <v>6.93423795700073</v>
+        <v>6.93423748016357</v>
       </c>
       <c r="H346" t="n">
         <v>1470</v>
@@ -10548,7 +10548,7 @@
         <v>8.5</v>
       </c>
       <c r="G351" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H351" t="n">
         <v>441</v>
@@ -10577,7 +10577,7 @@
         <v>8.5</v>
       </c>
       <c r="G352" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>8.5</v>
       </c>
       <c r="G353" t="n">
-        <v>7.27666902542114</v>
+        <v>7.2766695022583</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>7.79031658172607</v>
+        <v>7.79031705856323</v>
       </c>
       <c r="H357" t="n">
         <v>4994</v>
@@ -10780,7 +10780,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G359" t="n">
-        <v>7.83312082290649</v>
+        <v>7.83312034606934</v>
       </c>
       <c r="H359" t="n">
         <v>11764</v>
@@ -10867,7 +10867,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H362" t="n">
         <v>13708</v>
@@ -10896,7 +10896,7 @@
         <v>10</v>
       </c>
       <c r="G363" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H363" t="n">
         <v>19547</v>
@@ -11012,7 +11012,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>8.30396366119385</v>
+        <v>8.30396270751953</v>
       </c>
       <c r="H367" t="n">
         <v>14100</v>
@@ -11186,7 +11186,7 @@
         <v>9.5</v>
       </c>
       <c r="G373" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H373" t="n">
         <v>1893</v>
@@ -11244,7 +11244,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>8.30396366119385</v>
+        <v>8.30396270751953</v>
       </c>
       <c r="H375" t="n">
         <v>609</v>
@@ -11273,7 +11273,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H376" t="n">
         <v>19650</v>
@@ -11302,7 +11302,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H377" t="n">
         <v>1925</v>
@@ -11331,7 +11331,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H378" t="n">
         <v>4890</v>
@@ -11360,7 +11360,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H379" t="n">
         <v>1750</v>
@@ -11389,7 +11389,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H380" t="n">
         <v>2479</v>
@@ -11418,7 +11418,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H381" t="n">
         <v>955</v>
@@ -11476,7 +11476,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G383" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H383" t="n">
         <v>500</v>
@@ -11505,7 +11505,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>7.96153163909912</v>
+        <v>7.96153259277344</v>
       </c>
       <c r="H384" t="n">
         <v>1430</v>
@@ -11563,7 +11563,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G386" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H386" t="n">
         <v>802</v>
@@ -11592,7 +11592,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>8.30396366119385</v>
+        <v>8.30396270751953</v>
       </c>
       <c r="H387" t="n">
         <v>1761</v>
@@ -11708,7 +11708,7 @@
         <v>9.5</v>
       </c>
       <c r="G391" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H391" t="n">
         <v>4396</v>
@@ -11940,7 +11940,7 @@
         <v>9.5</v>
       </c>
       <c r="G399" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H399" t="n">
         <v>4059</v>
@@ -11969,7 +11969,7 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>9.5</v>
       </c>
       <c r="G401" t="n">
-        <v>8.1327486038208</v>
+        <v>8.13274765014648</v>
       </c>
       <c r="H401" t="n">
         <v>2000</v>
@@ -12114,7 +12114,7 @@
         <v>10</v>
       </c>
       <c r="G405" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H405" t="n">
         <v>6672</v>
@@ -12201,7 +12201,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H408" t="n">
         <v>1750</v>
@@ -12259,7 +12259,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G410" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H410" t="n">
         <v>1015</v>
@@ -12346,7 +12346,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H413" t="n">
         <v>1223</v>
@@ -12375,7 +12375,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>8.26115894317627</v>
+        <v>8.26115989685059</v>
       </c>
       <c r="H414" t="n">
         <v>225</v>
@@ -12462,7 +12462,7 @@
         <v>9.75</v>
       </c>
       <c r="G417" t="n">
-        <v>8.34676837921143</v>
+        <v>8.34676742553711</v>
       </c>
       <c r="H417" t="n">
         <v>5344</v>
@@ -12491,7 +12491,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H418" t="n">
         <v>4587</v>
@@ -12520,7 +12520,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H419" t="n">
         <v>3997</v>
@@ -12694,7 +12694,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H425" t="n">
         <v>3177</v>
@@ -12723,7 +12723,7 @@
         <v>10</v>
       </c>
       <c r="G426" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H426" t="n">
         <v>4148</v>
@@ -12752,7 +12752,7 @@
         <v>10.5</v>
       </c>
       <c r="G427" t="n">
-        <v>8.98882579803467</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H427" t="n">
         <v>14779</v>
@@ -12810,7 +12810,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>8.98882579803467</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H429" t="n">
         <v>39883</v>
@@ -12955,7 +12955,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G434" t="n">
-        <v>9.24565029144287</v>
+        <v>9.24565124511719</v>
       </c>
       <c r="H434" t="n">
         <v>2641</v>
@@ -13071,7 +13071,7 @@
         <v>10</v>
       </c>
       <c r="G438" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H438" t="n">
         <v>11185</v>
@@ -13100,7 +13100,7 @@
         <v>10</v>
       </c>
       <c r="G439" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H439" t="n">
         <v>15109</v>
@@ -13129,7 +13129,7 @@
         <v>10</v>
       </c>
       <c r="G440" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H440" t="n">
         <v>6043</v>
@@ -13187,7 +13187,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H442" t="n">
         <v>90803</v>
@@ -13216,7 +13216,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>8.51798248291016</v>
+        <v>8.51798343658447</v>
       </c>
       <c r="H443" t="n">
         <v>7339</v>
@@ -13245,7 +13245,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G444" t="n">
-        <v>8.54366588592529</v>
+        <v>8.54366493225098</v>
       </c>
       <c r="H444" t="n">
         <v>5918</v>
@@ -13274,7 +13274,7 @@
         <v>10</v>
       </c>
       <c r="G445" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H445" t="n">
         <v>9128</v>
@@ -13303,7 +13303,7 @@
         <v>10</v>
       </c>
       <c r="G446" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H446" t="n">
         <v>7831</v>
@@ -13361,7 +13361,7 @@
         <v>10</v>
       </c>
       <c r="G448" t="n">
-        <v>8.56078815460205</v>
+        <v>8.56078720092773</v>
       </c>
       <c r="H448" t="n">
         <v>4670</v>
@@ -13419,7 +13419,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>8.8604154586792</v>
+        <v>8.86041450500488</v>
       </c>
       <c r="H450" t="n">
         <v>18892</v>
@@ -13448,7 +13448,7 @@
         <v>10.5</v>
       </c>
       <c r="G451" t="n">
-        <v>8.98882579803467</v>
+        <v>8.98882675170898</v>
       </c>
       <c r="H451" t="n">
         <v>20478</v>
@@ -13477,7 +13477,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>9.28845500946045</v>
+        <v>9.28845405578613</v>
       </c>
       <c r="H452" t="n">
         <v>71285</v>
@@ -13564,7 +13564,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>9.14202404022217</v>
+        <v>9.14202308654785</v>
       </c>
       <c r="H455" t="n">
         <v>31996</v>
@@ -13767,7 +13767,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H462" t="n">
         <v>2003</v>
@@ -13854,7 +13854,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G465" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H465" t="n">
         <v>14331</v>
@@ -13883,7 +13883,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H466" t="n">
         <v>15525</v>
@@ -13912,7 +13912,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H467" t="n">
         <v>4027</v>
@@ -14173,7 +14173,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H476" t="n">
         <v>4298</v>
@@ -14202,7 +14202,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H477" t="n">
         <v>8570</v>
@@ -14231,7 +14231,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H478" t="n">
         <v>208</v>
@@ -14260,7 +14260,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H479" t="n">
         <v>1263</v>
@@ -14318,7 +14318,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H481" t="n">
         <v>1124</v>
@@ -14463,7 +14463,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H486" t="n">
         <v>1373</v>
@@ -14579,7 +14579,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H490" t="n">
         <v>758</v>
@@ -14666,7 +14666,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G493" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H493" t="n">
         <v>524</v>
@@ -14695,7 +14695,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H494" t="n">
         <v>3075</v>
@@ -14869,7 +14869,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G500" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H500" t="n">
         <v>4578</v>
@@ -15362,7 +15362,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H517" t="n">
         <v>542</v>
@@ -15449,7 +15449,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G520" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H520" t="n">
         <v>1778</v>
@@ -15884,7 +15884,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H535" t="n">
         <v>2389</v>
@@ -15913,7 +15913,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G536" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H536" t="n">
         <v>150</v>
@@ -16087,7 +16087,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H542" t="n">
         <v>1350</v>
@@ -16232,7 +16232,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G547" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H547" t="n">
         <v>5100</v>
@@ -16348,7 +16348,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H551" t="n">
         <v>2999</v>
@@ -16377,7 +16377,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H552" t="n">
         <v>155</v>
@@ -16406,7 +16406,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H553" t="n">
         <v>128</v>
@@ -16435,7 +16435,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H554" t="n">
         <v>208</v>
@@ -16464,7 +16464,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H555" t="n">
         <v>1378</v>
@@ -16493,7 +16493,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H556" t="n">
         <v>9590</v>
@@ -16522,7 +16522,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H557" t="n">
         <v>2253</v>
@@ -16609,7 +16609,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H560" t="n">
         <v>575</v>
@@ -16899,7 +16899,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H570" t="n">
         <v>560</v>
@@ -16928,7 +16928,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>10.0924310684204</v>
+        <v>10.0924320220947</v>
       </c>
       <c r="H571" t="n">
         <v>390</v>
@@ -17189,7 +17189,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H580" t="n">
         <v>2025</v>
@@ -17276,7 +17276,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H583" t="n">
         <v>373</v>
@@ -17363,7 +17363,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G586" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H586" t="n">
         <v>237736</v>
@@ -17392,7 +17392,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H587" t="n">
         <v>4477</v>
@@ -17624,7 +17624,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G595" t="n">
-        <v>10.6807804107666</v>
+        <v>10.6807794570923</v>
       </c>
       <c r="H595" t="n">
         <v>972</v>
@@ -17653,7 +17653,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G596" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H596" t="n">
         <v>2317</v>
@@ -17682,7 +17682,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>9.82088756561279</v>
+        <v>9.82088661193848</v>
       </c>
       <c r="H597" t="n">
         <v>4064</v>
@@ -17914,7 +17914,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H605" t="n">
         <v>7786</v>
@@ -17943,7 +17943,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G606" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H606" t="n">
         <v>5869</v>
@@ -17972,7 +17972,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G607" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H607" t="n">
         <v>3504</v>
@@ -18001,7 +18001,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>9.91140079498291</v>
+        <v>9.91140174865723</v>
       </c>
       <c r="H608" t="n">
         <v>650</v>
@@ -18030,7 +18030,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H609" t="n">
         <v>2810</v>
@@ -18059,7 +18059,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>10.363977432251</v>
+        <v>10.3639764785767</v>
       </c>
       <c r="H610" t="n">
         <v>2274</v>
@@ -18088,7 +18088,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>10.2282037734985</v>
+        <v>10.2282047271729</v>
       </c>
       <c r="H611" t="n">
         <v>530</v>
@@ -18117,7 +18117,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>10.4544925689697</v>
+        <v>10.4544916152954</v>
       </c>
       <c r="H612" t="n">
         <v>1300</v>
@@ -18204,7 +18204,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>10.4544925689697</v>
+        <v>10.4544916152954</v>
       </c>
       <c r="H615" t="n">
         <v>6497</v>
@@ -18233,7 +18233,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H616" t="n">
         <v>954</v>
@@ -18262,7 +18262,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H617" t="n">
         <v>668</v>
@@ -18291,7 +18291,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>10.5450077056885</v>
+        <v>10.5450067520142</v>
       </c>
       <c r="H618" t="n">
         <v>458</v>
@@ -18349,7 +18349,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>11.495415687561</v>
+        <v>11.4954147338867</v>
       </c>
       <c r="H620" t="n">
         <v>18194</v>
@@ -18378,7 +18378,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H621" t="n">
         <v>3478</v>
@@ -18407,7 +18407,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H622" t="n">
         <v>1875</v>
@@ -18494,7 +18494,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H625" t="n">
         <v>550</v>
@@ -18610,7 +18610,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H629" t="n">
         <v>849</v>
@@ -18639,7 +18639,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H630" t="n">
         <v>1274</v>
@@ -18668,7 +18668,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>11.133355140686</v>
+        <v>11.1333560943604</v>
       </c>
       <c r="H631" t="n">
         <v>50</v>
@@ -18697,7 +18697,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H632" t="n">
         <v>919</v>
@@ -18726,7 +18726,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H633" t="n">
         <v>630</v>
@@ -18755,7 +18755,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H634" t="n">
         <v>529</v>
@@ -18784,7 +18784,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G635" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H635" t="n">
         <v>2833</v>
@@ -18900,7 +18900,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H639" t="n">
         <v>7525</v>
@@ -18929,7 +18929,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>11.4501571655273</v>
+        <v>11.4501581192017</v>
       </c>
       <c r="H640" t="n">
         <v>5598</v>
@@ -19016,7 +19016,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G643" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H643" t="n">
         <v>1624</v>
@@ -19074,7 +19074,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G645" t="n">
-        <v>11.1786127090454</v>
+        <v>11.1786136627197</v>
       </c>
       <c r="H645" t="n">
         <v>8997</v>
@@ -19103,7 +19103,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H646" t="n">
         <v>1298</v>
@@ -19132,7 +19132,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H647" t="n">
         <v>1027</v>
@@ -19161,7 +19161,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G648" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H648" t="n">
         <v>2656</v>
@@ -19248,7 +19248,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H651" t="n">
         <v>2853</v>
@@ -19277,7 +19277,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H652" t="n">
         <v>201</v>
@@ -19306,7 +19306,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H653" t="n">
         <v>2152</v>
@@ -19364,7 +19364,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G655" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H655" t="n">
         <v>1923</v>
@@ -19393,7 +19393,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H656" t="n">
         <v>3358</v>
@@ -19422,7 +19422,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H657" t="n">
         <v>2271</v>
@@ -19451,7 +19451,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H658" t="n">
         <v>3130</v>
@@ -19480,7 +19480,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>11.2691268920898</v>
+        <v>11.2691278457642</v>
       </c>
       <c r="H659" t="n">
         <v>1473</v>
@@ -19509,7 +19509,7 @@
         <v>12.75</v>
       </c>
       <c r="G660" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H660" t="n">
         <v>6035</v>
@@ -19538,7 +19538,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>11.3596429824829</v>
+        <v>11.3596439361572</v>
       </c>
       <c r="H661" t="n">
         <v>51639</v>
@@ -19654,7 +19654,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H665" t="n">
         <v>655</v>
@@ -19683,7 +19683,7 @@
         <v>12.75</v>
       </c>
       <c r="G666" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H666" t="n">
         <v>3045</v>
@@ -19712,7 +19712,7 @@
         <v>12.75</v>
       </c>
       <c r="G667" t="n">
-        <v>11.5406732559204</v>
+        <v>11.5406723022461</v>
       </c>
       <c r="H667" t="n">
         <v>2279</v>
@@ -19886,7 +19886,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G673" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H673" t="n">
         <v>17329</v>
@@ -19915,7 +19915,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>11.7217035293579</v>
+        <v>11.7217025756836</v>
       </c>
       <c r="H674" t="n">
         <v>6333</v>
@@ -19944,7 +19944,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>12.8078842163086</v>
+        <v>12.8078832626343</v>
       </c>
       <c r="H675" t="n">
         <v>6880</v>
@@ -20089,7 +20089,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>13.4867477416992</v>
+        <v>13.4867467880249</v>
       </c>
       <c r="H680" t="n">
         <v>11651</v>
@@ -20147,7 +20147,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>12.8531408309937</v>
+        <v>12.853141784668</v>
       </c>
       <c r="H682" t="n">
         <v>7422</v>
@@ -20176,7 +20176,7 @@
         <v>14</v>
       </c>
       <c r="G683" t="n">
-        <v>12.6721115112305</v>
+        <v>12.6721124649048</v>
       </c>
       <c r="H683" t="n">
         <v>6279</v>
@@ -20205,7 +20205,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>12.8531408309937</v>
+        <v>12.853141784668</v>
       </c>
       <c r="H684" t="n">
         <v>7438</v>
@@ -20321,7 +20321,7 @@
         <v>15</v>
       </c>
       <c r="G688" t="n">
-        <v>13.5772619247437</v>
+        <v>13.577262878418</v>
       </c>
       <c r="H688" t="n">
         <v>15723</v>
@@ -20437,7 +20437,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>14.5729293823242</v>
+        <v>14.5729284286499</v>
       </c>
       <c r="H692" t="n">
         <v>25981</v>
@@ -20669,7 +20669,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>14.1203536987305</v>
+        <v>14.1203527450562</v>
       </c>
       <c r="H700" t="n">
         <v>6735</v>
@@ -20727,7 +20727,7 @@
         <v>15.5</v>
       </c>
       <c r="G702" t="n">
-        <v>14.0298385620117</v>
+        <v>14.0298376083374</v>
       </c>
       <c r="H702" t="n">
         <v>16297</v>
@@ -20756,7 +20756,7 @@
         <v>15.5</v>
       </c>
       <c r="G703" t="n">
-        <v>14.0298385620117</v>
+        <v>14.0298376083374</v>
       </c>
       <c r="H703" t="n">
         <v>6474</v>
@@ -32188,6 +32188,35 @@
         <v>3475</v>
       </c>
       <c r="I1097" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1098" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1098" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>18.0499992370605</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1098" t="n">
+        <v>4104</v>
+      </c>
+      <c r="I1098" t="s">
         <v>9</v>
       </c>
     </row>
